--- a/research/traditional_assets/database/data/brazil/brazil_beverage_alcoholic.xlsx
+++ b/research/traditional_assets/database/data/brazil/brazil_beverage_alcoholic.xlsx
@@ -650,10 +650,10 @@
         <v>0.1417030483115043</v>
       </c>
       <c r="X2">
-        <v>0.09956078329235418</v>
+        <v>0.09955263690515964</v>
       </c>
       <c r="Y2">
-        <v>0.04214226501915017</v>
+        <v>0.04215041140634471</v>
       </c>
       <c r="Z2">
         <v>2.054324808600749</v>
@@ -662,10 +662,10 @@
         <v>0.4082582570406104</v>
       </c>
       <c r="AB2">
-        <v>0.09862430177725047</v>
+        <v>0.09861632133517827</v>
       </c>
       <c r="AC2">
-        <v>0.3096339552633599</v>
+        <v>0.3096419357054321</v>
       </c>
       <c r="AD2">
         <v>620.8</v>
@@ -787,10 +787,10 @@
         <v>0.1417030483115043</v>
       </c>
       <c r="X3">
-        <v>0.09956078329235418</v>
+        <v>0.09955263690515964</v>
       </c>
       <c r="Y3">
-        <v>0.04214226501915017</v>
+        <v>0.04215041140634471</v>
       </c>
       <c r="Z3">
         <v>2.054324808600749</v>
@@ -799,10 +799,10 @@
         <v>0.4082582570406104</v>
       </c>
       <c r="AB3">
-        <v>0.09862430177725047</v>
+        <v>0.09861632133517827</v>
       </c>
       <c r="AC3">
-        <v>0.3096339552633599</v>
+        <v>0.3096419357054321</v>
       </c>
       <c r="AD3">
         <v>620.8</v>
@@ -1139,49 +1139,49 @@
         <v>9.580713342140029</v>
       </c>
       <c r="F2">
-        <v>3.06153378762142</v>
+        <v>3.03189972105768</v>
       </c>
       <c r="G2">
         <v>0.143414882066209</v>
       </c>
       <c r="H2">
-        <v>3.30896851248643</v>
+        <v>3.44977568323053</v>
       </c>
       <c r="I2">
         <v>0.0203703946763969</v>
       </c>
       <c r="J2">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="K2">
         <v>29854.8</v>
       </c>
       <c r="L2">
-        <v>18387.966141948</v>
+        <v>18390.5125357187</v>
       </c>
       <c r="M2">
         <v>26842.2</v>
       </c>
       <c r="N2">
-        <v>29078.098141948</v>
+        <v>29690.1565357187</v>
       </c>
       <c r="O2">
         <v>620.8</v>
       </c>
       <c r="P2">
-        <v>14323.532</v>
+        <v>14933.044</v>
       </c>
       <c r="Q2">
-        <v>0.0986243017772505</v>
+        <v>0.09861632133517829</v>
       </c>
       <c r="R2">
-        <v>0.09448400238928049</v>
+        <v>0.09345140317606231</v>
       </c>
       <c r="S2">
         <v>0.0535881092239028</v>
       </c>
       <c r="T2">
-        <v>0.0545781092239028</v>
+        <v>0.0528621092239028</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.0995607832923542</v>
+        <v>0.0995526369051596</v>
       </c>
       <c r="X2">
-        <v>0.129872247271785</v>
+        <v>0.13244896011049</v>
       </c>
       <c r="Y2">
         <v>0.700577053917513</v>
       </c>
       <c r="Z2">
-        <v>1.09557717917902</v>
+        <v>1.12932642367534</v>
       </c>
       <c r="AA2">
         <v>620.8</v>
@@ -1236,7 +1236,7 @@
         <v>29854.8</v>
       </c>
       <c r="AK2">
-        <v>0.07673785915729414</v>
+        <v>0.07672623104708272</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.09883295769346132</v>
+        <v>0.09882492159389236</v>
       </c>
       <c r="C2">
-        <v>30371.98481860654</v>
+        <v>30372.01160100004</v>
       </c>
       <c r="D2">
-        <v>26738.58481860654</v>
+        <v>26738.61160100004</v>
       </c>
       <c r="E2">
         <v>-620.8</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.09883295769346132</v>
+        <v>0.09882492159389236</v>
       </c>
       <c r="T2">
         <v>0.6910924838905985</v>
       </c>
       <c r="U2">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V2">
         <v>0.34</v>
       </c>
       <c r="W2">
-        <v>0.0504861092239028</v>
+        <v>0.0495621092239028</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.09869950672954257</v>
+        <v>0.09868225795271214</v>
       </c>
       <c r="C3">
-        <v>30133.40599774067</v>
+        <v>30138.01401390921</v>
       </c>
       <c r="D3">
-        <v>26804.76199774067</v>
+        <v>26809.37001390921</v>
       </c>
       <c r="E3">
         <v>-316.044</v>
@@ -1539,37 +1539,37 @@
         <v>3626.3</v>
       </c>
       <c r="M3">
-        <v>23.312037428242</v>
+        <v>22.885379028242</v>
       </c>
       <c r="N3">
-        <v>3602.987962571758</v>
+        <v>3603.414620971758</v>
       </c>
       <c r="O3">
-        <v>1225.015907274398</v>
+        <v>1225.160971130398</v>
       </c>
       <c r="P3">
-        <v>2377.97205529736</v>
+        <v>2378.25364984136</v>
       </c>
       <c r="Q3">
-        <v>3080.37205529736</v>
+        <v>3080.65364984136</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.09918651074475106</v>
+        <v>0.09917842107118496</v>
       </c>
       <c r="T3">
         <v>0.6956997671165358</v>
       </c>
       <c r="U3">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V3">
         <v>0.34</v>
       </c>
       <c r="W3">
-        <v>0.0504861092239028</v>
+        <v>0.0495621092239028</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>155.5548291805168</v>
+        <v>158.4548805385708</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.09856605576562384</v>
+        <v>0.09853959431153193</v>
       </c>
       <c r="C4">
-        <v>29895.15556260565</v>
+        <v>29904.39191658594</v>
       </c>
       <c r="D4">
-        <v>26871.26756260565</v>
+        <v>26880.50391658594</v>
       </c>
       <c r="E4">
         <v>-11.28800000000001</v>
@@ -1621,37 +1621,37 @@
         <v>3626.3</v>
       </c>
       <c r="M4">
-        <v>46.62407485648401</v>
+        <v>45.77075805648401</v>
       </c>
       <c r="N4">
-        <v>3579.675925143516</v>
+        <v>3580.529241943516</v>
       </c>
       <c r="O4">
-        <v>1217.089814548796</v>
+        <v>1217.379942260796</v>
       </c>
       <c r="P4">
-        <v>2362.586110594721</v>
+        <v>2363.149299682721</v>
       </c>
       <c r="Q4">
-        <v>3064.98611059472</v>
+        <v>3065.549299682721</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.09954727916443447</v>
+        <v>0.09953913482352436</v>
       </c>
       <c r="T4">
         <v>0.7004010765307576</v>
       </c>
       <c r="U4">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V4">
         <v>0.34</v>
       </c>
       <c r="W4">
-        <v>0.0504861092239028</v>
+        <v>0.0495621092239028</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>77.77741459025842</v>
+        <v>79.22744026928541</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.0984326048017051</v>
+        <v>0.09839693067035173</v>
       </c>
       <c r="C5">
-        <v>29657.23596356454</v>
+        <v>29671.14830586806</v>
       </c>
       <c r="D5">
-        <v>26938.10396356454</v>
+        <v>26952.01630586806</v>
       </c>
       <c r="E5">
         <v>293.468</v>
@@ -1703,37 +1703,37 @@
         <v>3626.3</v>
       </c>
       <c r="M5">
-        <v>69.93611228472601</v>
+        <v>68.65613708472601</v>
       </c>
       <c r="N5">
-        <v>3556.363887715274</v>
+        <v>3557.643862915274</v>
       </c>
       <c r="O5">
-        <v>1209.163721823193</v>
+        <v>1209.598913391193</v>
       </c>
       <c r="P5">
-        <v>2347.200165892081</v>
+        <v>2348.044949524081</v>
       </c>
       <c r="Q5">
-        <v>3049.60016589208</v>
+        <v>3050.444949524081</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.09991548610823507</v>
+        <v>0.09990728597281923</v>
       </c>
       <c r="T5">
         <v>0.7051993201597057</v>
       </c>
       <c r="U5">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V5">
         <v>0.34</v>
       </c>
       <c r="W5">
-        <v>0.0504861092239028</v>
+        <v>0.0495621092239028</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>51.85160972683895</v>
+        <v>52.81829351285693</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.09829915383778634</v>
+        <v>0.09825426702917152</v>
       </c>
       <c r="C6">
-        <v>29419.64967542014</v>
+        <v>29438.28621056941</v>
       </c>
       <c r="D6">
-        <v>27005.27367542014</v>
+        <v>27023.91021056941</v>
       </c>
       <c r="E6">
         <v>598.2239999999999</v>
@@ -1785,37 +1785,37 @@
         <v>3626.3</v>
       </c>
       <c r="M6">
-        <v>93.24814971296802</v>
+        <v>91.54151611296801</v>
       </c>
       <c r="N6">
-        <v>3533.051850287032</v>
+        <v>3534.758483887032</v>
       </c>
       <c r="O6">
-        <v>1201.237629097591</v>
+        <v>1201.817884521591</v>
       </c>
       <c r="P6">
-        <v>2331.814221189441</v>
+        <v>2332.940599365441</v>
       </c>
       <c r="Q6">
-        <v>3034.214221189441</v>
+        <v>3035.340599365441</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.1002913640300315</v>
+        <v>0.1002831069377244</v>
       </c>
       <c r="T6">
         <v>0.71009752719759</v>
       </c>
       <c r="U6">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V6">
         <v>0.34</v>
       </c>
       <c r="W6">
-        <v>0.0504861092239028</v>
+        <v>0.0495621092239028</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>38.88870729512922</v>
+        <v>39.6137201346427</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.09816570287386761</v>
+        <v>0.09811160338799133</v>
       </c>
       <c r="C7">
-        <v>29182.39919772047</v>
+        <v>29205.80869190744</v>
       </c>
       <c r="D7">
-        <v>27072.77919772047</v>
+        <v>27096.18869190743</v>
       </c>
       <c r="E7">
         <v>902.98</v>
@@ -1867,37 +1867,37 @@
         <v>3626.3</v>
       </c>
       <c r="M7">
-        <v>116.56018714121</v>
+        <v>114.42689514121</v>
       </c>
       <c r="N7">
-        <v>3509.73981285879</v>
+        <v>3511.87310485879</v>
       </c>
       <c r="O7">
-        <v>1193.311536371989</v>
+        <v>1194.036855651989</v>
       </c>
       <c r="P7">
-        <v>2316.428276486801</v>
+        <v>2317.836249206801</v>
       </c>
       <c r="Q7">
-        <v>3018.828276486801</v>
+        <v>3020.236249206801</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.1006751551712342</v>
+        <v>0.1006668399229434</v>
       </c>
       <c r="T7">
         <v>0.7150988543836404</v>
       </c>
       <c r="U7">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V7">
         <v>0.34</v>
       </c>
       <c r="W7">
-        <v>0.0504861092239028</v>
+        <v>0.0495621092239028</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>31.11096583610337</v>
+        <v>31.69097610771416</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.09803225190994888</v>
+        <v>0.09796893974681112</v>
       </c>
       <c r="C8">
-        <v>28945.48705506883</v>
+        <v>28973.71884393769</v>
       </c>
       <c r="D8">
-        <v>27140.62305506883</v>
+        <v>27168.85484393769</v>
       </c>
       <c r="E8">
         <v>1207.736</v>
@@ -1949,37 +1949,37 @@
         <v>3626.3</v>
       </c>
       <c r="M8">
-        <v>139.872224569452</v>
+        <v>137.312274169452</v>
       </c>
       <c r="N8">
-        <v>3486.427775430548</v>
+        <v>3488.987725830548</v>
       </c>
       <c r="O8">
-        <v>1185.385443646386</v>
+        <v>1186.255826782387</v>
       </c>
       <c r="P8">
-        <v>2301.042331784161</v>
+        <v>2302.731899048162</v>
       </c>
       <c r="Q8">
-        <v>3003.442331784161</v>
+        <v>3005.131899048161</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.1010671120813986</v>
+        <v>0.1010587374397627</v>
       </c>
       <c r="T8">
         <v>0.7202065927864153</v>
       </c>
       <c r="U8">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V8">
         <v>0.34</v>
       </c>
       <c r="W8">
-        <v>0.0504861092239028</v>
+        <v>0.0495621092239028</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>25.92580486341948</v>
+        <v>26.40914675642847</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.09789880094603014</v>
+        <v>0.09782627610563091</v>
       </c>
       <c r="C9">
-        <v>28708.91579743854</v>
+        <v>28742.01979399533</v>
       </c>
       <c r="D9">
-        <v>27208.80779743854</v>
+        <v>27241.91179399533</v>
       </c>
       <c r="E9">
         <v>1512.492</v>
@@ -2031,37 +2031,37 @@
         <v>3626.3</v>
       </c>
       <c r="M9">
-        <v>163.184261997694</v>
+        <v>160.197653197694</v>
       </c>
       <c r="N9">
-        <v>3463.115738002306</v>
+        <v>3466.102346802306</v>
       </c>
       <c r="O9">
-        <v>1177.459350920784</v>
+        <v>1178.474797912784</v>
       </c>
       <c r="P9">
-        <v>2285.656387081522</v>
+        <v>2287.627548889522</v>
       </c>
       <c r="Q9">
-        <v>2988.056387081521</v>
+        <v>2990.027548889522</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.1014674981724268</v>
+        <v>0.1014590628601696</v>
       </c>
       <c r="T9">
         <v>0.725424175025809</v>
       </c>
       <c r="U9">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V9">
         <v>0.34</v>
       </c>
       <c r="W9">
-        <v>0.0504861092239028</v>
+        <v>0.0495621092239028</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>22.22211845435955</v>
+        <v>22.63641150551011</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.09776534998211139</v>
+        <v>0.0976836124644507</v>
       </c>
       <c r="C10">
-        <v>28472.68800049238</v>
+        <v>28510.7147031438</v>
       </c>
       <c r="D10">
-        <v>27277.33600049238</v>
+        <v>27315.3627031438</v>
       </c>
       <c r="E10">
         <v>1817.248</v>
@@ -2113,37 +2113,37 @@
         <v>3626.3</v>
       </c>
       <c r="M10">
-        <v>186.496299425936</v>
+        <v>183.083032225936</v>
       </c>
       <c r="N10">
-        <v>3439.803700574064</v>
+        <v>3443.216967774064</v>
       </c>
       <c r="O10">
-        <v>1169.533258195182</v>
+        <v>1170.693769043182</v>
       </c>
       <c r="P10">
-        <v>2270.270442378882</v>
+        <v>2272.523198730882</v>
       </c>
       <c r="Q10">
-        <v>2972.670442378882</v>
+        <v>2974.923198730882</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.1018765883089121</v>
+        <v>0.101868091007107</v>
       </c>
       <c r="T10">
         <v>0.7307551829660589</v>
       </c>
       <c r="U10">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V10">
         <v>0.34</v>
       </c>
       <c r="W10">
-        <v>0.0504861092239028</v>
+        <v>0.0495621092239028</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>19.44435364756461</v>
+        <v>19.80686006732135</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.09763189901819266</v>
+        <v>0.09754094882327051</v>
       </c>
       <c r="C11">
-        <v>28236.80626590696</v>
+        <v>28279.80676663071</v>
       </c>
       <c r="D11">
-        <v>27346.21026590696</v>
+        <v>27389.21076663071</v>
       </c>
       <c r="E11">
         <v>2122.004</v>
@@ -2195,37 +2195,37 @@
         <v>3626.3</v>
       </c>
       <c r="M11">
-        <v>209.808336854178</v>
+        <v>205.968411254178</v>
       </c>
       <c r="N11">
-        <v>3416.491663145822</v>
+        <v>3420.331588745822</v>
       </c>
       <c r="O11">
-        <v>1161.60716546958</v>
+        <v>1162.91274017358</v>
       </c>
       <c r="P11">
-        <v>2254.884497676243</v>
+        <v>2257.418848572242</v>
       </c>
       <c r="Q11">
-        <v>2957.284497676242</v>
+        <v>2959.818848572242</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.1022946694374081</v>
+        <v>0.1022861087836475</v>
       </c>
       <c r="T11">
         <v>0.7362033559159848</v>
       </c>
       <c r="U11">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V11">
         <v>0.34</v>
       </c>
       <c r="W11">
-        <v>0.0504861092239028</v>
+        <v>0.0495621092239028</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>17.28386990894632</v>
+        <v>17.60609783761898</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.09749844805427391</v>
+        <v>0.09739828518209029</v>
       </c>
       <c r="C12">
-        <v>28001.27322170197</v>
+        <v>28049.29921435125</v>
       </c>
       <c r="D12">
-        <v>27415.43322170197</v>
+        <v>27463.45921435125</v>
       </c>
       <c r="E12">
         <v>2426.76</v>
@@ -2277,37 +2277,37 @@
         <v>3626.3</v>
       </c>
       <c r="M12">
-        <v>233.12037428242</v>
+        <v>228.8537902824201</v>
       </c>
       <c r="N12">
-        <v>3393.17962571758</v>
+        <v>3397.44620971758</v>
       </c>
       <c r="O12">
-        <v>1153.681072743977</v>
+        <v>1155.131711303977</v>
       </c>
       <c r="P12">
-        <v>2239.498552973603</v>
+        <v>2242.314498413603</v>
       </c>
       <c r="Q12">
-        <v>2941.898552973602</v>
+        <v>2944.714498413603</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.1027220412576485</v>
+        <v>0.1027134158441111</v>
       </c>
       <c r="T12">
         <v>0.741772599375909</v>
       </c>
       <c r="U12">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V12">
         <v>0.34</v>
       </c>
       <c r="W12">
-        <v>0.0504861092239028</v>
+        <v>0.0495621092239028</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>15.55548291805168</v>
+        <v>15.84548805385708</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.09736499709035518</v>
+        <v>0.09725562154091008</v>
       </c>
       <c r="C13">
-        <v>27766.09152257436</v>
+        <v>27819.19531131901</v>
       </c>
       <c r="D13">
-        <v>27485.00752257436</v>
+        <v>27538.111311319</v>
       </c>
       <c r="E13">
         <v>2731.516</v>
@@ -2359,37 +2359,37 @@
         <v>3626.3</v>
       </c>
       <c r="M13">
-        <v>256.4324117106621</v>
+        <v>251.739169310662</v>
       </c>
       <c r="N13">
-        <v>3369.867588289338</v>
+        <v>3374.560830689338</v>
       </c>
       <c r="O13">
-        <v>1145.754980018375</v>
+        <v>1147.350682434375</v>
       </c>
       <c r="P13">
-        <v>2224.112608270963</v>
+        <v>2227.210148254963</v>
       </c>
       <c r="Q13">
-        <v>2926.512608270963</v>
+        <v>2929.610148254963</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.1031590169390178</v>
+        <v>0.1031503253104278</v>
       </c>
       <c r="T13">
         <v>0.7474669943742585</v>
       </c>
       <c r="U13">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V13">
         <v>0.34</v>
       </c>
       <c r="W13">
-        <v>0.0504861092239028</v>
+        <v>0.0495621092239028</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>14.14134810731971</v>
+        <v>14.40498913987007</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.09723154612643643</v>
+        <v>0.09711295789972989</v>
       </c>
       <c r="C14">
-        <v>27531.26385023787</v>
+        <v>27589.49835814461</v>
       </c>
       <c r="D14">
-        <v>27554.93585023787</v>
+        <v>27613.17035814461</v>
       </c>
       <c r="E14">
         <v>3036.272</v>
@@ -2441,37 +2441,37 @@
         <v>3626.3</v>
       </c>
       <c r="M14">
-        <v>279.744449138904</v>
+        <v>274.624548338904</v>
       </c>
       <c r="N14">
-        <v>3346.555550861096</v>
+        <v>3351.675451661096</v>
       </c>
       <c r="O14">
-        <v>1137.828887292773</v>
+        <v>1139.569653564773</v>
       </c>
       <c r="P14">
-        <v>2208.726663568324</v>
+        <v>2212.105798096323</v>
       </c>
       <c r="Q14">
-        <v>2911.126663568323</v>
+        <v>2914.505798096323</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.1036059238858728</v>
+        <v>0.1035971645373427</v>
       </c>
       <c r="T14">
         <v>0.7532908074407524</v>
       </c>
       <c r="U14">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V14">
         <v>0.34</v>
       </c>
       <c r="W14">
-        <v>0.0504861092239028</v>
+        <v>0.0495621092239028</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>12.96290243170974</v>
+        <v>13.20457337821423</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.0970980951625177</v>
+        <v>0.09697029425854967</v>
       </c>
       <c r="C15">
-        <v>27296.79291376743</v>
+        <v>27360.21169152223</v>
       </c>
       <c r="D15">
-        <v>27625.22091376743</v>
+        <v>27688.63969152222</v>
       </c>
       <c r="E15">
         <v>3341.028</v>
@@ -2523,37 +2523,37 @@
         <v>3626.3</v>
       </c>
       <c r="M15">
-        <v>303.0564865671461</v>
+        <v>297.5099273671461</v>
       </c>
       <c r="N15">
-        <v>3323.243513432854</v>
+        <v>3328.790072632854</v>
       </c>
       <c r="O15">
-        <v>1129.902794567171</v>
+        <v>1131.78862469517</v>
       </c>
       <c r="P15">
-        <v>2193.340718865684</v>
+        <v>2197.001447937683</v>
       </c>
       <c r="Q15">
-        <v>2895.740718865683</v>
+        <v>2899.401447937683</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.1040631045556441</v>
+        <v>0.1040542759303935</v>
       </c>
       <c r="T15">
         <v>0.7592485012673955</v>
       </c>
       <c r="U15">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V15">
         <v>0.34</v>
       </c>
       <c r="W15">
-        <v>0.0504861092239028</v>
+        <v>0.0495621092239028</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.96575609080899</v>
+        <v>12.18883696450544</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.09696464419859895</v>
+        <v>0.09682763061736946</v>
       </c>
       <c r="C16">
-        <v>27062.68144994912</v>
+        <v>27131.33868472389</v>
       </c>
       <c r="D16">
-        <v>27695.86544994912</v>
+        <v>27764.52268472389</v>
       </c>
       <c r="E16">
         <v>3645.784</v>
@@ -2605,37 +2605,37 @@
         <v>3626.3</v>
       </c>
       <c r="M16">
-        <v>326.368523995388</v>
+        <v>320.395306395388</v>
       </c>
       <c r="N16">
-        <v>3299.931476004612</v>
+        <v>3305.904693604612</v>
       </c>
       <c r="O16">
-        <v>1121.976701841568</v>
+        <v>1124.007595825568</v>
       </c>
       <c r="P16">
-        <v>2177.954774163044</v>
+        <v>2181.897097779044</v>
       </c>
       <c r="Q16">
-        <v>2880.354774163044</v>
+        <v>2884.297097779044</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.1045309173340146</v>
+        <v>0.1045220178209571</v>
       </c>
       <c r="T16">
         <v>0.7653447461132628</v>
       </c>
       <c r="U16">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V16">
         <v>0.34</v>
       </c>
       <c r="W16">
-        <v>0.0504861092239028</v>
+        <v>0.0495621092239028</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.11105922717977</v>
+        <v>11.31820575275506</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.0968311932346802</v>
+        <v>0.09668496697618927</v>
       </c>
       <c r="C17">
-        <v>26828.93222363531</v>
+        <v>26902.88274810221</v>
       </c>
       <c r="D17">
-        <v>27766.87222363531</v>
+        <v>27840.82274810221</v>
       </c>
       <c r="E17">
         <v>3950.539999999999</v>
@@ -2687,37 +2687,37 @@
         <v>3626.3</v>
       </c>
       <c r="M17">
-        <v>349.68056142363</v>
+        <v>343.28068542363</v>
       </c>
       <c r="N17">
-        <v>3276.61943857637</v>
+        <v>3283.01931457637</v>
       </c>
       <c r="O17">
-        <v>1114.050609115966</v>
+        <v>1116.226566955966</v>
       </c>
       <c r="P17">
-        <v>2162.568829460404</v>
+        <v>2166.792747620404</v>
       </c>
       <c r="Q17">
-        <v>2864.968829460404</v>
+        <v>2869.192747620404</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.1050097374718762</v>
+        <v>0.1050007654030633</v>
       </c>
       <c r="T17">
         <v>0.771584432014327</v>
       </c>
       <c r="U17">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V17">
         <v>0.34</v>
       </c>
       <c r="W17">
-        <v>0.0504861092239028</v>
+        <v>0.0495621092239028</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>10.37032194536779</v>
+        <v>10.56365870257139</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.09669774227076146</v>
+        <v>0.09654230333500906</v>
       </c>
       <c r="C18">
-        <v>26595.54802810543</v>
+        <v>26674.84732960127</v>
       </c>
       <c r="D18">
-        <v>27838.24402810542</v>
+        <v>27917.54332960127</v>
       </c>
       <c r="E18">
         <v>4255.295999999999</v>
@@ -2769,37 +2769,37 @@
         <v>3626.3</v>
       </c>
       <c r="M18">
-        <v>372.9925988518721</v>
+        <v>366.166064451872</v>
       </c>
       <c r="N18">
-        <v>3253.307401148128</v>
+        <v>3260.133935548128</v>
       </c>
       <c r="O18">
-        <v>1106.124516390364</v>
+        <v>1108.445538086364</v>
       </c>
       <c r="P18">
-        <v>2147.182884757764</v>
+        <v>2151.688397461764</v>
       </c>
       <c r="Q18">
-        <v>2849.582884757764</v>
+        <v>2854.088397461764</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.1054999580892107</v>
+        <v>0.1054909117371245</v>
       </c>
       <c r="T18">
         <v>0.7779726818654166</v>
       </c>
       <c r="U18">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V18">
         <v>0.34</v>
       </c>
       <c r="W18">
-        <v>0.0504861092239028</v>
+        <v>0.0495621092239028</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>9.722176823782302</v>
+        <v>9.903430033660676</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.09656429130684273</v>
+        <v>0.09639963969382884</v>
       </c>
       <c r="C19">
-        <v>26362.53168543222</v>
+        <v>26447.23591527597</v>
       </c>
       <c r="D19">
-        <v>27909.98368543222</v>
+        <v>27994.68791527597</v>
       </c>
       <c r="E19">
         <v>4560.052</v>
@@ -2851,37 +2851,37 @@
         <v>3626.3</v>
       </c>
       <c r="M19">
-        <v>396.3046362801141</v>
+        <v>389.0514434801141</v>
       </c>
       <c r="N19">
-        <v>3229.995363719886</v>
+        <v>3237.248556519886</v>
       </c>
       <c r="O19">
-        <v>1098.198423664761</v>
+        <v>1100.664509216761</v>
       </c>
       <c r="P19">
-        <v>2131.796940055125</v>
+        <v>2136.584047303125</v>
       </c>
       <c r="Q19">
-        <v>2834.196940055124</v>
+        <v>2838.984047303124</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.1060019912515413</v>
+        <v>0.1059928688262233</v>
       </c>
       <c r="T19">
         <v>0.7845148654478578</v>
       </c>
       <c r="U19">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V19">
         <v>0.34</v>
       </c>
       <c r="W19">
-        <v>0.0504861092239028</v>
+        <v>0.0495621092239028</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>9.150284069442167</v>
+        <v>9.320875325798282</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.096430840342924</v>
+        <v>0.09625697605264866</v>
       </c>
       <c r="C20">
-        <v>26129.88604685376</v>
+        <v>26220.05202982002</v>
       </c>
       <c r="D20">
-        <v>27982.09404685376</v>
+        <v>28072.26002982002</v>
       </c>
       <c r="E20">
         <v>4864.807999999999</v>
@@ -2933,37 +2933,37 @@
         <v>3626.3</v>
       </c>
       <c r="M20">
-        <v>419.616673708356</v>
+        <v>411.936822508356</v>
       </c>
       <c r="N20">
-        <v>3206.683326291644</v>
+        <v>3214.363177491644</v>
       </c>
       <c r="O20">
-        <v>1090.272330939159</v>
+        <v>1092.883480347159</v>
       </c>
       <c r="P20">
-        <v>2116.410995352485</v>
+        <v>2121.479697144485</v>
       </c>
       <c r="Q20">
-        <v>2818.810995352484</v>
+        <v>2823.879697144484</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.1065162691251482</v>
+        <v>0.1065070687711538</v>
       </c>
       <c r="T20">
         <v>0.7912166144835291</v>
       </c>
       <c r="U20">
-        <v>0.07649410488470122</v>
+        <v>0.07509410488470122</v>
       </c>
       <c r="V20">
         <v>0.34</v>
       </c>
       <c r="W20">
-        <v>0.0504861092239028</v>
+        <v>0.0495621092239028</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.641934954473161</v>
+        <v>8.803048918809488</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.09643532937900526</v>
+        <v>0.09630241241146845</v>
       </c>
       <c r="C21">
-        <v>25822.69833596348</v>
+        <v>25890.54379061448</v>
       </c>
       <c r="D21">
-        <v>27979.66233596347</v>
+        <v>28047.50779061448</v>
       </c>
       <c r="E21">
         <v>5169.563999999999</v>
@@ -3015,37 +3015,37 @@
         <v>3626.3</v>
       </c>
       <c r="M21">
-        <v>449.2981115365981</v>
+        <v>443.5077475365981</v>
       </c>
       <c r="N21">
-        <v>3177.001888463402</v>
+        <v>3182.792252463402</v>
       </c>
       <c r="O21">
-        <v>1080.180642077557</v>
+        <v>1082.149365837557</v>
       </c>
       <c r="P21">
-        <v>2096.821246385845</v>
+        <v>2100.642886625846</v>
       </c>
       <c r="Q21">
-        <v>2799.221246385845</v>
+        <v>2803.042886625845</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.1070432452178564</v>
+        <v>0.1070339650110209</v>
       </c>
       <c r="T21">
         <v>0.7980838388040319</v>
       </c>
       <c r="U21">
-        <v>0.07759410488470123</v>
+        <v>0.07659410488470123</v>
       </c>
       <c r="V21">
         <v>0.34</v>
       </c>
       <c r="W21">
-        <v>0.0512121092239028</v>
+        <v>0.0505521092239028</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.071033255844469</v>
+        <v>8.176407334802555</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.09630913841508652</v>
+        <v>0.09616964877028823</v>
       </c>
       <c r="C22">
-        <v>25586.46142769396</v>
+        <v>25658.23595491345</v>
       </c>
       <c r="D22">
-        <v>28048.18142769395</v>
+        <v>28119.95595491344</v>
       </c>
       <c r="E22">
         <v>5474.32</v>
@@ -3097,37 +3097,37 @@
         <v>3626.3</v>
       </c>
       <c r="M22">
-        <v>472.9453805648401</v>
+        <v>466.8502605648401</v>
       </c>
       <c r="N22">
-        <v>3153.35461943516</v>
+        <v>3159.44973943516</v>
       </c>
       <c r="O22">
-        <v>1072.140570607954</v>
+        <v>1074.212911407955</v>
       </c>
       <c r="P22">
-        <v>2081.214048827206</v>
+        <v>2085.236828027206</v>
       </c>
       <c r="Q22">
-        <v>2783.614048827205</v>
+        <v>2787.636828027205</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.1075833957128824</v>
+        <v>0.1075740336568846</v>
       </c>
       <c r="T22">
         <v>0.8051227437325473</v>
       </c>
       <c r="U22">
-        <v>0.07759410488470123</v>
+        <v>0.07659410488470123</v>
       </c>
       <c r="V22">
         <v>0.34</v>
       </c>
       <c r="W22">
-        <v>0.0512121092239028</v>
+        <v>0.0505521092239028</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>7.667481593052244</v>
+        <v>7.767586968062426</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.09618294745116777</v>
+        <v>0.09603688512910803</v>
       </c>
       <c r="C23">
-        <v>25350.56093458956</v>
+        <v>25426.30336320333</v>
       </c>
       <c r="D23">
-        <v>28117.03693458956</v>
+        <v>28192.77936320332</v>
       </c>
       <c r="E23">
         <v>5779.075999999999</v>
@@ -3179,37 +3179,37 @@
         <v>3626.3</v>
       </c>
       <c r="M23">
-        <v>496.5926495930821</v>
+        <v>490.1927735930821</v>
       </c>
       <c r="N23">
-        <v>3129.707350406918</v>
+        <v>3136.107226406918</v>
       </c>
       <c r="O23">
-        <v>1064.100499138352</v>
+        <v>1066.276456978352</v>
       </c>
       <c r="P23">
-        <v>2065.606851268566</v>
+        <v>2069.830769428566</v>
       </c>
       <c r="Q23">
-        <v>2768.006851268566</v>
+        <v>2772.230769428566</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.108137220903985</v>
+        <v>0.1081277749266942</v>
       </c>
       <c r="T23">
         <v>0.8123398487858351</v>
       </c>
       <c r="U23">
-        <v>0.07759410488470123</v>
+        <v>0.07659410488470123</v>
       </c>
       <c r="V23">
         <v>0.34</v>
       </c>
       <c r="W23">
-        <v>0.0512121092239028</v>
+        <v>0.0505521092239028</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.302363421954518</v>
+        <v>7.397701874345168</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.09605675648724903</v>
+        <v>0.09590412148792783</v>
       </c>
       <c r="C24">
-        <v>25114.99934034522</v>
+        <v>25194.74893840822</v>
       </c>
       <c r="D24">
-        <v>28186.23134034522</v>
+        <v>28265.98093840822</v>
       </c>
       <c r="E24">
         <v>6083.831999999999</v>
@@ -3261,37 +3261,37 @@
         <v>3626.3</v>
       </c>
       <c r="M24">
-        <v>520.2399186213241</v>
+        <v>513.5352866213241</v>
       </c>
       <c r="N24">
-        <v>3106.060081378676</v>
+        <v>3112.764713378676</v>
       </c>
       <c r="O24">
-        <v>1056.06042766875</v>
+        <v>1058.34000254875</v>
       </c>
       <c r="P24">
-        <v>2049.999653709926</v>
+        <v>2054.424710829926</v>
       </c>
       <c r="Q24">
-        <v>2752.399653709926</v>
+        <v>2756.824710829926</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.1087052467410133</v>
+        <v>0.1086957146906015</v>
       </c>
       <c r="T24">
         <v>0.8197420078148484</v>
       </c>
       <c r="U24">
-        <v>0.07759410488470123</v>
+        <v>0.07659410488470123</v>
       </c>
       <c r="V24">
         <v>0.34</v>
       </c>
       <c r="W24">
-        <v>0.0512121092239028</v>
+        <v>0.0505521092239028</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.970437811865676</v>
+        <v>7.06144269823857</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.09626452552333027</v>
+        <v>0.09577135784674762</v>
       </c>
       <c r="C25">
-        <v>24696.49767155521</v>
+        <v>24963.57563388832</v>
       </c>
       <c r="D25">
-        <v>28072.48567155521</v>
+        <v>28339.56363388832</v>
       </c>
       <c r="E25">
         <v>6388.588</v>
@@ -3343,45 +3343,45 @@
         <v>3626.3</v>
       </c>
       <c r="M25">
-        <v>559.3078412495661</v>
+        <v>536.8777996495661</v>
       </c>
       <c r="N25">
-        <v>3066.992158750434</v>
+        <v>3089.422200350434</v>
       </c>
       <c r="O25">
-        <v>1042.777333975148</v>
+        <v>1050.403548119148</v>
       </c>
       <c r="P25">
-        <v>2024.214824775286</v>
+        <v>2039.018652231287</v>
       </c>
       <c r="Q25">
-        <v>2726.614824775286</v>
+        <v>2741.418652231286</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.1092880264958865</v>
+        <v>0.1092784061366883</v>
       </c>
       <c r="T25">
         <v>0.8273364307147451</v>
       </c>
       <c r="U25">
-        <v>0.07979410488470122</v>
+        <v>0.07659410488470123</v>
       </c>
       <c r="V25">
         <v>0.34</v>
       </c>
       <c r="W25">
-        <v>0.0526641092239028</v>
+        <v>0.0505521092239028</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y25">
-        <v>6.483549366835939</v>
+        <v>6.754423450489067</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.09615285455941154</v>
+        <v>0.09590787420556741</v>
       </c>
       <c r="C26">
-        <v>24452.76293116203</v>
+        <v>24583.16259117241</v>
       </c>
       <c r="D26">
-        <v>28133.50693116203</v>
+        <v>28263.90659117241</v>
       </c>
       <c r="E26">
         <v>6693.343999999999</v>
@@ -3425,37 +3425,37 @@
         <v>3626.3</v>
       </c>
       <c r="M26">
-        <v>583.6255734778081</v>
+        <v>572.654357477808</v>
       </c>
       <c r="N26">
-        <v>3042.674426522192</v>
+        <v>3053.645642522192</v>
       </c>
       <c r="O26">
-        <v>1034.509305017546</v>
+        <v>1038.239518457546</v>
       </c>
       <c r="P26">
-        <v>2008.165121504647</v>
+        <v>2015.406124064647</v>
       </c>
       <c r="Q26">
-        <v>2710.565121504646</v>
+        <v>2717.806124064647</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.1098861425600985</v>
+        <v>0.1098764315681983</v>
       </c>
       <c r="T26">
         <v>0.8351307068488495</v>
       </c>
       <c r="U26">
-        <v>0.07979410488470122</v>
+        <v>0.07829410488470122</v>
       </c>
       <c r="V26">
         <v>0.34</v>
       </c>
       <c r="W26">
-        <v>0.0526641092239028</v>
+        <v>0.05167410922390279</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.213401476551109</v>
+        <v>6.332441118533756</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.09604118359549281</v>
+        <v>0.09578633056438721</v>
       </c>
       <c r="C27">
-        <v>24209.29405292224</v>
+        <v>24345.74601942384</v>
       </c>
       <c r="D27">
-        <v>28194.79405292224</v>
+        <v>28331.24601942384</v>
       </c>
       <c r="E27">
         <v>6998.099999999999</v>
@@ -3507,37 +3507,37 @@
         <v>3626.3</v>
       </c>
       <c r="M27">
-        <v>607.9433057060501</v>
+        <v>596.51495570605</v>
       </c>
       <c r="N27">
-        <v>3018.35669429395</v>
+        <v>3029.78504429395</v>
       </c>
       <c r="O27">
-        <v>1026.241276059943</v>
+        <v>1030.126915059943</v>
       </c>
       <c r="P27">
-        <v>1992.115418234007</v>
+        <v>1999.658129234007</v>
       </c>
       <c r="Q27">
-        <v>2694.515418234007</v>
+        <v>2702.058129234007</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1105002083860228</v>
+        <v>0.1104904043445487</v>
       </c>
       <c r="T27">
         <v>0.8431328303465302</v>
       </c>
       <c r="U27">
-        <v>0.07979410488470122</v>
+        <v>0.07829410488470122</v>
       </c>
       <c r="V27">
         <v>0.34</v>
       </c>
       <c r="W27">
-        <v>0.0526641092239028</v>
+        <v>0.05167410922390279</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.964865417489064</v>
+        <v>6.079143473792406</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.09592951263157408</v>
+        <v>0.095664786923207</v>
       </c>
       <c r="C28">
-        <v>23966.09277812237</v>
+        <v>24108.65108956673</v>
       </c>
       <c r="D28">
-        <v>28256.34877812236</v>
+        <v>28398.90708956673</v>
       </c>
       <c r="E28">
         <v>7302.856</v>
@@ -3589,37 +3589,37 @@
         <v>3626.3</v>
       </c>
       <c r="M28">
-        <v>632.2610379342922</v>
+        <v>620.3755539342922</v>
       </c>
       <c r="N28">
-        <v>2994.038962065708</v>
+        <v>3005.924446065708</v>
       </c>
       <c r="O28">
-        <v>1017.973247102341</v>
+        <v>1022.014311662341</v>
       </c>
       <c r="P28">
-        <v>1976.065714963367</v>
+        <v>1983.910134403367</v>
       </c>
       <c r="Q28">
-        <v>2678.465714963367</v>
+        <v>2686.310134403367</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1111308705856207</v>
+        <v>0.1111209709797193</v>
       </c>
       <c r="T28">
         <v>0.8513512274522563</v>
       </c>
       <c r="U28">
-        <v>0.07979410488470122</v>
+        <v>0.07829410488470122</v>
       </c>
       <c r="V28">
         <v>0.34</v>
       </c>
       <c r="W28">
-        <v>0.0526641092239028</v>
+        <v>0.05167410922390279</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.735447516816407</v>
+        <v>5.845330263261928</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.09608514166765532</v>
+        <v>0.09554324328202679</v>
       </c>
       <c r="C29">
-        <v>23575.62519764464</v>
+        <v>23871.88011156647</v>
       </c>
       <c r="D29">
-        <v>28170.63719764464</v>
+        <v>28466.89211156647</v>
       </c>
       <c r="E29">
         <v>7607.612</v>
@@ -3671,45 +3671,45 @@
         <v>3626.3</v>
       </c>
       <c r="M29">
-        <v>668.9213881625342</v>
+        <v>644.2361521625342</v>
       </c>
       <c r="N29">
-        <v>2957.378611837466</v>
+        <v>2982.063847837466</v>
       </c>
       <c r="O29">
-        <v>1005.508728024739</v>
+        <v>1013.901708264738</v>
       </c>
       <c r="P29">
-        <v>1951.869883812727</v>
+        <v>1968.162139572727</v>
       </c>
       <c r="Q29">
-        <v>2654.269883812727</v>
+        <v>2670.562139572727</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.111778811201646</v>
+        <v>0.1117688134131138</v>
       </c>
       <c r="T29">
         <v>0.8597947861225227</v>
       </c>
       <c r="U29">
-        <v>0.08129410488470122</v>
+        <v>0.07829410488470122</v>
       </c>
       <c r="V29">
         <v>0.34</v>
       </c>
       <c r="W29">
-        <v>0.0536541092239028</v>
+        <v>0.05167410922390279</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>5.421115342060021</v>
+        <v>5.628836549807782</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.09598337070373658</v>
+        <v>0.09556953964084658</v>
       </c>
       <c r="C30">
-        <v>23326.85987466918</v>
+        <v>23552.38775343516</v>
       </c>
       <c r="D30">
-        <v>28226.62787466918</v>
+        <v>28452.15575343516</v>
       </c>
       <c r="E30">
         <v>7912.367999999999</v>
@@ -3753,37 +3753,37 @@
         <v>3626.3</v>
       </c>
       <c r="M30">
-        <v>693.6962543907762</v>
+        <v>674.9232847907762</v>
       </c>
       <c r="N30">
-        <v>2932.603745609224</v>
+        <v>2951.376715209224</v>
       </c>
       <c r="O30">
-        <v>997.0852735071362</v>
+        <v>1003.468083171136</v>
       </c>
       <c r="P30">
-        <v>1935.518472102088</v>
+        <v>1947.908632038088</v>
       </c>
       <c r="Q30">
-        <v>2637.918472102087</v>
+        <v>2650.308632038088</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1124447501681164</v>
+        <v>0.1124346514696581</v>
       </c>
       <c r="T30">
         <v>0.8684728880891854</v>
       </c>
       <c r="U30">
-        <v>0.08129410488470122</v>
+        <v>0.07909410488470123</v>
       </c>
       <c r="V30">
         <v>0.34</v>
       </c>
       <c r="W30">
-        <v>0.0536541092239028</v>
+        <v>0.0522021092239028</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.227504079843591</v>
+        <v>5.37290693878511</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.09588159973981783</v>
+        <v>0.09545327599966637</v>
       </c>
       <c r="C31">
-        <v>23078.31756398815</v>
+        <v>23312.90101863055</v>
       </c>
       <c r="D31">
-        <v>28282.84156398815</v>
+        <v>28517.42501863055</v>
       </c>
       <c r="E31">
         <v>8217.124</v>
@@ -3835,37 +3835,37 @@
         <v>3626.3</v>
       </c>
       <c r="M31">
-        <v>718.4711206190181</v>
+        <v>699.0276878190182</v>
       </c>
       <c r="N31">
-        <v>2907.828879380982</v>
+        <v>2927.272312180982</v>
       </c>
       <c r="O31">
-        <v>988.6618189895339</v>
+        <v>995.272586141534</v>
       </c>
       <c r="P31">
-        <v>1919.167060391448</v>
+        <v>1931.999726039448</v>
       </c>
       <c r="Q31">
-        <v>2621.567060391448</v>
+        <v>2634.399726039448</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1131294479787127</v>
+        <v>0.1131192455277951</v>
       </c>
       <c r="T31">
         <v>0.8773954436323739</v>
       </c>
       <c r="U31">
-        <v>0.08129410488470122</v>
+        <v>0.07909410488470123</v>
       </c>
       <c r="V31">
         <v>0.34</v>
       </c>
       <c r="W31">
-        <v>0.0536541092239028</v>
+        <v>0.0522021092239028</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.047245318469675</v>
+        <v>5.187634285723555</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.09577982877589911</v>
+        <v>0.09533701235848616</v>
       </c>
       <c r="C32">
-        <v>22829.99960065578</v>
+        <v>23073.71442783652</v>
       </c>
       <c r="D32">
-        <v>28339.27960065578</v>
+        <v>28582.99442783652</v>
       </c>
       <c r="E32">
         <v>8521.879999999999</v>
@@ -3917,37 +3917,37 @@
         <v>3626.3</v>
       </c>
       <c r="M32">
-        <v>743.24598684726</v>
+        <v>723.1320908472601</v>
       </c>
       <c r="N32">
-        <v>2883.05401315274</v>
+        <v>2903.16790915274</v>
       </c>
       <c r="O32">
-        <v>980.2383644719317</v>
+        <v>987.0770891119317</v>
       </c>
       <c r="P32">
-        <v>1902.815648680808</v>
+        <v>1916.090820040808</v>
       </c>
       <c r="Q32">
-        <v>2605.215648680808</v>
+        <v>2618.490820040808</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1138337085838975</v>
+        <v>0.1138233994161648</v>
       </c>
       <c r="T32">
         <v>0.8865729293339393</v>
       </c>
       <c r="U32">
-        <v>0.08129410488470122</v>
+        <v>0.07909410488470123</v>
       </c>
       <c r="V32">
         <v>0.34</v>
       </c>
       <c r="W32">
-        <v>0.0536541092239028</v>
+        <v>0.0522021092239028</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.879003807854019</v>
+        <v>5.014713142866103</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.09567805781198037</v>
+        <v>0.09522074871730596</v>
       </c>
       <c r="C33">
-        <v>22581.907330404</v>
+        <v>22834.83005616538</v>
       </c>
       <c r="D33">
-        <v>28395.943330404</v>
+        <v>28648.86605616538</v>
       </c>
       <c r="E33">
         <v>8826.636</v>
@@ -3999,37 +3999,37 @@
         <v>3626.3</v>
       </c>
       <c r="M33">
-        <v>768.0208530755021</v>
+        <v>747.2364938755022</v>
       </c>
       <c r="N33">
-        <v>2858.279146924498</v>
+        <v>2879.063506124498</v>
       </c>
       <c r="O33">
-        <v>971.8149099543294</v>
+        <v>978.8815920823293</v>
       </c>
       <c r="P33">
-        <v>1886.464236970169</v>
+        <v>1900.181914042169</v>
       </c>
       <c r="Q33">
-        <v>2588.864236970168</v>
+        <v>2602.581914042168</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1145583825399573</v>
+        <v>0.1145479635621683</v>
       </c>
       <c r="T33">
         <v>0.8960164291138109</v>
       </c>
       <c r="U33">
-        <v>0.08129410488470122</v>
+        <v>0.07909410488470123</v>
       </c>
       <c r="V33">
         <v>0.34</v>
       </c>
       <c r="W33">
-        <v>0.0536541092239028</v>
+        <v>0.0522021092239028</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.721616588245825</v>
+        <v>4.852948202773648</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.09557628684806163</v>
+        <v>0.09510448507612576</v>
       </c>
       <c r="C34">
-        <v>22334.04210974931</v>
+        <v>22596.24999790267</v>
       </c>
       <c r="D34">
-        <v>28452.8341097493</v>
+        <v>28715.04199790266</v>
       </c>
       <c r="E34">
         <v>9131.392</v>
@@ -4081,37 +4081,37 @@
         <v>3626.3</v>
       </c>
       <c r="M34">
-        <v>792.7957193037441</v>
+        <v>771.3408969037441</v>
       </c>
       <c r="N34">
-        <v>2833.504280696256</v>
+        <v>2854.959103096256</v>
       </c>
       <c r="O34">
-        <v>963.3914554367271</v>
+        <v>970.6860950527272</v>
       </c>
       <c r="P34">
-        <v>1870.112825259529</v>
+        <v>1884.273008043529</v>
       </c>
       <c r="Q34">
-        <v>2572.512825259529</v>
+        <v>2586.673008043529</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1153043704359011</v>
+        <v>0.1152938384183483</v>
       </c>
       <c r="T34">
         <v>0.9057376788872079</v>
       </c>
       <c r="U34">
-        <v>0.08129410488470122</v>
+        <v>0.07909410488470123</v>
       </c>
       <c r="V34">
         <v>0.34</v>
       </c>
       <c r="W34">
-        <v>0.0536541092239028</v>
+        <v>0.0522021092239028</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.574066069863143</v>
+        <v>4.701293571436972</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.09547451588414288</v>
+        <v>0.09498822143494554</v>
       </c>
       <c r="C35">
-        <v>22086.40530610106</v>
+        <v>22357.97636672903</v>
       </c>
       <c r="D35">
-        <v>28509.95330610106</v>
+        <v>28781.52436672903</v>
       </c>
       <c r="E35">
         <v>9436.148000000001</v>
@@ -4163,37 +4163,37 @@
         <v>3626.3</v>
       </c>
       <c r="M35">
-        <v>817.5705855319862</v>
+        <v>795.4452999319863</v>
       </c>
       <c r="N35">
-        <v>2808.729414468014</v>
+        <v>2830.854700068014</v>
       </c>
       <c r="O35">
-        <v>954.9680009191248</v>
+        <v>962.4905980231247</v>
       </c>
       <c r="P35">
-        <v>1853.761413548889</v>
+        <v>1868.364102044889</v>
       </c>
       <c r="Q35">
-        <v>2556.161413548889</v>
+        <v>2570.764102044889</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1160726266272462</v>
+        <v>0.1160619781956084</v>
       </c>
       <c r="T35">
         <v>0.915749115221005</v>
       </c>
       <c r="U35">
-        <v>0.08129410488470122</v>
+        <v>0.07909410488470123</v>
       </c>
       <c r="V35">
         <v>0.34</v>
       </c>
       <c r="W35">
-        <v>0.0536541092239028</v>
+        <v>0.0522021092239028</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.435458007140017</v>
+        <v>4.558830129878275</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.09537274492022413</v>
+        <v>0.09487195779376534</v>
       </c>
       <c r="C36">
-        <v>21838.99829787102</v>
+        <v>22120.0112959453</v>
       </c>
       <c r="D36">
-        <v>28567.30229787101</v>
+        <v>28848.3152959453</v>
       </c>
       <c r="E36">
         <v>9740.904</v>
@@ -4245,37 +4245,37 @@
         <v>3626.3</v>
       </c>
       <c r="M36">
-        <v>842.3454517602281</v>
+        <v>819.5497029602283</v>
       </c>
       <c r="N36">
-        <v>2783.954548239772</v>
+        <v>2806.750297039772</v>
       </c>
       <c r="O36">
-        <v>946.5445464015226</v>
+        <v>954.2951009935225</v>
       </c>
       <c r="P36">
-        <v>1837.41000183825</v>
+        <v>1852.455196046249</v>
       </c>
       <c r="Q36">
-        <v>2539.810001838249</v>
+        <v>2554.855196046249</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1168641633092382</v>
+        <v>0.1168533949358158</v>
       </c>
       <c r="T36">
         <v>0.926063928413402</v>
       </c>
       <c r="U36">
-        <v>0.08129410488470122</v>
+        <v>0.07909410488470123</v>
       </c>
       <c r="V36">
         <v>0.34</v>
       </c>
       <c r="W36">
-        <v>0.0536541092239028</v>
+        <v>0.0522021092239028</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.305003359871193</v>
+        <v>4.424746890764208</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.09559437395630541</v>
+        <v>0.09475569415258514</v>
       </c>
       <c r="C37">
-        <v>21409.64662136292</v>
+        <v>21882.35693870067</v>
       </c>
       <c r="D37">
-        <v>28442.70662136292</v>
+        <v>28915.41693870067</v>
       </c>
       <c r="E37">
         <v>10045.66</v>
@@ -4327,45 +4327,45 @@
         <v>3626.3</v>
       </c>
       <c r="M37">
-        <v>882.0533619884702</v>
+        <v>843.6541059884703</v>
       </c>
       <c r="N37">
-        <v>2744.24663801153</v>
+        <v>2782.64589401153</v>
       </c>
       <c r="O37">
-        <v>933.0438569239203</v>
+        <v>946.0996039639202</v>
       </c>
       <c r="P37">
-        <v>1811.20278108761</v>
+        <v>1836.54629004761</v>
       </c>
       <c r="Q37">
-        <v>2513.602781087609</v>
+        <v>2538.946290047609</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1176800549660607</v>
+        <v>0.1176691629603372</v>
       </c>
       <c r="T37">
         <v>0.9366961204732573</v>
       </c>
       <c r="U37">
-        <v>0.08269410488470122</v>
+        <v>0.07909410488470123</v>
       </c>
       <c r="V37">
         <v>0.34</v>
       </c>
       <c r="W37">
-        <v>0.0545781092239028</v>
+        <v>0.0522021092239028</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y37">
-        <v>4.111202514805903</v>
+        <v>4.298325551028087</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.09550184299238666</v>
+        <v>0.09487703051140495</v>
       </c>
       <c r="C38">
-        <v>21156.77739118908</v>
+        <v>21507.57866321506</v>
       </c>
       <c r="D38">
-        <v>28494.59339118907</v>
+        <v>28845.39466321505</v>
       </c>
       <c r="E38">
         <v>10350.416</v>
@@ -4409,37 +4409,37 @@
         <v>3626.3</v>
       </c>
       <c r="M38">
-        <v>907.254886616712</v>
+        <v>878.7297250167121</v>
       </c>
       <c r="N38">
-        <v>2719.045113383288</v>
+        <v>2747.570274983288</v>
       </c>
       <c r="O38">
-        <v>924.475338550318</v>
+        <v>934.173893494318</v>
       </c>
       <c r="P38">
-        <v>1794.56977483297</v>
+        <v>1813.39638148897</v>
       </c>
       <c r="Q38">
-        <v>2496.96977483297</v>
+        <v>2515.79638148897</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1185214432371588</v>
+        <v>0.1185104237356249</v>
       </c>
       <c r="T38">
         <v>0.9476605685349831</v>
       </c>
       <c r="U38">
-        <v>0.08269410488470122</v>
+        <v>0.08009410488470123</v>
       </c>
       <c r="V38">
         <v>0.34</v>
       </c>
       <c r="W38">
-        <v>0.0545781092239028</v>
+        <v>0.0528621092239028</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.997002444950184</v>
+        <v>4.126752398106293</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.09540931202846792</v>
+        <v>0.09476736687022473</v>
       </c>
       <c r="C39">
-        <v>20904.09781646704</v>
+        <v>21266.09392783671</v>
       </c>
       <c r="D39">
-        <v>28546.66981646703</v>
+        <v>28908.6659278367</v>
       </c>
       <c r="E39">
         <v>10655.172</v>
@@ -4491,37 +4491,37 @@
         <v>3626.3</v>
       </c>
       <c r="M39">
-        <v>932.4564112449542</v>
+        <v>903.1388840449542</v>
       </c>
       <c r="N39">
-        <v>2693.843588755046</v>
+        <v>2723.161115955046</v>
       </c>
       <c r="O39">
-        <v>915.9068201767157</v>
+        <v>925.8747794247156</v>
       </c>
       <c r="P39">
-        <v>1777.93676857833</v>
+        <v>1797.28633653033</v>
       </c>
       <c r="Q39">
-        <v>2480.33676857833</v>
+        <v>2499.68633653033</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.119389542247022</v>
+        <v>0.1193783912021916</v>
       </c>
       <c r="T39">
         <v>0.9589730943129543</v>
       </c>
       <c r="U39">
-        <v>0.08269410488470122</v>
+        <v>0.08009410488470123</v>
       </c>
       <c r="V39">
         <v>0.34</v>
       </c>
       <c r="W39">
-        <v>0.0545781092239028</v>
+        <v>0.0528621092239028</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.888975351843422</v>
+        <v>4.015218549508825</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.09531678106454917</v>
+        <v>0.09465770322904453</v>
       </c>
       <c r="C40">
-        <v>20651.60893893772</v>
+        <v>21024.88736880214</v>
       </c>
       <c r="D40">
-        <v>28598.93693893771</v>
+        <v>28972.21536880214</v>
       </c>
       <c r="E40">
         <v>10959.928</v>
@@ -4573,37 +4573,37 @@
         <v>3626.3</v>
       </c>
       <c r="M40">
-        <v>957.6579358731962</v>
+        <v>927.5480430731963</v>
       </c>
       <c r="N40">
-        <v>2668.642064126804</v>
+        <v>2698.751956926804</v>
       </c>
       <c r="O40">
-        <v>907.3383018031135</v>
+        <v>917.5756653551134</v>
       </c>
       <c r="P40">
-        <v>1761.303762323691</v>
+        <v>1781.17629157169</v>
       </c>
       <c r="Q40">
-        <v>2463.70376232369</v>
+        <v>2483.57629157169</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1202856444507518</v>
+        <v>0.1202743576192927</v>
       </c>
       <c r="T40">
         <v>0.9706505402773116</v>
       </c>
       <c r="U40">
-        <v>0.08269410488470122</v>
+        <v>0.08009410488470123</v>
       </c>
       <c r="V40">
         <v>0.34</v>
       </c>
       <c r="W40">
-        <v>0.0545781092239028</v>
+        <v>0.0528621092239028</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.786633895215964</v>
+        <v>3.909554903469119</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.09522425010063043</v>
+        <v>0.09454803958786433</v>
       </c>
       <c r="C41">
-        <v>20399.31180798549</v>
+        <v>20783.9608246844</v>
       </c>
       <c r="D41">
-        <v>28651.39580798549</v>
+        <v>29036.0448246844</v>
       </c>
       <c r="E41">
         <v>11264.684</v>
@@ -4655,37 +4655,37 @@
         <v>3626.3</v>
       </c>
       <c r="M41">
-        <v>982.8594605014382</v>
+        <v>951.9572021014383</v>
       </c>
       <c r="N41">
-        <v>2643.440539498562</v>
+        <v>2674.342797898562</v>
       </c>
       <c r="O41">
-        <v>898.7697834295111</v>
+        <v>909.2765512855111</v>
       </c>
       <c r="P41">
-        <v>1744.670756069051</v>
+        <v>1765.066246613051</v>
       </c>
       <c r="Q41">
-        <v>2447.070756069051</v>
+        <v>2467.46624661305</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1212111270546039</v>
+        <v>0.1211996999844955</v>
       </c>
       <c r="T41">
         <v>0.9827108533224674</v>
       </c>
       <c r="U41">
-        <v>0.08269410488470122</v>
+        <v>0.08009410488470123</v>
       </c>
       <c r="V41">
         <v>0.34</v>
       </c>
       <c r="W41">
-        <v>0.0545781092239028</v>
+        <v>0.0528621092239028</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.689540718415554</v>
+        <v>3.80930990594427</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.0951317191367117</v>
+        <v>0.09443837594668412</v>
       </c>
       <c r="C42">
-        <v>20147.20748070836</v>
+        <v>20543.31615029475</v>
       </c>
       <c r="D42">
-        <v>28704.04748070836</v>
+        <v>29100.15615029474</v>
       </c>
       <c r="E42">
         <v>11569.44</v>
@@ -4737,37 +4737,37 @@
         <v>3626.3</v>
       </c>
       <c r="M42">
-        <v>1008.06098512968</v>
+        <v>976.3663611296803</v>
       </c>
       <c r="N42">
-        <v>2618.23901487032</v>
+        <v>2649.93363887032</v>
       </c>
       <c r="O42">
-        <v>890.2012650559088</v>
+        <v>900.9774372159088</v>
       </c>
       <c r="P42">
-        <v>1728.037749814411</v>
+        <v>1748.956201654411</v>
       </c>
       <c r="Q42">
-        <v>2430.43774981441</v>
+        <v>2451.356201654411</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1221674590785843</v>
+        <v>0.122155887095205</v>
       </c>
       <c r="T42">
         <v>0.9951731768024619</v>
       </c>
       <c r="U42">
-        <v>0.08269410488470122</v>
+        <v>0.08009410488470123</v>
       </c>
       <c r="V42">
         <v>0.34</v>
       </c>
       <c r="W42">
-        <v>0.0545781092239028</v>
+        <v>0.0528621092239028</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.597302200455165</v>
+        <v>3.714077158295663</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.09503918817279296</v>
+        <v>0.09432871230550391</v>
       </c>
       <c r="C43">
-        <v>19895.29702198908</v>
+        <v>20302.9552168623</v>
       </c>
       <c r="D43">
-        <v>28756.89302198908</v>
+        <v>29164.5512168623</v>
       </c>
       <c r="E43">
         <v>11874.196</v>
@@ -4819,37 +4819,37 @@
         <v>3626.3</v>
       </c>
       <c r="M43">
-        <v>1033.262509757922</v>
+        <v>1000.775520157922</v>
       </c>
       <c r="N43">
-        <v>2593.037490242078</v>
+        <v>2625.524479842078</v>
       </c>
       <c r="O43">
-        <v>881.6327466823066</v>
+        <v>892.6783231463064</v>
       </c>
       <c r="P43">
-        <v>1711.404743559772</v>
+        <v>1732.846156695771</v>
       </c>
       <c r="Q43">
-        <v>2413.804743559771</v>
+        <v>2435.246156695771</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.123156209137276</v>
+        <v>0.1231444873283115</v>
       </c>
       <c r="T43">
         <v>1.008057951925846</v>
       </c>
       <c r="U43">
-        <v>0.08269410488470122</v>
+        <v>0.08009410488470123</v>
       </c>
       <c r="V43">
         <v>0.34</v>
       </c>
       <c r="W43">
-        <v>0.0545781092239028</v>
+        <v>0.0528621092239028</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.509563122395283</v>
+        <v>3.623489910532354</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.09494665720887423</v>
+        <v>0.09421904866432371</v>
       </c>
       <c r="C44">
-        <v>19643.58150456677</v>
+        <v>20062.8799122161</v>
       </c>
       <c r="D44">
-        <v>28809.93350456677</v>
+        <v>29229.2319122161</v>
       </c>
       <c r="E44">
         <v>12178.952</v>
@@ -4901,37 +4901,37 @@
         <v>3626.3</v>
       </c>
       <c r="M44">
-        <v>1058.464034386164</v>
+        <v>1025.184679186164</v>
       </c>
       <c r="N44">
-        <v>2567.835965613836</v>
+        <v>2601.115320813836</v>
       </c>
       <c r="O44">
-        <v>873.0642283087044</v>
+        <v>884.3792090767042</v>
       </c>
       <c r="P44">
-        <v>1694.771737305132</v>
+        <v>1716.736111737132</v>
       </c>
       <c r="Q44">
-        <v>2397.171737305132</v>
+        <v>2419.136111737131</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1241790540255777</v>
+        <v>0.1241671772246285</v>
       </c>
       <c r="T44">
         <v>1.021387029639691</v>
       </c>
       <c r="U44">
-        <v>0.08269410488470122</v>
+        <v>0.08009410488470123</v>
       </c>
       <c r="V44">
         <v>0.34</v>
       </c>
       <c r="W44">
-        <v>0.0545781092239028</v>
+        <v>0.0528621092239028</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.426002095671587</v>
+        <v>3.537216341233965</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.09485412624495548</v>
+        <v>0.0941093850231435</v>
       </c>
       <c r="C45">
-        <v>19392.06200910969</v>
+        <v>19823.09214096964</v>
       </c>
       <c r="D45">
-        <v>28863.17000910969</v>
+        <v>29294.20014096964</v>
       </c>
       <c r="E45">
         <v>12483.708</v>
@@ -4983,37 +4983,37 @@
         <v>3626.3</v>
       </c>
       <c r="M45">
-        <v>1083.665559014406</v>
+        <v>1049.593838214406</v>
       </c>
       <c r="N45">
-        <v>2542.634440985594</v>
+        <v>2576.706161785594</v>
       </c>
       <c r="O45">
-        <v>864.4957099351019</v>
+        <v>876.0800950071019</v>
       </c>
       <c r="P45">
-        <v>1678.138731050492</v>
+        <v>1700.626066778492</v>
       </c>
       <c r="Q45">
-        <v>2380.538731050492</v>
+        <v>2403.026066778491</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1252377882082057</v>
+        <v>0.1252257509769567</v>
       </c>
       <c r="T45">
         <v>1.035183794290865</v>
       </c>
       <c r="U45">
-        <v>0.08269410488470122</v>
+        <v>0.08009410488470123</v>
       </c>
       <c r="V45">
         <v>0.34</v>
       </c>
       <c r="W45">
-        <v>0.0545781092239028</v>
+        <v>0.0528621092239028</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.346327628330386</v>
+        <v>3.454955496088989</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.09476159528103674</v>
+        <v>0.09399972138196329</v>
       </c>
       <c r="C46">
-        <v>19140.73962428852</v>
+        <v>19583.59382470777</v>
       </c>
       <c r="D46">
-        <v>28916.60362428851</v>
+        <v>29359.45782470777</v>
       </c>
       <c r="E46">
         <v>12788.464</v>
@@ -5065,37 +5065,37 @@
         <v>3626.3</v>
       </c>
       <c r="M46">
-        <v>1108.867083642648</v>
+        <v>1074.002997242648</v>
       </c>
       <c r="N46">
-        <v>2517.432916357352</v>
+        <v>2552.297002757352</v>
       </c>
       <c r="O46">
-        <v>855.9271915614997</v>
+        <v>867.7809809374997</v>
       </c>
       <c r="P46">
-        <v>1661.505724795852</v>
+        <v>1684.516021819852</v>
       </c>
       <c r="Q46">
-        <v>2363.905724795852</v>
+        <v>2386.916021819852</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1263343343259277</v>
+        <v>0.1263221309347251</v>
       </c>
       <c r="T46">
         <v>1.049473300536723</v>
       </c>
       <c r="U46">
-        <v>0.08269410488470122</v>
+        <v>0.08009410488470123</v>
       </c>
       <c r="V46">
         <v>0.34</v>
       </c>
       <c r="W46">
-        <v>0.0545781092239028</v>
+        <v>0.0528621092239028</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.270274727686514</v>
+        <v>3.376433780268785</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.09466906431711801</v>
+        <v>0.09389005774078309</v>
       </c>
       <c r="C47">
-        <v>18889.61544685056</v>
+        <v>19344.38690217612</v>
       </c>
       <c r="D47">
-        <v>28970.23544685055</v>
+        <v>29425.00690217613</v>
       </c>
       <c r="E47">
         <v>13093.22</v>
@@ -5147,37 +5147,37 @@
         <v>3626.3</v>
       </c>
       <c r="M47">
-        <v>1134.06860827089</v>
+        <v>1098.41215627089</v>
       </c>
       <c r="N47">
-        <v>2492.23139172911</v>
+        <v>2527.88784372911</v>
       </c>
       <c r="O47">
-        <v>847.3586731878975</v>
+        <v>859.4818668678973</v>
       </c>
       <c r="P47">
-        <v>1644.872718541212</v>
+        <v>1668.405976861212</v>
       </c>
       <c r="Q47">
-        <v>2347.272718541212</v>
+        <v>2370.805976861212</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1274707548479304</v>
+        <v>0.1274583792545942</v>
       </c>
       <c r="T47">
         <v>1.064282425191522</v>
       </c>
       <c r="U47">
-        <v>0.08269410488470122</v>
+        <v>0.08009410488470123</v>
       </c>
       <c r="V47">
         <v>0.34</v>
       </c>
       <c r="W47">
-        <v>0.0545781092239028</v>
+        <v>0.0528621092239028</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.197601955960147</v>
+        <v>3.301401918485034</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.09457653335319925</v>
+        <v>0.09378039409960287</v>
       </c>
       <c r="C48">
-        <v>18638.69058169487</v>
+        <v>19105.47332947324</v>
       </c>
       <c r="D48">
-        <v>29024.06658169487</v>
+        <v>29490.84932947324</v>
       </c>
       <c r="E48">
         <v>13397.976</v>
@@ -5229,37 +5229,37 @@
         <v>3626.3</v>
       </c>
       <c r="M48">
-        <v>1159.270132899132</v>
+        <v>1122.821315299132</v>
       </c>
       <c r="N48">
-        <v>2467.029867100868</v>
+        <v>2503.478684700868</v>
       </c>
       <c r="O48">
-        <v>838.7901548142951</v>
+        <v>851.1827527982953</v>
       </c>
       <c r="P48">
-        <v>1628.239712286573</v>
+        <v>1652.295931902573</v>
       </c>
       <c r="Q48">
-        <v>2330.639712286572</v>
+        <v>2354.695931902573</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1286492650188962</v>
+        <v>0.1286367108455696</v>
       </c>
       <c r="T48">
         <v>1.079640035944646</v>
       </c>
       <c r="U48">
-        <v>0.08269410488470122</v>
+        <v>0.08009410488470123</v>
       </c>
       <c r="V48">
         <v>0.34</v>
       </c>
       <c r="W48">
-        <v>0.0545781092239028</v>
+        <v>0.0528621092239028</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.128088869961013</v>
+        <v>3.229632311561446</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.09448400238928052</v>
+        <v>0.09367073045842268</v>
       </c>
       <c r="C49">
-        <v>18387.96614194804</v>
+        <v>18866.85508024495</v>
       </c>
       <c r="D49">
-        <v>29078.09814194804</v>
+        <v>29556.98708024495</v>
       </c>
       <c r="E49">
         <v>13702.732</v>
@@ -5311,37 +5311,37 @@
         <v>3626.3</v>
       </c>
       <c r="M49">
-        <v>1184.471657527374</v>
+        <v>1147.230474327374</v>
       </c>
       <c r="N49">
-        <v>2441.828342472626</v>
+        <v>2479.069525672626</v>
       </c>
       <c r="O49">
-        <v>830.2216364406929</v>
+        <v>842.8836387286929</v>
       </c>
       <c r="P49">
-        <v>1611.606706031933</v>
+        <v>1636.185886943933</v>
       </c>
       <c r="Q49">
-        <v>2314.006706031932</v>
+        <v>2338.585886943933</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1298722472717853</v>
+        <v>0.1298595077796007</v>
       </c>
       <c r="T49">
         <v>1.095577179179021</v>
       </c>
       <c r="U49">
-        <v>0.08269410488470122</v>
+        <v>0.08009410488470123</v>
       </c>
       <c r="V49">
         <v>0.34</v>
       </c>
       <c r="W49">
-        <v>0.0545781092239028</v>
+        <v>0.0528621092239028</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.061533787621417</v>
+        <v>3.160916730464394</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.09521515142536177</v>
+        <v>0.09356106681724247</v>
       </c>
       <c r="C50">
-        <v>17661.67654262998</v>
+        <v>18628.53414588179</v>
       </c>
       <c r="D50">
-        <v>28656.56454262998</v>
+        <v>29623.42214588179</v>
       </c>
       <c r="E50">
         <v>14007.488</v>
@@ -5393,45 +5393,45 @@
         <v>3626.3</v>
       </c>
       <c r="M50">
-        <v>1247.706730955616</v>
+        <v>1171.639633355616</v>
       </c>
       <c r="N50">
-        <v>2378.593269044384</v>
+        <v>2454.660366644384</v>
       </c>
       <c r="O50">
-        <v>808.7217114750907</v>
+        <v>834.5845246590906</v>
       </c>
       <c r="P50">
-        <v>1569.871557569294</v>
+        <v>1620.075841985293</v>
       </c>
       <c r="Q50">
-        <v>2272.271557569293</v>
+        <v>2322.475841985293</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1311422673036316</v>
+        <v>0.1311293353649406</v>
       </c>
       <c r="T50">
         <v>1.112127289460871</v>
       </c>
       <c r="U50">
-        <v>0.08529410488470121</v>
+        <v>0.08009410488470123</v>
       </c>
       <c r="V50">
         <v>0.34</v>
       </c>
       <c r="W50">
-        <v>0.05629410922390279</v>
+        <v>0.0528621092239028</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y50">
-        <v>2.906372074487908</v>
+        <v>3.095064298579719</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.09513978046144303</v>
+        <v>0.09345140317606225</v>
       </c>
       <c r="C51">
-        <v>17399.80875771105</v>
+        <v>18390.51253571874</v>
       </c>
       <c r="D51">
-        <v>28699.45275771105</v>
+        <v>29690.15653571875</v>
       </c>
       <c r="E51">
         <v>14312.244</v>
@@ -5475,45 +5475,45 @@
         <v>3626.3</v>
       </c>
       <c r="M51">
-        <v>1273.700621183858</v>
+        <v>1196.048792383858</v>
       </c>
       <c r="N51">
-        <v>2352.599378816142</v>
+        <v>2430.251207616142</v>
       </c>
       <c r="O51">
-        <v>799.8837887974884</v>
+        <v>826.2854105894884</v>
       </c>
       <c r="P51">
-        <v>1552.715590018654</v>
+        <v>1603.965797026653</v>
       </c>
       <c r="Q51">
-        <v>2255.115590018654</v>
+        <v>2306.365797026653</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1324620920426091</v>
+        <v>0.13244896011049</v>
       </c>
       <c r="T51">
         <v>1.129326423675343</v>
       </c>
       <c r="U51">
-        <v>0.08529410488470121</v>
+        <v>0.08009410488470123</v>
       </c>
       <c r="V51">
         <v>0.34</v>
       </c>
       <c r="W51">
-        <v>0.05629410922390279</v>
+        <v>0.0528621092239028</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y51">
-        <v>2.847058358682032</v>
+        <v>3.031899721057684</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.09506440949752429</v>
+        <v>0.09416673953488205</v>
       </c>
       <c r="C52">
-        <v>17138.06954061205</v>
+        <v>17655.78552092092</v>
       </c>
       <c r="D52">
-        <v>28742.46954061204</v>
+        <v>29260.18552092092</v>
       </c>
       <c r="E52">
         <v>14617</v>
@@ -5557,37 +5557,37 @@
         <v>3626.3</v>
       </c>
       <c r="M52">
-        <v>1299.6945114121</v>
+        <v>1258.5524514121</v>
       </c>
       <c r="N52">
-        <v>2326.6054885879</v>
+        <v>2367.7475485879</v>
       </c>
       <c r="O52">
-        <v>791.0458661198861</v>
+        <v>805.0341665198861</v>
       </c>
       <c r="P52">
-        <v>1535.559622468014</v>
+        <v>1562.713382068014</v>
       </c>
       <c r="Q52">
-        <v>2237.959622468014</v>
+        <v>2265.113382068013</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1338347097711458</v>
+        <v>0.1338213698458613</v>
       </c>
       <c r="T52">
         <v>1.147213523258394</v>
       </c>
       <c r="U52">
-        <v>0.08529410488470121</v>
+        <v>0.08259410488470123</v>
       </c>
       <c r="V52">
         <v>0.34</v>
       </c>
       <c r="W52">
-        <v>0.05629410922390279</v>
+        <v>0.0545121092239028</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.790117191508392</v>
+        <v>2.881326078965782</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.09498903853360555</v>
+        <v>0.09407357589370184</v>
       </c>
       <c r="C53">
-        <v>16876.45947032061</v>
+        <v>17406.32120462709</v>
       </c>
       <c r="D53">
-        <v>28785.6154703206</v>
+        <v>29315.47720462708</v>
       </c>
       <c r="E53">
         <v>14921.756</v>
@@ -5639,37 +5639,37 @@
         <v>3626.3</v>
       </c>
       <c r="M53">
-        <v>1325.688401640342</v>
+        <v>1283.723500440342</v>
       </c>
       <c r="N53">
-        <v>2300.611598359658</v>
+        <v>2342.576499559658</v>
       </c>
       <c r="O53">
-        <v>782.2079434422839</v>
+        <v>796.4760098502837</v>
       </c>
       <c r="P53">
-        <v>1518.403654917374</v>
+        <v>1546.100489709374</v>
       </c>
       <c r="Q53">
-        <v>2220.803654917374</v>
+        <v>2248.500489709374</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1352633527130921</v>
+        <v>0.1352497963051253</v>
       </c>
       <c r="T53">
         <v>1.165830708538712</v>
       </c>
       <c r="U53">
-        <v>0.08529410488470121</v>
+        <v>0.08259410488470123</v>
       </c>
       <c r="V53">
         <v>0.34</v>
       </c>
       <c r="W53">
-        <v>0.05629410922390279</v>
+        <v>0.0545121092239028</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.735409011282737</v>
+        <v>2.824829489182139</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.0949136675696868</v>
+        <v>0.09398041225252164</v>
       </c>
       <c r="C54">
-        <v>16614.97912930611</v>
+        <v>17157.06624847022</v>
       </c>
       <c r="D54">
-        <v>28828.89112930611</v>
+        <v>29370.97824847022</v>
       </c>
       <c r="E54">
         <v>15226.512</v>
@@ -5721,37 +5721,37 @@
         <v>3626.3</v>
       </c>
       <c r="M54">
-        <v>1351.682291868584</v>
+        <v>1308.894549468585</v>
       </c>
       <c r="N54">
-        <v>2274.617708131416</v>
+        <v>2317.405450531416</v>
       </c>
       <c r="O54">
-        <v>773.3700207646816</v>
+        <v>787.9178531806814</v>
       </c>
       <c r="P54">
-        <v>1501.247687366735</v>
+        <v>1529.487597350734</v>
       </c>
       <c r="Q54">
-        <v>2203.647687366734</v>
+        <v>2231.887597350734</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1367515224442861</v>
+        <v>0.1367377405335254</v>
       </c>
       <c r="T54">
         <v>1.185223609872376</v>
       </c>
       <c r="U54">
-        <v>0.08529410488470121</v>
+        <v>0.08259410488470123</v>
       </c>
       <c r="V54">
         <v>0.34</v>
       </c>
       <c r="W54">
-        <v>0.05629410922390279</v>
+        <v>0.0545121092239028</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.682804991834992</v>
+        <v>2.770505845159406</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.09483829660576806</v>
+        <v>0.09388724861134143</v>
       </c>
       <c r="C55">
-        <v>16353.62910354591</v>
+        <v>16908.02184380874</v>
       </c>
       <c r="D55">
-        <v>28872.2971035459</v>
+        <v>29426.68984380874</v>
       </c>
       <c r="E55">
         <v>15531.268</v>
@@ -5803,37 +5803,37 @@
         <v>3626.3</v>
       </c>
       <c r="M55">
-        <v>1377.676182096826</v>
+        <v>1334.065598496826</v>
       </c>
       <c r="N55">
-        <v>2248.623817903174</v>
+        <v>2292.234401503174</v>
       </c>
       <c r="O55">
-        <v>764.5320980870794</v>
+        <v>779.3596965110792</v>
       </c>
       <c r="P55">
-        <v>1484.091719816095</v>
+        <v>1512.874704992095</v>
       </c>
       <c r="Q55">
-        <v>2186.491719816095</v>
+        <v>2215.274704992094</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1383030185470204</v>
+        <v>0.138289001537602</v>
       </c>
       <c r="T55">
         <v>1.205441741050027</v>
       </c>
       <c r="U55">
-        <v>0.08529410488470121</v>
+        <v>0.08259410488470123</v>
       </c>
       <c r="V55">
         <v>0.34</v>
       </c>
       <c r="W55">
-        <v>0.05629410922390279</v>
+        <v>0.0545121092239028</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.632186029724898</v>
+        <v>2.718232149967719</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.09476292564184932</v>
+        <v>0.09379408497016123</v>
       </c>
       <c r="C56">
-        <v>16092.40998255173</v>
+        <v>16659.1891910574</v>
       </c>
       <c r="D56">
-        <v>28915.83398255173</v>
+        <v>29482.6131910574</v>
       </c>
       <c r="E56">
         <v>15836.024</v>
@@ -5885,37 +5885,37 @@
         <v>3626.3</v>
       </c>
       <c r="M56">
-        <v>1403.670072325068</v>
+        <v>1359.236647525069</v>
       </c>
       <c r="N56">
-        <v>2222.629927674932</v>
+        <v>2267.063352474932</v>
       </c>
       <c r="O56">
-        <v>755.694175409477</v>
+        <v>770.8015398414769</v>
       </c>
       <c r="P56">
-        <v>1466.935752265455</v>
+        <v>1496.261812633455</v>
       </c>
       <c r="Q56">
-        <v>2169.335752265455</v>
+        <v>2198.661812633455</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1399219710020475</v>
+        <v>0.1399077086722907</v>
       </c>
       <c r="T56">
         <v>1.226538921409315</v>
       </c>
       <c r="U56">
-        <v>0.08529410488470121</v>
+        <v>0.08259410488470123</v>
       </c>
       <c r="V56">
         <v>0.34</v>
       </c>
       <c r="W56">
-        <v>0.05629410922390279</v>
+        <v>0.0545121092239028</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.583441843989252</v>
+        <v>2.667894517560909</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.09468755467793058</v>
+        <v>0.09370092132898103</v>
       </c>
       <c r="C57">
-        <v>15831.32235939644</v>
+        <v>16410.56949977357</v>
       </c>
       <c r="D57">
-        <v>28959.50235939644</v>
+        <v>29538.74949977357</v>
       </c>
       <c r="E57">
         <v>16140.78</v>
@@ -5967,37 +5967,37 @@
         <v>3626.3</v>
       </c>
       <c r="M57">
-        <v>1429.66396255331</v>
+        <v>1384.407696553311</v>
       </c>
       <c r="N57">
-        <v>2196.63603744669</v>
+        <v>2241.89230344669</v>
       </c>
       <c r="O57">
-        <v>746.8562527318746</v>
+        <v>762.2433831718746</v>
       </c>
       <c r="P57">
-        <v>1449.779784714815</v>
+        <v>1479.648920274815</v>
       </c>
       <c r="Q57">
-        <v>2152.179784714815</v>
+        <v>2182.048920274815</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1416128768995201</v>
+        <v>0.1415983583462989</v>
       </c>
       <c r="T57">
         <v>1.248573754229015</v>
       </c>
       <c r="U57">
-        <v>0.08529410488470121</v>
+        <v>0.08259410488470123</v>
       </c>
       <c r="V57">
         <v>0.34</v>
       </c>
       <c r="W57">
-        <v>0.05629410922390279</v>
+        <v>0.0545121092239028</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.536470174098538</v>
+        <v>2.619387344514347</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09561010371401184</v>
+        <v>0.0936077576878008</v>
       </c>
       <c r="C58">
-        <v>15000.96894035854</v>
+        <v>16162.16398874443</v>
       </c>
       <c r="D58">
-        <v>28433.90494035854</v>
+        <v>29595.09998874443</v>
       </c>
       <c r="E58">
         <v>16445.536</v>
@@ -6049,45 +6049,45 @@
         <v>3626.3</v>
       </c>
       <c r="M58">
-        <v>1501.736959981552</v>
+        <v>1409.578745581552</v>
       </c>
       <c r="N58">
-        <v>2124.563040018448</v>
+        <v>2216.721254418448</v>
       </c>
       <c r="O58">
-        <v>722.3514336062724</v>
+        <v>753.6852265022723</v>
       </c>
       <c r="P58">
-        <v>1402.211606412176</v>
+        <v>1463.036027916175</v>
       </c>
       <c r="Q58">
-        <v>2104.611606412175</v>
+        <v>2165.436027916175</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1433806421559688</v>
+        <v>0.1433658557327619</v>
       </c>
       <c r="T58">
         <v>1.271610170358701</v>
       </c>
       <c r="U58">
-        <v>0.08799410488470122</v>
+        <v>0.08259410488470123</v>
       </c>
       <c r="V58">
         <v>0.34</v>
       </c>
       <c r="W58">
-        <v>0.0580761092239028</v>
+        <v>0.0545121092239028</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y58">
-        <v>2.414737132156984</v>
+        <v>2.572612570505163</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09555255275009311</v>
+        <v>0.0935145940466206</v>
       </c>
       <c r="C59">
-        <v>14728.4424552136</v>
+        <v>15913.97388607508</v>
       </c>
       <c r="D59">
-        <v>28466.1344552136</v>
+        <v>29651.66588607509</v>
       </c>
       <c r="E59">
         <v>16750.292</v>
@@ -6131,45 +6131,45 @@
         <v>3626.3</v>
       </c>
       <c r="M59">
-        <v>1528.553691409794</v>
+        <v>1434.749794609794</v>
       </c>
       <c r="N59">
-        <v>2097.746308590206</v>
+        <v>2191.550205390206</v>
       </c>
       <c r="O59">
-        <v>713.23374492067</v>
+        <v>745.1270698326699</v>
       </c>
       <c r="P59">
-        <v>1384.512563669536</v>
+        <v>1446.423135557536</v>
       </c>
       <c r="Q59">
-        <v>2086.912563669535</v>
+        <v>2148.823135557535</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1452306290522524</v>
+        <v>0.1452155622999907</v>
       </c>
       <c r="T59">
         <v>1.295718047703722</v>
       </c>
       <c r="U59">
-        <v>0.08799410488470122</v>
+        <v>0.08259410488470123</v>
       </c>
       <c r="V59">
         <v>0.34</v>
       </c>
       <c r="W59">
-        <v>0.0580761092239028</v>
+        <v>0.0545121092239028</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y59">
-        <v>2.372373322820896</v>
+        <v>2.527479016636651</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.09549500178617437</v>
+        <v>0.09476123040544039</v>
       </c>
       <c r="C60">
-        <v>14455.98911657233</v>
+        <v>14869.76660893239</v>
       </c>
       <c r="D60">
-        <v>28498.43711657232</v>
+        <v>28912.21460893239</v>
       </c>
       <c r="E60">
         <v>17055.048</v>
@@ -6213,37 +6213,37 @@
         <v>3626.3</v>
       </c>
       <c r="M60">
-        <v>1555.370422838036</v>
+        <v>1521.786311638036</v>
       </c>
       <c r="N60">
-        <v>2070.929577161964</v>
+        <v>2104.513688361964</v>
       </c>
       <c r="O60">
-        <v>704.1160562350678</v>
+        <v>715.5346540430679</v>
       </c>
       <c r="P60">
-        <v>1366.813520926896</v>
+        <v>1388.979034318897</v>
       </c>
       <c r="Q60">
-        <v>2069.213520926896</v>
+        <v>2091.379034318896</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1471687105626446</v>
+        <v>0.1471533501323256</v>
       </c>
       <c r="T60">
         <v>1.320973919208029</v>
       </c>
       <c r="U60">
-        <v>0.08799410488470122</v>
+        <v>0.08609410488470122</v>
       </c>
       <c r="V60">
         <v>0.34</v>
       </c>
       <c r="W60">
-        <v>0.0580761092239028</v>
+        <v>0.05682210922390279</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.331470334496398</v>
+        <v>2.382923260820164</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.09543745082225563</v>
+        <v>0.0946911667642602</v>
       </c>
       <c r="C61">
-        <v>14183.60917373211</v>
+        <v>14605.58984417184</v>
       </c>
       <c r="D61">
-        <v>28530.81317373211</v>
+        <v>28952.79384417184</v>
       </c>
       <c r="E61">
         <v>17359.804</v>
@@ -6295,37 +6295,37 @@
         <v>3626.3</v>
       </c>
       <c r="M61">
-        <v>1582.187154266278</v>
+        <v>1548.024006666278</v>
       </c>
       <c r="N61">
-        <v>2044.112845733722</v>
+        <v>2078.275993333722</v>
       </c>
       <c r="O61">
-        <v>694.9983675494656</v>
+        <v>706.6138377334655</v>
       </c>
       <c r="P61">
-        <v>1349.114478184256</v>
+        <v>1371.662155600256</v>
       </c>
       <c r="Q61">
-        <v>2051.514478184256</v>
+        <v>2074.062155600256</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1492013326345195</v>
+        <v>0.1491856642003843</v>
       </c>
       <c r="T61">
         <v>1.347461784444255</v>
       </c>
       <c r="U61">
-        <v>0.08799410488470122</v>
+        <v>0.08609410488470122</v>
       </c>
       <c r="V61">
         <v>0.34</v>
       </c>
       <c r="W61">
-        <v>0.0580761092239028</v>
+        <v>0.05682210922390279</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.291953888149001</v>
+        <v>2.342534730975755</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.09537989985833689</v>
+        <v>0.09462110312307997</v>
       </c>
       <c r="C62">
-        <v>13911.30287712452</v>
+        <v>14341.52714806805</v>
       </c>
       <c r="D62">
-        <v>28563.26287712451</v>
+        <v>28993.48714806805</v>
       </c>
       <c r="E62">
         <v>17664.56</v>
@@ -6377,37 +6377,37 @@
         <v>3626.3</v>
       </c>
       <c r="M62">
-        <v>1609.00388569452</v>
+        <v>1574.26170169452</v>
       </c>
       <c r="N62">
-        <v>2017.29611430548</v>
+        <v>2052.03829830548</v>
       </c>
       <c r="O62">
-        <v>685.8806788638633</v>
+        <v>697.6930214238633</v>
       </c>
       <c r="P62">
-        <v>1331.415435441617</v>
+        <v>1354.345276881617</v>
       </c>
       <c r="Q62">
-        <v>2033.815435441617</v>
+        <v>2056.745276881617</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.151335585809988</v>
+        <v>0.1513195939718458</v>
       </c>
       <c r="T62">
         <v>1.375274042942291</v>
       </c>
       <c r="U62">
-        <v>0.08799410488470122</v>
+        <v>0.08609410488470122</v>
       </c>
       <c r="V62">
         <v>0.34</v>
       </c>
       <c r="W62">
-        <v>0.0580761092239028</v>
+        <v>0.05682210922390279</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.253754656679852</v>
+        <v>2.303492485459492</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.09721456889441815</v>
+        <v>0.09455103948189977</v>
       </c>
       <c r="C63">
-        <v>12607.14144404102</v>
+        <v>14077.57900227026</v>
       </c>
       <c r="D63">
-        <v>27563.85744404102</v>
+        <v>29034.29500227025</v>
       </c>
       <c r="E63">
         <v>17969.316</v>
@@ -6459,45 +6459,45 @@
         <v>3626.3</v>
       </c>
       <c r="M63">
-        <v>1723.194162322762</v>
+        <v>1600.499396722762</v>
       </c>
       <c r="N63">
-        <v>1903.105837677238</v>
+        <v>2025.800603277238</v>
       </c>
       <c r="O63">
-        <v>647.0559848102608</v>
+        <v>688.7722051142609</v>
       </c>
       <c r="P63">
-        <v>1256.049852866977</v>
+        <v>1337.028398162977</v>
       </c>
       <c r="Q63">
-        <v>1958.449852866976</v>
+        <v>2039.428398162977</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1535792878662499</v>
+        <v>0.1535629560392797</v>
       </c>
       <c r="T63">
         <v>1.404512571106893</v>
       </c>
       <c r="U63">
-        <v>0.09269410488470123</v>
+        <v>0.08609410488470122</v>
       </c>
       <c r="V63">
         <v>0.34</v>
       </c>
       <c r="W63">
-        <v>0.0611781092239028</v>
+        <v>0.05682210922390279</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y63">
-        <v>2.104405922030264</v>
+        <v>2.265730313566714</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.09718803793049942</v>
+        <v>0.0956267358407196</v>
       </c>
       <c r="C64">
-        <v>12316.33913113276</v>
+        <v>13158.6838899324</v>
       </c>
       <c r="D64">
-        <v>27577.81113113276</v>
+        <v>28420.1558899324</v>
       </c>
       <c r="E64">
         <v>18274.072</v>
@@ -6541,37 +6541,37 @@
         <v>3626.3</v>
       </c>
       <c r="M64">
-        <v>1751.443246951004</v>
+        <v>1679.642733351004</v>
       </c>
       <c r="N64">
-        <v>1874.856753048996</v>
+        <v>1946.657266648996</v>
       </c>
       <c r="O64">
-        <v>637.4512960366586</v>
+        <v>661.8634706606587</v>
       </c>
       <c r="P64">
-        <v>1237.405457012337</v>
+        <v>1284.793795988337</v>
       </c>
       <c r="Q64">
-        <v>1939.805457012337</v>
+        <v>1987.193795988337</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1559410795044202</v>
+        <v>0.1559243897944733</v>
       </c>
       <c r="T64">
         <v>1.435289969174896</v>
       </c>
       <c r="U64">
-        <v>0.09269410488470123</v>
+        <v>0.08889410488470123</v>
       </c>
       <c r="V64">
         <v>0.34</v>
       </c>
       <c r="W64">
-        <v>0.0611781092239028</v>
+        <v>0.0586701092239028</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.070463891029775</v>
+        <v>2.158971028776625</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.09716150696658066</v>
+        <v>0.09557515219953937</v>
       </c>
       <c r="C65">
-        <v>12025.55095296597</v>
+        <v>12882.78447693065</v>
       </c>
       <c r="D65">
-        <v>27591.77895296597</v>
+        <v>28449.01247693065</v>
       </c>
       <c r="E65">
         <v>18578.828</v>
@@ -6623,37 +6623,37 @@
         <v>3626.3</v>
       </c>
       <c r="M65">
-        <v>1779.692331579246</v>
+        <v>1706.733745179247</v>
       </c>
       <c r="N65">
-        <v>1846.607668420754</v>
+        <v>1919.566254820754</v>
       </c>
       <c r="O65">
-        <v>627.8466072630563</v>
+        <v>652.6525266390563</v>
       </c>
       <c r="P65">
-        <v>1218.761061157697</v>
+        <v>1266.913728181697</v>
       </c>
       <c r="Q65">
-        <v>1921.161061157697</v>
+        <v>1969.313728181697</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1584305355554646</v>
+        <v>0.1584134686175152</v>
       </c>
       <c r="T65">
         <v>1.467731010381709</v>
       </c>
       <c r="U65">
-        <v>0.09269410488470123</v>
+        <v>0.08889410488470123</v>
       </c>
       <c r="V65">
         <v>0.34</v>
       </c>
       <c r="W65">
-        <v>0.0611781092239028</v>
+        <v>0.0586701092239028</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.037599384822953</v>
+        <v>2.124701647367472</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.09713497600266192</v>
+        <v>0.09552356855835917</v>
       </c>
       <c r="C66">
-        <v>11734.77693102873</v>
+        <v>12606.94372292892</v>
       </c>
       <c r="D66">
-        <v>27605.76093102873</v>
+        <v>28477.92772292891</v>
       </c>
       <c r="E66">
         <v>18883.584</v>
@@ -6705,37 +6705,37 @@
         <v>3626.3</v>
       </c>
       <c r="M66">
-        <v>1807.941416207488</v>
+        <v>1733.824757007488</v>
       </c>
       <c r="N66">
-        <v>1818.358583792512</v>
+        <v>1892.475242992512</v>
       </c>
       <c r="O66">
-        <v>618.2419184894541</v>
+        <v>643.4415826174541</v>
       </c>
       <c r="P66">
-        <v>1200.116665303058</v>
+        <v>1249.033660375058</v>
       </c>
       <c r="Q66">
-        <v>1902.516665303057</v>
+        <v>1951.433660375057</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1610582947204559</v>
+        <v>0.1610408295973927</v>
       </c>
       <c r="T66">
         <v>1.501974331655567</v>
       </c>
       <c r="U66">
-        <v>0.09269410488470123</v>
+        <v>0.08889410488470123</v>
       </c>
       <c r="V66">
         <v>0.34</v>
       </c>
       <c r="W66">
-        <v>0.0611781092239028</v>
+        <v>0.0586701092239028</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.005761894435095</v>
+        <v>2.091503184127355</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1010981450387432</v>
+        <v>0.09547198491717898</v>
       </c>
       <c r="C67">
-        <v>9487.399123261075</v>
+        <v>12331.16180697015</v>
       </c>
       <c r="D67">
-        <v>25663.13912326107</v>
+        <v>28506.90180697015</v>
       </c>
       <c r="E67">
         <v>19188.34</v>
@@ -6787,45 +6787,45 @@
         <v>3626.3</v>
       </c>
       <c r="M67">
-        <v>2020.41550283573</v>
+        <v>1760.91576883573</v>
       </c>
       <c r="N67">
-        <v>1605.88449716427</v>
+        <v>1865.38423116427</v>
       </c>
       <c r="O67">
-        <v>546.0007290358518</v>
+        <v>634.2306385958518</v>
       </c>
       <c r="P67">
-        <v>1059.883768128418</v>
+        <v>1231.153592568418</v>
       </c>
       <c r="Q67">
-        <v>1762.283768128418</v>
+        <v>1933.553592568418</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1638362115520182</v>
+        <v>0.1638183254904061</v>
       </c>
       <c r="T67">
         <v>1.538174414145075</v>
       </c>
       <c r="U67">
-        <v>0.1019941048847012</v>
+        <v>0.08889410488470123</v>
       </c>
       <c r="V67">
         <v>0.34</v>
       </c>
       <c r="W67">
-        <v>0.0673161092239028</v>
+        <v>0.0586701092239028</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y67">
-        <v>1.794828833430723</v>
+        <v>2.059326212063858</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1011329940748245</v>
+        <v>0.09542040127599877</v>
       </c>
       <c r="C68">
-        <v>9166.773089906525</v>
+        <v>12055.43890882673</v>
       </c>
       <c r="D68">
-        <v>25647.26908990652</v>
+        <v>28535.93490882673</v>
       </c>
       <c r="E68">
         <v>19493.096</v>
@@ -6869,45 +6869,45 @@
         <v>3626.3</v>
       </c>
       <c r="M68">
-        <v>2051.498818263972</v>
+        <v>1788.006780663973</v>
       </c>
       <c r="N68">
-        <v>1574.801181736028</v>
+        <v>1838.293219336028</v>
       </c>
       <c r="O68">
-        <v>535.4324017902495</v>
+        <v>625.0196945742493</v>
       </c>
       <c r="P68">
-        <v>1039.368779945778</v>
+        <v>1213.273524761778</v>
       </c>
       <c r="Q68">
-        <v>1741.768779945778</v>
+        <v>1915.673524761778</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1667775352560253</v>
+        <v>0.1667592034947733</v>
       </c>
       <c r="T68">
         <v>1.576503913251613</v>
       </c>
       <c r="U68">
-        <v>0.1019941048847012</v>
+        <v>0.08889410488470123</v>
       </c>
       <c r="V68">
         <v>0.34</v>
       </c>
       <c r="W68">
-        <v>0.0673161092239028</v>
+        <v>0.0586701092239028</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y68">
-        <v>1.767634457166621</v>
+        <v>2.02812429975986</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1032461831109057</v>
+        <v>0.09881797763481856</v>
       </c>
       <c r="C69">
-        <v>7935.039515466968</v>
+        <v>9956.79502203831</v>
       </c>
       <c r="D69">
-        <v>24720.29151546697</v>
+        <v>26742.04702203831</v>
       </c>
       <c r="E69">
         <v>19797.852</v>
@@ -6951,45 +6951,45 @@
         <v>3626.3</v>
       </c>
       <c r="M69">
-        <v>2178.549798092215</v>
+        <v>1974.363278092215</v>
       </c>
       <c r="N69">
-        <v>1447.750201907786</v>
+        <v>1651.936721907785</v>
       </c>
       <c r="O69">
-        <v>492.2350686486471</v>
+        <v>561.6584854486471</v>
       </c>
       <c r="P69">
-        <v>955.5151332591385</v>
+        <v>1090.278236459138</v>
       </c>
       <c r="Q69">
-        <v>1657.915133259138</v>
+        <v>1792.678236459138</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1698971210026995</v>
+        <v>0.1698783165297081</v>
       </c>
       <c r="T69">
         <v>1.617156412304001</v>
       </c>
       <c r="U69">
-        <v>0.1066941048847012</v>
+        <v>0.09669410488470123</v>
       </c>
       <c r="V69">
         <v>0.34</v>
       </c>
       <c r="W69">
-        <v>0.07041810922390279</v>
+        <v>0.06381810922390281</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y69">
-        <v>1.664547674409646</v>
+        <v>1.836693398949365</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.103312052146987</v>
+        <v>0.09881787399363834</v>
       </c>
       <c r="C70">
-        <v>7602.464891482789</v>
+        <v>9652.09030366542</v>
       </c>
       <c r="D70">
-        <v>24692.47289148279</v>
+        <v>26742.09830366542</v>
       </c>
       <c r="E70">
         <v>20102.608</v>
@@ -7033,45 +7033,45 @@
         <v>3626.3</v>
       </c>
       <c r="M70">
-        <v>2211.065466720456</v>
+        <v>2003.831386720457</v>
       </c>
       <c r="N70">
-        <v>1415.234533279544</v>
+        <v>1622.468613279544</v>
       </c>
       <c r="O70">
-        <v>481.179741315045</v>
+        <v>551.6393285150449</v>
       </c>
       <c r="P70">
-        <v>934.0547919644989</v>
+        <v>1070.829284764499</v>
       </c>
       <c r="Q70">
-        <v>1636.454791964499</v>
+        <v>1773.229284764499</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1732116808585408</v>
+        <v>0.1731923741293264</v>
       </c>
       <c r="T70">
         <v>1.660349692547163</v>
       </c>
       <c r="U70">
-        <v>0.1066941048847012</v>
+        <v>0.09669410488470123</v>
       </c>
       <c r="V70">
         <v>0.34</v>
       </c>
       <c r="W70">
-        <v>0.07041810922390279</v>
+        <v>0.06381810922390281</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y70">
-        <v>1.640069032138916</v>
+        <v>1.809683201905992</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1033779211830682</v>
+        <v>0.09881777035245815</v>
       </c>
       <c r="C71">
-        <v>7269.952807695503</v>
+        <v>9347.385585489188</v>
       </c>
       <c r="D71">
-        <v>24664.7168076955</v>
+        <v>26742.14958548919</v>
       </c>
       <c r="E71">
         <v>20407.364</v>
@@ -7115,45 +7115,45 @@
         <v>3626.3</v>
       </c>
       <c r="M71">
-        <v>2243.581135348698</v>
+        <v>2033.299495348699</v>
       </c>
       <c r="N71">
-        <v>1382.718864651302</v>
+        <v>1593.000504651302</v>
       </c>
       <c r="O71">
-        <v>470.1244139814427</v>
+        <v>541.6201715814426</v>
       </c>
       <c r="P71">
-        <v>912.5944506698592</v>
+        <v>1051.380333069859</v>
       </c>
       <c r="Q71">
-        <v>1614.994450669859</v>
+        <v>1753.780333069858</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1767400832857268</v>
+        <v>0.176720241896662</v>
       </c>
       <c r="T71">
         <v>1.70632963603182</v>
       </c>
       <c r="U71">
-        <v>0.1066941048847012</v>
+        <v>0.09669410488470123</v>
       </c>
       <c r="V71">
         <v>0.34</v>
       </c>
       <c r="W71">
-        <v>0.07041810922390279</v>
+        <v>0.06381810922390281</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y71">
-        <v>1.616299915731106</v>
+        <v>1.783455909124746</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1034437902191495</v>
+        <v>0.09881766671127792</v>
       </c>
       <c r="C72">
-        <v>6937.503053443106</v>
+        <v>9042.680867509654</v>
       </c>
       <c r="D72">
-        <v>24637.02305344311</v>
+        <v>26742.20086750965</v>
       </c>
       <c r="E72">
         <v>20712.12</v>
@@ -7197,45 +7197,45 @@
         <v>3626.3</v>
       </c>
       <c r="M72">
-        <v>2276.09680397694</v>
+        <v>2062.767603976941</v>
       </c>
       <c r="N72">
-        <v>1350.20319602306</v>
+        <v>1563.532396023059</v>
       </c>
       <c r="O72">
-        <v>459.0690866478403</v>
+        <v>531.6010146478402</v>
       </c>
       <c r="P72">
-        <v>891.1341093752194</v>
+        <v>1031.931381375219</v>
       </c>
       <c r="Q72">
-        <v>1593.534109375219</v>
+        <v>1734.331381375219</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1805037125413917</v>
+        <v>0.1804833008484866</v>
       </c>
       <c r="T72">
         <v>1.75537490908212</v>
       </c>
       <c r="U72">
-        <v>0.1066941048847012</v>
+        <v>0.09669410488470123</v>
       </c>
       <c r="V72">
         <v>0.34</v>
       </c>
       <c r="W72">
-        <v>0.07041810922390279</v>
+        <v>0.06381810922390281</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y72">
-        <v>1.593209916934947</v>
+        <v>1.757977967565821</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1035096592552307</v>
+        <v>0.1006451030700977</v>
       </c>
       <c r="C73">
-        <v>6605.115419008671</v>
+        <v>7863.275380364546</v>
       </c>
       <c r="D73">
-        <v>24609.39141900867</v>
+        <v>25867.55138036454</v>
       </c>
       <c r="E73">
         <v>21016.876</v>
@@ -7279,37 +7279,37 @@
         <v>3626.3</v>
       </c>
       <c r="M73">
-        <v>2308.612472605182</v>
+        <v>2176.622649005182</v>
       </c>
       <c r="N73">
-        <v>1317.687527394818</v>
+        <v>1449.677350994818</v>
       </c>
       <c r="O73">
-        <v>448.0137593142382</v>
+        <v>492.8902993382382</v>
       </c>
       <c r="P73">
-        <v>869.6737680805799</v>
+        <v>956.7870516565798</v>
       </c>
       <c r="Q73">
-        <v>1572.07376808058</v>
+        <v>1659.18705165658</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1845269024353784</v>
+        <v>0.1845058811073336</v>
       </c>
       <c r="T73">
         <v>1.807802614756579</v>
       </c>
       <c r="U73">
-        <v>0.1066941048847012</v>
+        <v>0.1005941048847012</v>
       </c>
       <c r="V73">
         <v>0.34</v>
       </c>
       <c r="W73">
-        <v>0.07041810922390279</v>
+        <v>0.06639210922390279</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.570770340640089</v>
+        <v>1.666021439985194</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.103575528291312</v>
+        <v>0.1006707394289175</v>
       </c>
       <c r="C74">
-        <v>6272.789695615051</v>
+        <v>7546.656037600376</v>
       </c>
       <c r="D74">
-        <v>24581.82169561505</v>
+        <v>25855.68803760037</v>
       </c>
       <c r="E74">
         <v>21321.632</v>
@@ -7361,37 +7361,37 @@
         <v>3626.3</v>
       </c>
       <c r="M74">
-        <v>2341.128141233424</v>
+        <v>2207.279306033424</v>
       </c>
       <c r="N74">
-        <v>1285.171858766576</v>
+        <v>1419.020693966576</v>
       </c>
       <c r="O74">
-        <v>436.958431980636</v>
+        <v>482.467035948636</v>
       </c>
       <c r="P74">
-        <v>848.2134267859403</v>
+        <v>936.5536580179403</v>
       </c>
       <c r="Q74">
-        <v>1550.61342678594</v>
+        <v>1638.95365801794</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1888374630360785</v>
+        <v>0.1888157885275268</v>
       </c>
       <c r="T74">
         <v>1.863975156550643</v>
       </c>
       <c r="U74">
-        <v>0.1066941048847012</v>
+        <v>0.1005941048847012</v>
       </c>
       <c r="V74">
         <v>0.34</v>
       </c>
       <c r="W74">
-        <v>0.07041810922390279</v>
+        <v>0.06639210922390279</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.548954085908977</v>
+        <v>1.642882253318733</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1036413973273933</v>
+        <v>0.1006963757877373</v>
       </c>
       <c r="C75">
-        <v>5940.525675419609</v>
+        <v>7230.047571349682</v>
       </c>
       <c r="D75">
-        <v>24554.31367541961</v>
+        <v>25843.83557134968</v>
       </c>
       <c r="E75">
         <v>21626.388</v>
@@ -7443,37 +7443,37 @@
         <v>3626.3</v>
       </c>
       <c r="M75">
-        <v>2373.643809861666</v>
+        <v>2237.935963061666</v>
       </c>
       <c r="N75">
-        <v>1252.656190138334</v>
+        <v>1388.364036938334</v>
       </c>
       <c r="O75">
-        <v>425.9031046470337</v>
+        <v>472.0437725590335</v>
       </c>
       <c r="P75">
-        <v>826.7530854913007</v>
+        <v>916.3202643793003</v>
       </c>
       <c r="Q75">
-        <v>1529.1530854913</v>
+        <v>1618.7202643793</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1934673244220156</v>
+        <v>0.1934449483492158</v>
       </c>
       <c r="T75">
         <v>1.924308627366488</v>
       </c>
       <c r="U75">
-        <v>0.1066941048847012</v>
+        <v>0.1005941048847012</v>
       </c>
       <c r="V75">
         <v>0.34</v>
       </c>
       <c r="W75">
-        <v>0.07041810922390279</v>
+        <v>0.06639210922390279</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.527735536786936</v>
+        <v>1.620377016971901</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1037072663634745</v>
+        <v>0.1007220121465571</v>
       </c>
       <c r="C76">
-        <v>5608.323151509019</v>
+        <v>6913.449966661661</v>
       </c>
       <c r="D76">
-        <v>24526.86715150902</v>
+        <v>25831.99396666166</v>
       </c>
       <c r="E76">
         <v>21931.144</v>
@@ -7525,37 +7525,37 @@
         <v>3626.3</v>
       </c>
       <c r="M76">
-        <v>2406.159478489908</v>
+        <v>2268.592620089908</v>
       </c>
       <c r="N76">
-        <v>1220.140521510092</v>
+        <v>1357.707379910092</v>
       </c>
       <c r="O76">
-        <v>414.8477773134314</v>
+        <v>461.6205091694312</v>
       </c>
       <c r="P76">
-        <v>805.2927441966608</v>
+        <v>896.0868707406605</v>
       </c>
       <c r="Q76">
-        <v>1507.69274419666</v>
+        <v>1598.48687074066</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1984533289914863</v>
+        <v>0.1984301973879578</v>
       </c>
       <c r="T76">
         <v>1.989283134398938</v>
       </c>
       <c r="U76">
-        <v>0.1066941048847012</v>
+        <v>0.1005941048847012</v>
       </c>
       <c r="V76">
         <v>0.34</v>
       </c>
       <c r="W76">
-        <v>0.07041810922390279</v>
+        <v>0.06639210922390279</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.507090461965491</v>
+        <v>1.598480030256064</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1118416353995558</v>
+        <v>0.1007476485053769</v>
       </c>
       <c r="C77">
-        <v>2328.566886073444</v>
+        <v>6596.863208612904</v>
       </c>
       <c r="D77">
-        <v>21551.86688607344</v>
+        <v>25820.1632086129</v>
       </c>
       <c r="E77">
         <v>22235.9</v>
@@ -7607,45 +7607,45 @@
         <v>3626.3</v>
       </c>
       <c r="M77">
-        <v>2811.23935711815</v>
+        <v>2299.24927711815</v>
       </c>
       <c r="N77">
-        <v>815.0606428818501</v>
+        <v>1327.05072288185</v>
       </c>
       <c r="O77">
-        <v>277.1206185798291</v>
+        <v>451.1972457798291</v>
       </c>
       <c r="P77">
-        <v>537.940024302021</v>
+        <v>875.8534771020211</v>
       </c>
       <c r="Q77">
-        <v>1240.340024302021</v>
+        <v>1578.253477102021</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.2038382139265147</v>
+        <v>0.2038142663497992</v>
       </c>
       <c r="T77">
         <v>2.059455601993983</v>
       </c>
       <c r="U77">
-        <v>0.1229941048847012</v>
+        <v>0.1005941048847012</v>
       </c>
       <c r="V77">
         <v>0.34</v>
       </c>
       <c r="W77">
-        <v>0.0811761092239028</v>
+        <v>0.06639210922390279</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y77">
-        <v>1.289929294287265</v>
+        <v>1.577166963185983</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.112015084435637</v>
+        <v>0.1007732848641967</v>
       </c>
       <c r="C78">
-        <v>1968.213286252336</v>
+        <v>6280.287282307323</v>
       </c>
       <c r="D78">
-        <v>21496.26928625233</v>
+        <v>25808.34328230732</v>
       </c>
       <c r="E78">
         <v>22540.656</v>
@@ -7689,45 +7689,45 @@
         <v>3626.3</v>
       </c>
       <c r="M78">
-        <v>2848.722548546392</v>
+        <v>2329.905934146392</v>
       </c>
       <c r="N78">
-        <v>777.5774514536079</v>
+        <v>1296.394065853608</v>
       </c>
       <c r="O78">
-        <v>264.3763334942267</v>
+        <v>440.7739823902268</v>
       </c>
       <c r="P78">
-        <v>513.2011179593812</v>
+        <v>855.6200834633812</v>
       </c>
       <c r="Q78">
-        <v>1215.601117959381</v>
+        <v>1558.020083463381</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.2096718392727955</v>
+        <v>0.2096470077251274</v>
       </c>
       <c r="T78">
         <v>2.135475775221949</v>
       </c>
       <c r="U78">
-        <v>0.1229941048847012</v>
+        <v>0.1005941048847012</v>
       </c>
       <c r="V78">
         <v>0.34</v>
       </c>
       <c r="W78">
-        <v>0.0811761092239028</v>
+        <v>0.06639210922390279</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y78">
-        <v>1.272956540415064</v>
+        <v>1.556414766301957</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.1121885334717183</v>
+        <v>0.1007989212230165</v>
       </c>
       <c r="C79">
-        <v>1608.145799881317</v>
+        <v>5963.722172876081</v>
       </c>
       <c r="D79">
-        <v>21440.95779988131</v>
+        <v>25796.53417287608</v>
       </c>
       <c r="E79">
         <v>22845.412</v>
@@ -7771,45 +7771,45 @@
         <v>3626.3</v>
       </c>
       <c r="M79">
-        <v>2886.205739974635</v>
+        <v>2360.562591174634</v>
       </c>
       <c r="N79">
-        <v>740.0942600253657</v>
+        <v>1265.737408825366</v>
       </c>
       <c r="O79">
-        <v>251.6320484086243</v>
+        <v>430.3507190006245</v>
       </c>
       <c r="P79">
-        <v>488.4622116167413</v>
+        <v>835.3866898247416</v>
       </c>
       <c r="Q79">
-        <v>1190.862211616741</v>
+        <v>1537.786689824741</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.216012736388318</v>
+        <v>0.215986944002658</v>
       </c>
       <c r="T79">
         <v>2.218106398295825</v>
       </c>
       <c r="U79">
-        <v>0.1229941048847012</v>
+        <v>0.1005941048847012</v>
       </c>
       <c r="V79">
         <v>0.34</v>
       </c>
       <c r="W79">
-        <v>0.0811761092239028</v>
+        <v>0.06639210922390279</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y79">
-        <v>1.256424637292791</v>
+        <v>1.536201587518815</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.1303131952614645</v>
+        <v>0.1008245575818363</v>
       </c>
       <c r="C80">
-        <v>-3239.954325810169</v>
+        <v>5647.167865477575</v>
       </c>
       <c r="D80">
-        <v>16897.61367418983</v>
+        <v>25784.73586547757</v>
       </c>
       <c r="E80">
         <v>23150.168</v>
@@ -7853,45 +7853,45 @@
         <v>3626.3</v>
       </c>
       <c r="M80">
-        <v>3700.999585002877</v>
+        <v>2391.219248202876</v>
       </c>
       <c r="N80">
-        <v>-74.69958500287657</v>
+        <v>1235.080751797124</v>
       </c>
       <c r="O80">
-        <v>-25.39785890097804</v>
+        <v>419.9274556110221</v>
       </c>
       <c r="P80">
-        <v>-49.30172610189854</v>
+        <v>815.1532961861017</v>
       </c>
       <c r="Q80">
-        <v>653.0982738981011</v>
+        <v>1517.553296186101</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.2242203939764942</v>
+        <v>0.2229032381236004</v>
       </c>
       <c r="T80">
-        <v>2.325063481517973</v>
+        <v>2.308248896194599</v>
       </c>
       <c r="U80">
-        <v>0.1556941048847012</v>
+        <v>0.1005941048847012</v>
       </c>
       <c r="V80">
-        <v>0.3331375677522649</v>
+        <v>0.34</v>
       </c>
       <c r="W80">
-        <v>0.1038265494700458</v>
+        <v>0.06639210922390279</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y80">
-        <v>0.9798163757419556</v>
+        <v>1.516506695371138</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.1314121363103115</v>
+        <v>0.1082540739406561</v>
       </c>
       <c r="C81">
-        <v>-3759.057139513749</v>
+        <v>2324.754956514269</v>
       </c>
       <c r="D81">
-        <v>16683.26686048625</v>
+        <v>22767.07895651427</v>
       </c>
       <c r="E81">
         <v>23454.924</v>
@@ -7935,45 +7935,45 @@
         <v>3626.3</v>
       </c>
       <c r="M81">
-        <v>3748.448297631118</v>
+        <v>2763.751186031119</v>
       </c>
       <c r="N81">
-        <v>-122.1482976311181</v>
+        <v>862.5488139688814</v>
       </c>
       <c r="O81">
-        <v>-41.53042119458016</v>
+        <v>293.2665967494197</v>
       </c>
       <c r="P81">
-        <v>-80.61787643653795</v>
+        <v>569.2822172194617</v>
       </c>
       <c r="Q81">
-        <v>621.7821235634617</v>
+        <v>1271.682217219461</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2327166032134701</v>
+        <v>0.230478226922728</v>
       </c>
       <c r="T81">
-        <v>2.435780790161686</v>
+        <v>2.406976393893256</v>
       </c>
       <c r="U81">
-        <v>0.1556941048847012</v>
+        <v>0.1147941048847012</v>
       </c>
       <c r="V81">
-        <v>0.3289206365148945</v>
+        <v>0.34</v>
       </c>
       <c r="W81">
-        <v>0.1044831008044086</v>
+        <v>0.07576410922390281</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y81">
-        <v>0.9674136368085132</v>
+        <v>1.312093512009503</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.1325110773591585</v>
+        <v>0.1083734302994759</v>
       </c>
       <c r="C82">
-        <v>-4272.790076799327</v>
+        <v>1977.273792885295</v>
       </c>
       <c r="D82">
-        <v>16474.28992320067</v>
+        <v>22724.35379288529</v>
       </c>
       <c r="E82">
         <v>23759.68</v>
@@ -8017,45 +8017,45 @@
         <v>3626.3</v>
       </c>
       <c r="M82">
-        <v>3795.897010259361</v>
+        <v>2798.735378259361</v>
       </c>
       <c r="N82">
-        <v>-169.5970102593606</v>
+        <v>827.5646217406393</v>
       </c>
       <c r="O82">
-        <v>-57.6629834881826</v>
+        <v>281.3719713918174</v>
       </c>
       <c r="P82">
-        <v>-111.934026771178</v>
+        <v>546.1926503488219</v>
       </c>
       <c r="Q82">
-        <v>590.4659732288217</v>
+        <v>1248.592650348822</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2420624333741436</v>
+        <v>0.2388107146017682</v>
       </c>
       <c r="T82">
-        <v>2.55756982966977</v>
+        <v>2.515576641361779</v>
       </c>
       <c r="U82">
-        <v>0.1556941048847012</v>
+        <v>0.1147941048847012</v>
       </c>
       <c r="V82">
-        <v>0.3248091285584583</v>
+        <v>0.34</v>
       </c>
       <c r="W82">
-        <v>0.1051232383554122</v>
+        <v>0.07576410922390281</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y82">
-        <v>0.9553209663484067</v>
+        <v>1.295692343109384</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1336100184080055</v>
+        <v>0.1084927866582957</v>
       </c>
       <c r="C83">
-        <v>-4781.352432741169</v>
+        <v>1629.952686712091</v>
       </c>
       <c r="D83">
-        <v>16270.48356725883</v>
+        <v>22681.78868671209</v>
       </c>
       <c r="E83">
         <v>24064.436</v>
@@ -8099,45 +8099,45 @@
         <v>3626.3</v>
       </c>
       <c r="M83">
-        <v>3843.345722887603</v>
+        <v>2833.719570487603</v>
       </c>
       <c r="N83">
-        <v>-217.0457228876026</v>
+        <v>792.5804295123971</v>
       </c>
       <c r="O83">
-        <v>-73.79554578178487</v>
+        <v>269.477346034215</v>
       </c>
       <c r="P83">
-        <v>-143.2501771058177</v>
+        <v>523.103083478182</v>
       </c>
       <c r="Q83">
-        <v>559.149822894182</v>
+        <v>1225.503083478182</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2523920351306775</v>
+        <v>0.2480203062470232</v>
       </c>
       <c r="T83">
-        <v>2.692178768073443</v>
+        <v>2.635608493826988</v>
       </c>
       <c r="U83">
-        <v>0.1556941048847012</v>
+        <v>0.1147941048847012</v>
       </c>
       <c r="V83">
-        <v>0.3207991393169958</v>
+        <v>0.34</v>
       </c>
       <c r="W83">
-        <v>0.105747570040959</v>
+        <v>0.07576410922390281</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y83">
-        <v>0.9435268803441054</v>
+        <v>1.279696141342602</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1347089594568525</v>
+        <v>0.1086121430171155</v>
       </c>
       <c r="C84">
-        <v>-5284.933760869397</v>
+        <v>1282.790740262837</v>
       </c>
       <c r="D84">
-        <v>16071.65823913061</v>
+        <v>22639.38274026284</v>
       </c>
       <c r="E84">
         <v>24369.192</v>
@@ -8181,45 +8181,45 @@
         <v>3626.3</v>
       </c>
       <c r="M84">
-        <v>3890.794435515845</v>
+        <v>2868.703762715845</v>
       </c>
       <c r="N84">
-        <v>-264.4944355158445</v>
+        <v>757.596237284155</v>
       </c>
       <c r="O84">
-        <v>-89.92810807538716</v>
+        <v>257.5827206766127</v>
       </c>
       <c r="P84">
-        <v>-174.5663274404574</v>
+        <v>500.0135166075423</v>
       </c>
       <c r="Q84">
-        <v>527.8336725595423</v>
+        <v>1202.413516607542</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2638693704157152</v>
+        <v>0.2582531858528621</v>
       </c>
       <c r="T84">
-        <v>2.841744255188634</v>
+        <v>2.768977218788332</v>
       </c>
       <c r="U84">
-        <v>0.1556941048847012</v>
+        <v>0.1147941048847012</v>
       </c>
       <c r="V84">
-        <v>0.3168869546911788</v>
+        <v>0.34</v>
       </c>
       <c r="W84">
-        <v>0.1063566741244193</v>
+        <v>0.07576410922390281</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y84">
-        <v>0.9320204549740553</v>
+        <v>1.264090090838424</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1358079005056995</v>
+        <v>0.1244110761599524</v>
       </c>
       <c r="C85">
-        <v>-5783.714461192718</v>
+        <v>-3513.185228246137</v>
       </c>
       <c r="D85">
-        <v>15877.63353880728</v>
+        <v>18148.16277175386</v>
       </c>
       <c r="E85">
         <v>24673.948</v>
@@ -8263,37 +8263,37 @@
         <v>3626.3</v>
       </c>
       <c r="M85">
-        <v>3938.243148144087</v>
+        <v>3627.117747744087</v>
       </c>
       <c r="N85">
-        <v>-311.9431481440865</v>
+        <v>-0.8177477440863186</v>
       </c>
       <c r="O85">
-        <v>-106.0606703689894</v>
+        <v>-0.2780342329893483</v>
       </c>
       <c r="P85">
-        <v>-205.8824777750971</v>
+        <v>-0.5397135110969702</v>
       </c>
       <c r="Q85">
-        <v>496.5175222249026</v>
+        <v>701.8602864889027</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.276696980440169</v>
+        <v>0.2697097784063625</v>
       </c>
       <c r="T85">
-        <v>3.008905681964436</v>
+        <v>2.918295025712408</v>
       </c>
       <c r="U85">
-        <v>0.1556941048847012</v>
+        <v>0.1433941048847012</v>
       </c>
       <c r="V85">
-        <v>0.3130690395744176</v>
+        <v>0.3399233456831772</v>
       </c>
       <c r="W85">
-        <v>0.1069511010010492</v>
+        <v>0.09465110100104916</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.9207912928659341</v>
+        <v>0.9997745461269916</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.1369068415545465</v>
+        <v>0.1253870172087994</v>
       </c>
       <c r="C86">
-        <v>-6277.866326135976</v>
+        <v>-4037.645508790069</v>
       </c>
       <c r="D86">
-        <v>15688.23767386402</v>
+        <v>17928.45849120993</v>
       </c>
       <c r="E86">
         <v>24978.704</v>
@@ -8345,37 +8345,37 @@
         <v>3626.3</v>
       </c>
       <c r="M86">
-        <v>3985.691860772328</v>
+        <v>3670.817961572328</v>
       </c>
       <c r="N86">
-        <v>-359.3918607723281</v>
+        <v>-44.51796157232775</v>
       </c>
       <c r="O86">
-        <v>-122.1932326625916</v>
+        <v>-15.13610693459144</v>
       </c>
       <c r="P86">
-        <v>-237.1986281097365</v>
+        <v>-29.38185463773631</v>
       </c>
       <c r="Q86">
-        <v>465.2013718902631</v>
+        <v>673.0181453622633</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2911280417176794</v>
+        <v>0.2837041395567599</v>
       </c>
       <c r="T86">
-        <v>3.196962287087211</v>
+        <v>3.100688464819432</v>
       </c>
       <c r="U86">
-        <v>0.1556941048847012</v>
+        <v>0.1433941048847012</v>
       </c>
       <c r="V86">
-        <v>0.3093420271985318</v>
+        <v>0.3358766391869489</v>
       </c>
       <c r="W86">
-        <v>0.1075313748568069</v>
+        <v>0.09523137485680691</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.9098294917603874</v>
+        <v>0.9878724681969085</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.1380057826033936</v>
+        <v>0.1263629582576464</v>
       </c>
       <c r="C87">
-        <v>-6767.553047865</v>
+        <v>-4556.849874670432</v>
       </c>
       <c r="D87">
-        <v>15503.306952135</v>
+        <v>17714.01012532957</v>
       </c>
       <c r="E87">
         <v>25283.46</v>
@@ -8427,37 +8427,37 @@
         <v>3626.3</v>
       </c>
       <c r="M87">
-        <v>4033.14057340057</v>
+        <v>3714.51817540057</v>
       </c>
       <c r="N87">
-        <v>-406.8405734005701</v>
+        <v>-88.21817540057009</v>
       </c>
       <c r="O87">
-        <v>-138.3257949561938</v>
+        <v>-29.99417963619383</v>
       </c>
       <c r="P87">
-        <v>-268.5147784443762</v>
+        <v>-58.22399576437626</v>
       </c>
       <c r="Q87">
-        <v>433.8852215556234</v>
+        <v>644.1760042356234</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.3074832444988581</v>
+        <v>0.2995644155272107</v>
       </c>
       <c r="T87">
-        <v>3.410093106226359</v>
+        <v>3.307401029140728</v>
       </c>
       <c r="U87">
-        <v>0.1556941048847012</v>
+        <v>0.1433941048847012</v>
       </c>
       <c r="V87">
-        <v>0.3057027092314902</v>
+        <v>0.3319251493141613</v>
       </c>
       <c r="W87">
-        <v>0.1080979952100763</v>
+        <v>0.09579799521007627</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8991256153867357</v>
+        <v>0.9762504391592978</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.1391047236522406</v>
+        <v>0.1273388993064934</v>
       </c>
       <c r="C88">
-        <v>-7252.930690147885</v>
+        <v>-5070.984699931869</v>
       </c>
       <c r="D88">
-        <v>15322.68530985211</v>
+        <v>17504.63130006813</v>
       </c>
       <c r="E88">
         <v>25588.216</v>
@@ -8509,37 +8509,37 @@
         <v>3626.3</v>
       </c>
       <c r="M88">
-        <v>4080.589286028813</v>
+        <v>3758.218389228813</v>
       </c>
       <c r="N88">
-        <v>-454.2892860288125</v>
+        <v>-131.9183892288124</v>
       </c>
       <c r="O88">
-        <v>-154.4583572497963</v>
+        <v>-44.85225233779623</v>
       </c>
       <c r="P88">
-        <v>-299.8309287790162</v>
+        <v>-87.0661368910162</v>
       </c>
       <c r="Q88">
-        <v>402.5690712209834</v>
+        <v>615.3338631089835</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.3261749048202051</v>
+        <v>0.3176904452077257</v>
       </c>
       <c r="T88">
-        <v>3.653671185242528</v>
+        <v>3.543643959793637</v>
       </c>
       <c r="U88">
-        <v>0.1556941048847012</v>
+        <v>0.1433941048847012</v>
       </c>
       <c r="V88">
-        <v>0.3021480265660077</v>
+        <v>0.3280655545546943</v>
       </c>
       <c r="W88">
-        <v>0.1086514383458277</v>
+        <v>0.09635143834582773</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8886706663706109</v>
+        <v>0.9648986898667478</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.1402036647010876</v>
+        <v>0.1283148403553404</v>
       </c>
       <c r="C89">
-        <v>-7734.148127611603</v>
+        <v>-5580.227649824334</v>
       </c>
       <c r="D89">
-        <v>15146.22387238839</v>
+        <v>17300.14435017566</v>
       </c>
       <c r="E89">
         <v>25892.972</v>
@@ -8591,37 +8591,37 @@
         <v>3626.3</v>
       </c>
       <c r="M89">
-        <v>4128.037998657054</v>
+        <v>3801.918603057054</v>
       </c>
       <c r="N89">
-        <v>-501.737998657054</v>
+        <v>-175.6186030570539</v>
       </c>
       <c r="O89">
-        <v>-170.5909195433984</v>
+        <v>-59.71032503939832</v>
       </c>
       <c r="P89">
-        <v>-331.1470791136556</v>
+        <v>-115.9082780176555</v>
       </c>
       <c r="Q89">
-        <v>371.252920886344</v>
+        <v>586.4917219823441</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.34774220519099</v>
+        <v>0.3386050948390892</v>
       </c>
       <c r="T89">
-        <v>3.934722814876568</v>
+        <v>3.81623195670084</v>
       </c>
       <c r="U89">
-        <v>0.1556941048847012</v>
+        <v>0.1433941048847012</v>
       </c>
       <c r="V89">
-        <v>0.29867506074341</v>
+        <v>0.3242946861115369</v>
       </c>
       <c r="W89">
-        <v>0.1091921586508722</v>
+        <v>0.09689215865087224</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8784560610100293</v>
+        <v>0.9538079003280496</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.1413026057499346</v>
+        <v>0.1292907814041875</v>
       </c>
       <c r="C90">
-        <v>-8211.347454992316</v>
+        <v>-6084.748183604828</v>
       </c>
       <c r="D90">
-        <v>14973.78054500768</v>
+        <v>17100.37981639517</v>
       </c>
       <c r="E90">
         <v>26197.728</v>
@@ -8673,37 +8673,37 @@
         <v>3626.3</v>
       </c>
       <c r="M90">
-        <v>4175.486711285296</v>
+        <v>3845.618816885296</v>
       </c>
       <c r="N90">
-        <v>-549.186711285296</v>
+        <v>-219.3188168852962</v>
       </c>
       <c r="O90">
-        <v>-186.7234818370007</v>
+        <v>-74.56839774100071</v>
       </c>
       <c r="P90">
-        <v>-362.4632294482954</v>
+        <v>-144.7504191442955</v>
       </c>
       <c r="Q90">
-        <v>339.9367705517043</v>
+        <v>557.6495808557041</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.3729040556235727</v>
+        <v>0.3630055194090134</v>
       </c>
       <c r="T90">
-        <v>4.262616382782951</v>
+        <v>4.13425128642591</v>
       </c>
       <c r="U90">
-        <v>0.1556941048847012</v>
+        <v>0.1433941048847012</v>
       </c>
       <c r="V90">
-        <v>0.2952810259622348</v>
+        <v>0.3206095192239057</v>
       </c>
       <c r="W90">
-        <v>0.1097205898580749</v>
+        <v>0.09742058985807485</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8684736057712789</v>
+        <v>0.942969174187958</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.1424015467987816</v>
+        <v>0.1302667224530345</v>
       </c>
       <c r="C91">
-        <v>-8684.664368743906</v>
+        <v>-6584.708022901566</v>
       </c>
       <c r="D91">
-        <v>14805.21963125609</v>
+        <v>16905.17597709843</v>
       </c>
       <c r="E91">
         <v>26502.484</v>
@@ -8755,37 +8755,37 @@
         <v>3626.3</v>
       </c>
       <c r="M91">
-        <v>4222.935423913538</v>
+        <v>3889.319030713538</v>
       </c>
       <c r="N91">
-        <v>-596.635423913538</v>
+        <v>-263.0190307135381</v>
       </c>
       <c r="O91">
-        <v>-202.856044130603</v>
+        <v>-89.42647044260296</v>
       </c>
       <c r="P91">
-        <v>-393.7793797829351</v>
+        <v>-173.5925602709351</v>
       </c>
       <c r="Q91">
-        <v>308.6206202170646</v>
+        <v>528.8074397290645</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.4026407879529884</v>
+        <v>0.3918423848098327</v>
       </c>
       <c r="T91">
-        <v>4.650126963035945</v>
+        <v>4.510092312464629</v>
       </c>
       <c r="U91">
-        <v>0.1556941048847012</v>
+        <v>0.1433941048847012</v>
       </c>
       <c r="V91">
-        <v>0.2919632616255805</v>
+        <v>0.3170071650753226</v>
       </c>
       <c r="W91">
-        <v>0.1102371462066886</v>
+        <v>0.09793714620668863</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8587154753693544</v>
+        <v>0.9323740149274192</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.1435004878476286</v>
+        <v>0.1312426635018815</v>
       </c>
       <c r="C92">
-        <v>-9154.228523158759</v>
+        <v>-7080.261588361624</v>
       </c>
       <c r="D92">
-        <v>14640.41147684124</v>
+        <v>16714.37841163838</v>
       </c>
       <c r="E92">
         <v>26807.24</v>
@@ -8837,37 +8837,37 @@
         <v>3626.3</v>
       </c>
       <c r="M92">
-        <v>4270.384136541781</v>
+        <v>3933.019244541781</v>
       </c>
       <c r="N92">
-        <v>-644.0841365417809</v>
+        <v>-306.7192445417804</v>
       </c>
       <c r="O92">
-        <v>-218.9886064242055</v>
+        <v>-104.2845431442054</v>
       </c>
       <c r="P92">
-        <v>-425.0955301175754</v>
+        <v>-202.4347013975751</v>
       </c>
       <c r="Q92">
-        <v>277.3044698824242</v>
+        <v>499.9652986024246</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.4383248667482872</v>
+        <v>0.4264466232908161</v>
       </c>
       <c r="T92">
-        <v>5.115139659339541</v>
+        <v>4.961101543711093</v>
       </c>
       <c r="U92">
-        <v>0.1556941048847012</v>
+        <v>0.1433941048847012</v>
       </c>
       <c r="V92">
-        <v>0.2887192253852962</v>
+        <v>0.3134848632411523</v>
       </c>
       <c r="W92">
-        <v>0.1107422235253332</v>
+        <v>0.09844222352533323</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8491741923096947</v>
+        <v>0.9220143036504478</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.1445994288964756</v>
+        <v>0.1322186045507285</v>
       </c>
       <c r="C93">
-        <v>-9620.163862964768</v>
+        <v>-7571.55640705947</v>
       </c>
       <c r="D93">
-        <v>14479.23213703523</v>
+        <v>16527.83959294053</v>
       </c>
       <c r="E93">
         <v>27111.996</v>
@@ -8919,37 +8919,37 @@
         <v>3626.3</v>
       </c>
       <c r="M93">
-        <v>4317.832849170022</v>
+        <v>3976.719458370022</v>
       </c>
       <c r="N93">
-        <v>-691.532849170022</v>
+        <v>-350.4194583700223</v>
       </c>
       <c r="O93">
-        <v>-235.1211687178075</v>
+        <v>-119.1426158458076</v>
       </c>
       <c r="P93">
-        <v>-456.4116804522145</v>
+        <v>-231.2768425242147</v>
       </c>
       <c r="Q93">
-        <v>245.9883195477851</v>
+        <v>471.1231574757849</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.4819387408314302</v>
+        <v>0.4687406925453512</v>
       </c>
       <c r="T93">
-        <v>5.683488510377267</v>
+        <v>5.512335048567881</v>
       </c>
       <c r="U93">
-        <v>0.1556941048847012</v>
+        <v>0.1433941048847012</v>
       </c>
       <c r="V93">
-        <v>0.2855464866447985</v>
+        <v>0.3100399746341067</v>
       </c>
       <c r="W93">
-        <v>0.111236200243568</v>
+        <v>0.09893620024356801</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8398426077788191</v>
+        <v>0.9118822783356078</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.1456983699453226</v>
+        <v>0.1331945455995755</v>
       </c>
       <c r="C94">
-        <v>-10082.58893419194</v>
+        <v>-8058.7334929258</v>
       </c>
       <c r="D94">
-        <v>14321.56306580806</v>
+        <v>16345.4185070742</v>
       </c>
       <c r="E94">
         <v>27416.752</v>
@@ -9001,37 +9001,37 @@
         <v>3626.3</v>
       </c>
       <c r="M94">
-        <v>4365.281561798265</v>
+        <v>4020.419672198264</v>
       </c>
       <c r="N94">
-        <v>-738.9815617982649</v>
+        <v>-394.1196721982642</v>
       </c>
       <c r="O94">
-        <v>-251.2537310114101</v>
+        <v>-134.0006885474098</v>
       </c>
       <c r="P94">
-        <v>-487.7278307868548</v>
+        <v>-260.1189836508544</v>
       </c>
       <c r="Q94">
-        <v>214.6721692131448</v>
+        <v>442.2810163491453</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.5364560834353591</v>
+        <v>0.5216082791135203</v>
       </c>
       <c r="T94">
-        <v>6.393924574174427</v>
+        <v>6.201376929638869</v>
       </c>
       <c r="U94">
-        <v>0.1556941048847012</v>
+        <v>0.1433941048847012</v>
       </c>
       <c r="V94">
-        <v>0.2824427204856159</v>
+        <v>0.3066699749098229</v>
       </c>
       <c r="W94">
-        <v>0.1117194383374934</v>
+        <v>0.09941943833749338</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8307138837812231</v>
+        <v>0.9019705144406556</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.1467973109941696</v>
+        <v>0.1341704866484226</v>
       </c>
       <c r="C95">
-        <v>-10541.61717494688</v>
+        <v>-8541.92770225797</v>
       </c>
       <c r="D95">
-        <v>14167.29082505312</v>
+        <v>16166.98029774203</v>
       </c>
       <c r="E95">
         <v>27721.508</v>
@@ -9083,37 +9083,37 @@
         <v>3626.3</v>
       </c>
       <c r="M95">
-        <v>4412.730274426507</v>
+        <v>4064.119886026507</v>
       </c>
       <c r="N95">
-        <v>-786.4302744265069</v>
+        <v>-437.8198860265065</v>
       </c>
       <c r="O95">
-        <v>-267.3862933050124</v>
+        <v>-148.8587612490122</v>
       </c>
       <c r="P95">
-        <v>-519.0439811214945</v>
+        <v>-288.9611247774943</v>
       </c>
       <c r="Q95">
-        <v>183.3560188785051</v>
+        <v>413.4388752225053</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.6065498096404106</v>
+        <v>0.5895808904154519</v>
       </c>
       <c r="T95">
-        <v>7.307342370485062</v>
+        <v>7.087287919587281</v>
       </c>
       <c r="U95">
-        <v>0.1556941048847012</v>
+        <v>0.1433941048847012</v>
       </c>
       <c r="V95">
-        <v>0.2794057019857706</v>
+        <v>0.3033724482978893</v>
       </c>
       <c r="W95">
-        <v>0.1121922842143451</v>
+        <v>0.0998922842143451</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8217814764287369</v>
+        <v>0.8922719067584979</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1478962520430167</v>
+        <v>0.1351464276972695</v>
       </c>
       <c r="C96">
-        <v>-10997.35718759428</v>
+        <v>-9021.268066196026</v>
       </c>
       <c r="D96">
-        <v>14016.30681240572</v>
+        <v>15992.39593380397</v>
       </c>
       <c r="E96">
         <v>28026.264</v>
@@ -9165,37 +9165,37 @@
         <v>3626.3</v>
       </c>
       <c r="M96">
-        <v>4460.178987054749</v>
+        <v>4107.820099854749</v>
       </c>
       <c r="N96">
-        <v>-833.8789870547489</v>
+        <v>-481.5200998547489</v>
       </c>
       <c r="O96">
-        <v>-283.5188555986147</v>
+        <v>-163.7168339506146</v>
       </c>
       <c r="P96">
-        <v>-550.3601314561342</v>
+        <v>-317.8032659041343</v>
       </c>
       <c r="Q96">
-        <v>152.0398685438654</v>
+        <v>384.5967340958654</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.7000081112471459</v>
+        <v>0.6802110388180272</v>
       </c>
       <c r="T96">
-        <v>8.525232765565908</v>
+        <v>8.268502572851828</v>
       </c>
       <c r="U96">
-        <v>0.1556941048847012</v>
+        <v>0.1433941048847012</v>
       </c>
       <c r="V96">
-        <v>0.2764333009008155</v>
+        <v>0.3001450818266351</v>
       </c>
       <c r="W96">
-        <v>0.1126550695406255</v>
+        <v>0.1003550695406255</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8130391202965163</v>
+        <v>0.8827796524312798</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1489951930918637</v>
+        <v>0.1361223687461166</v>
       </c>
       <c r="C97">
-        <v>-11449.91299371771</v>
+        <v>-9496.878101886741</v>
       </c>
       <c r="D97">
-        <v>13868.50700628229</v>
+        <v>15821.54189811326</v>
       </c>
       <c r="E97">
         <v>28331.02</v>
@@ -9247,37 +9247,37 @@
         <v>3626.3</v>
       </c>
       <c r="M97">
-        <v>4507.627699682991</v>
+        <v>4151.52031368299</v>
       </c>
       <c r="N97">
-        <v>-881.3276996829909</v>
+        <v>-525.2203136829903</v>
       </c>
       <c r="O97">
-        <v>-299.6514178922169</v>
+        <v>-178.5749066522167</v>
       </c>
       <c r="P97">
-        <v>-581.6762817907741</v>
+        <v>-346.6454070307736</v>
       </c>
       <c r="Q97">
-        <v>120.7237182092256</v>
+        <v>355.7545929692261</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.8308497334965753</v>
+        <v>0.8070932465816331</v>
       </c>
       <c r="T97">
-        <v>10.23027931867909</v>
+        <v>9.922203087422199</v>
       </c>
       <c r="U97">
-        <v>0.1556941048847012</v>
+        <v>0.1433941048847012</v>
       </c>
       <c r="V97">
-        <v>0.273523476680807</v>
+        <v>0.2969856599126706</v>
       </c>
       <c r="W97">
-        <v>0.1131081120179315</v>
+        <v>0.1008081120179315</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8044808137670793</v>
+        <v>0.8734872350372664</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.1838780423301154</v>
+        <v>0.1370983097949636</v>
       </c>
       <c r="C98">
-        <v>-15232.57890902203</v>
+        <v>-9968.876103912575</v>
       </c>
       <c r="D98">
-        <v>10390.59709097797</v>
+        <v>15654.29989608742</v>
       </c>
       <c r="E98">
         <v>28635.776</v>
@@ -9329,45 +9329,45 @@
         <v>3626.3</v>
       </c>
       <c r="M98">
-        <v>5511.766447511232</v>
+        <v>4195.220527511232</v>
       </c>
       <c r="N98">
-        <v>-1885.466447511232</v>
+        <v>-568.9205275112317</v>
       </c>
       <c r="O98">
-        <v>-641.0585921538189</v>
+        <v>-193.4329793538188</v>
       </c>
       <c r="P98">
-        <v>-1244.407855357413</v>
+        <v>-375.4875481574129</v>
       </c>
       <c r="Q98">
-        <v>-542.0078553574135</v>
+        <v>326.9124518425867</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.086909871605835</v>
+        <v>0.9974165582270392</v>
       </c>
       <c r="T98">
-        <v>13.56709560364213</v>
+        <v>12.40275385927772</v>
       </c>
       <c r="U98">
-        <v>0.1883941048847012</v>
+        <v>0.1433941048847012</v>
       </c>
       <c r="V98">
-        <v>0.223692714802297</v>
+        <v>0.2938920592885803</v>
       </c>
       <c r="W98">
-        <v>0.1462517161102937</v>
+        <v>0.1012517161102937</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y98">
-        <v>0.6579197494185207</v>
+        <v>0.8643884096722949</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.1853039833789624</v>
+        <v>0.1380742508438106</v>
       </c>
       <c r="C99">
-        <v>-15642.77100889588</v>
+        <v>-10437.37541743073</v>
       </c>
       <c r="D99">
-        <v>10285.16099110412</v>
+        <v>15490.55658256926</v>
       </c>
       <c r="E99">
         <v>28940.532</v>
@@ -9411,45 +9411,45 @@
         <v>3626.3</v>
       </c>
       <c r="M99">
-        <v>5569.180681339475</v>
+        <v>4238.920741339474</v>
       </c>
       <c r="N99">
-        <v>-1942.880681339475</v>
+        <v>-612.6207413394741</v>
       </c>
       <c r="O99">
-        <v>-660.5794316554216</v>
+        <v>-208.2910520554212</v>
       </c>
       <c r="P99">
-        <v>-1282.301249684053</v>
+        <v>-404.3296892840528</v>
       </c>
       <c r="Q99">
-        <v>-579.9012496840537</v>
+        <v>298.0703107159468</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.433946495474446</v>
+        <v>1.314622077636052</v>
       </c>
       <c r="T99">
-        <v>18.08946080485618</v>
+        <v>16.53700514570363</v>
       </c>
       <c r="U99">
-        <v>0.1883941048847012</v>
+        <v>0.1433941048847012</v>
       </c>
       <c r="V99">
-        <v>0.2213866043404177</v>
+        <v>0.2908622442443681</v>
       </c>
       <c r="W99">
-        <v>0.1466861737265247</v>
+        <v>0.1016861737265247</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y99">
-        <v>0.6511370715894638</v>
+        <v>0.8554771889540238</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2403568202960627</v>
+        <v>0.1390501918926576</v>
       </c>
       <c r="C100">
-        <v>-18842.68167729054</v>
+        <v>-10902.48469434745</v>
       </c>
       <c r="D100">
-        <v>7390.006322709456</v>
+        <v>15330.20330565255</v>
       </c>
       <c r="E100">
         <v>29245.288</v>
@@ -9493,45 +9493,45 @@
         <v>3626.3</v>
       </c>
       <c r="M100">
-        <v>7185.604708767717</v>
+        <v>4282.620955167717</v>
       </c>
       <c r="N100">
-        <v>-3559.304708767717</v>
+        <v>-656.3209551677164</v>
       </c>
       <c r="O100">
-        <v>-1210.163600981024</v>
+        <v>-223.1491247570236</v>
       </c>
       <c r="P100">
-        <v>-2349.141107786693</v>
+        <v>-433.1718304106928</v>
       </c>
       <c r="Q100">
-        <v>-1646.741107786694</v>
+        <v>269.2281695893068</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>2.251564536624331</v>
+        <v>1.949033116454079</v>
       </c>
       <c r="T100">
-        <v>28.74415003033959</v>
+        <v>24.80550771855544</v>
       </c>
       <c r="U100">
-        <v>0.2405941048847012</v>
+        <v>0.1433941048847012</v>
       </c>
       <c r="V100">
-        <v>0.1715850022330885</v>
+        <v>0.2878942621602419</v>
       </c>
       <c r="W100">
-        <v>0.1993117648607919</v>
+        <v>0.1021117648607918</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y100">
-        <v>0.5046617712737897</v>
+        <v>0.8467478298830643</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2423047613449097</v>
+        <v>0.1400261329415046</v>
       </c>
       <c r="C101">
-        <v>-19220.31584476218</v>
+        <v>-11364.30813374431</v>
       </c>
       <c r="D101">
-        <v>7317.128155237823</v>
+        <v>15173.13586625569</v>
       </c>
       <c r="E101">
         <v>29550.044</v>
@@ -9575,45 +9575,45 @@
         <v>3626.3</v>
       </c>
       <c r="M101">
-        <v>7258.927205795958</v>
+        <v>4326.321168995958</v>
       </c>
       <c r="N101">
-        <v>-3632.627205795958</v>
+        <v>-700.0211689959579</v>
       </c>
       <c r="O101">
-        <v>-1235.093249970626</v>
+        <v>-238.0071974586257</v>
       </c>
       <c r="P101">
-        <v>-2397.533955825332</v>
+        <v>-462.0139715373322</v>
       </c>
       <c r="Q101">
-        <v>-1695.133955825332</v>
+        <v>240.3860284626675</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>4.457329073248663</v>
+        <v>3.852266232908156</v>
       </c>
       <c r="T101">
-        <v>57.48830006067918</v>
+        <v>49.61101543711087</v>
       </c>
       <c r="U101">
-        <v>0.2405941048847012</v>
+        <v>0.1433941048847012</v>
       </c>
       <c r="V101">
-        <v>0.1698518203923503</v>
+        <v>0.2849862393101385</v>
       </c>
       <c r="W101">
-        <v>0.1997287581943667</v>
+        <v>0.1025287581943667</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y101">
-        <v>0.4995641776245596</v>
+        <v>0.8381948215004072</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/brazil/brazil_beverage_alcoholic.xlsx
+++ b/research/traditional_assets/database/data/brazil/brazil_beverage_alcoholic.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09882492159389236</v>
+        <v>0.09868225795271214</v>
       </c>
       <c r="C2">
-        <v>30372.01160100004</v>
+        <v>30138.01401390921</v>
       </c>
       <c r="D2">
-        <v>26738.61160100004</v>
+        <v>26809.37001390921</v>
       </c>
       <c r="E2">
-        <v>-620.8</v>
+        <v>-316.044</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>304.756</v>
       </c>
       <c r="G2">
         <v>3633.4</v>
@@ -1457,28 +1457,28 @@
         <v>3626.3</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>22.885379028242</v>
       </c>
       <c r="N2">
-        <v>3626.3</v>
+        <v>3603.414620971758</v>
       </c>
       <c r="O2">
-        <v>1232.942</v>
+        <v>1225.160971130398</v>
       </c>
       <c r="P2">
-        <v>2393.358</v>
+        <v>2378.25364984136</v>
       </c>
       <c r="Q2">
-        <v>3095.758</v>
+        <v>3080.65364984136</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09882492159389236</v>
+        <v>0.09917842107118496</v>
       </c>
       <c r="T2">
-        <v>0.6910924838905985</v>
+        <v>0.6956997671165358</v>
       </c>
       <c r="U2">
         <v>0.07509410488470122</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>158.4548805385708</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09868225795271214</v>
+        <v>0.09853959431153193</v>
       </c>
       <c r="C3">
-        <v>30138.01401390921</v>
+        <v>29904.39191658594</v>
       </c>
       <c r="D3">
-        <v>26809.37001390921</v>
+        <v>26880.50391658594</v>
       </c>
       <c r="E3">
-        <v>-316.044</v>
+        <v>-11.28800000000001</v>
       </c>
       <c r="F3">
-        <v>304.756</v>
+        <v>609.5119999999999</v>
       </c>
       <c r="G3">
         <v>3633.4</v>
@@ -1539,28 +1539,28 @@
         <v>3626.3</v>
       </c>
       <c r="M3">
-        <v>22.885379028242</v>
+        <v>45.77075805648401</v>
       </c>
       <c r="N3">
-        <v>3603.414620971758</v>
+        <v>3580.529241943516</v>
       </c>
       <c r="O3">
-        <v>1225.160971130398</v>
+        <v>1217.379942260796</v>
       </c>
       <c r="P3">
-        <v>2378.25364984136</v>
+        <v>2363.149299682721</v>
       </c>
       <c r="Q3">
-        <v>3080.65364984136</v>
+        <v>3065.549299682721</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09917842107118496</v>
+        <v>0.09953913482352436</v>
       </c>
       <c r="T3">
-        <v>0.6956997671165358</v>
+        <v>0.7004010765307576</v>
       </c>
       <c r="U3">
         <v>0.07509410488470122</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>158.4548805385708</v>
+        <v>79.22744026928541</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09853959431153193</v>
+        <v>0.09839693067035173</v>
       </c>
       <c r="C4">
-        <v>29904.39191658594</v>
+        <v>29671.14830586806</v>
       </c>
       <c r="D4">
-        <v>26880.50391658594</v>
+        <v>26952.01630586806</v>
       </c>
       <c r="E4">
-        <v>-11.28800000000001</v>
+        <v>293.468</v>
       </c>
       <c r="F4">
-        <v>609.5119999999999</v>
+        <v>914.2679999999999</v>
       </c>
       <c r="G4">
         <v>3633.4</v>
@@ -1621,28 +1621,28 @@
         <v>3626.3</v>
       </c>
       <c r="M4">
-        <v>45.77075805648401</v>
+        <v>68.65613708472601</v>
       </c>
       <c r="N4">
-        <v>3580.529241943516</v>
+        <v>3557.643862915274</v>
       </c>
       <c r="O4">
-        <v>1217.379942260796</v>
+        <v>1209.598913391193</v>
       </c>
       <c r="P4">
-        <v>2363.149299682721</v>
+        <v>2348.044949524081</v>
       </c>
       <c r="Q4">
-        <v>3065.549299682721</v>
+        <v>3050.444949524081</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09953913482352436</v>
+        <v>0.09990728597281923</v>
       </c>
       <c r="T4">
-        <v>0.7004010765307576</v>
+        <v>0.7051993201597057</v>
       </c>
       <c r="U4">
         <v>0.07509410488470122</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>79.22744026928541</v>
+        <v>52.81829351285693</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09839693067035173</v>
+        <v>0.09825426702917152</v>
       </c>
       <c r="C5">
-        <v>29671.14830586806</v>
+        <v>29438.28621056941</v>
       </c>
       <c r="D5">
-        <v>26952.01630586806</v>
+        <v>27023.91021056941</v>
       </c>
       <c r="E5">
-        <v>293.468</v>
+        <v>598.2239999999999</v>
       </c>
       <c r="F5">
-        <v>914.2679999999999</v>
+        <v>1219.024</v>
       </c>
       <c r="G5">
         <v>3633.4</v>
@@ -1703,28 +1703,28 @@
         <v>3626.3</v>
       </c>
       <c r="M5">
-        <v>68.65613708472601</v>
+        <v>91.54151611296801</v>
       </c>
       <c r="N5">
-        <v>3557.643862915274</v>
+        <v>3534.758483887032</v>
       </c>
       <c r="O5">
-        <v>1209.598913391193</v>
+        <v>1201.817884521591</v>
       </c>
       <c r="P5">
-        <v>2348.044949524081</v>
+        <v>2332.940599365441</v>
       </c>
       <c r="Q5">
-        <v>3050.444949524081</v>
+        <v>3035.340599365441</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09990728597281923</v>
+        <v>0.1002831069377244</v>
       </c>
       <c r="T5">
-        <v>0.7051993201597057</v>
+        <v>0.71009752719759</v>
       </c>
       <c r="U5">
         <v>0.07509410488470122</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>52.81829351285693</v>
+        <v>39.6137201346427</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09825426702917152</v>
+        <v>0.09811160338799133</v>
       </c>
       <c r="C6">
-        <v>29438.28621056941</v>
+        <v>29205.80869190744</v>
       </c>
       <c r="D6">
-        <v>27023.91021056941</v>
+        <v>27096.18869190743</v>
       </c>
       <c r="E6">
-        <v>598.2239999999999</v>
+        <v>902.98</v>
       </c>
       <c r="F6">
-        <v>1219.024</v>
+        <v>1523.78</v>
       </c>
       <c r="G6">
         <v>3633.4</v>
@@ -1785,28 +1785,28 @@
         <v>3626.3</v>
       </c>
       <c r="M6">
-        <v>91.54151611296801</v>
+        <v>114.42689514121</v>
       </c>
       <c r="N6">
-        <v>3534.758483887032</v>
+        <v>3511.87310485879</v>
       </c>
       <c r="O6">
-        <v>1201.817884521591</v>
+        <v>1194.036855651989</v>
       </c>
       <c r="P6">
-        <v>2332.940599365441</v>
+        <v>2317.836249206801</v>
       </c>
       <c r="Q6">
-        <v>3035.340599365441</v>
+        <v>3020.236249206801</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1002831069377244</v>
+        <v>0.1006668399229434</v>
       </c>
       <c r="T6">
-        <v>0.71009752719759</v>
+        <v>0.7150988543836404</v>
       </c>
       <c r="U6">
         <v>0.07509410488470122</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>39.6137201346427</v>
+        <v>31.69097610771416</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09811160338799133</v>
+        <v>0.09796893974681112</v>
       </c>
       <c r="C7">
-        <v>29205.80869190744</v>
+        <v>28973.71884393769</v>
       </c>
       <c r="D7">
-        <v>27096.18869190743</v>
+        <v>27168.85484393769</v>
       </c>
       <c r="E7">
-        <v>902.98</v>
+        <v>1207.736</v>
       </c>
       <c r="F7">
-        <v>1523.78</v>
+        <v>1828.536</v>
       </c>
       <c r="G7">
         <v>3633.4</v>
@@ -1867,28 +1867,28 @@
         <v>3626.3</v>
       </c>
       <c r="M7">
-        <v>114.42689514121</v>
+        <v>137.3122741694521</v>
       </c>
       <c r="N7">
-        <v>3511.87310485879</v>
+        <v>3488.987725830548</v>
       </c>
       <c r="O7">
-        <v>1194.036855651989</v>
+        <v>1186.255826782387</v>
       </c>
       <c r="P7">
-        <v>2317.836249206801</v>
+        <v>2302.731899048162</v>
       </c>
       <c r="Q7">
-        <v>3020.236249206801</v>
+        <v>3005.131899048161</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1006668399229434</v>
+        <v>0.1010587374397627</v>
       </c>
       <c r="T7">
-        <v>0.7150988543836404</v>
+        <v>0.7202065927864153</v>
       </c>
       <c r="U7">
         <v>0.07509410488470122</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>31.69097610771416</v>
+        <v>26.40914675642846</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09796893974681112</v>
+        <v>0.09782627610563091</v>
       </c>
       <c r="C8">
-        <v>28973.71884393769</v>
+        <v>28742.01979399533</v>
       </c>
       <c r="D8">
-        <v>27168.85484393769</v>
+        <v>27241.91179399533</v>
       </c>
       <c r="E8">
-        <v>1207.736</v>
+        <v>1512.492</v>
       </c>
       <c r="F8">
-        <v>1828.536</v>
+        <v>2133.291999999999</v>
       </c>
       <c r="G8">
         <v>3633.4</v>
@@ -1949,28 +1949,28 @@
         <v>3626.3</v>
       </c>
       <c r="M8">
-        <v>137.312274169452</v>
+        <v>160.197653197694</v>
       </c>
       <c r="N8">
-        <v>3488.987725830548</v>
+        <v>3466.102346802306</v>
       </c>
       <c r="O8">
-        <v>1186.255826782387</v>
+        <v>1178.474797912784</v>
       </c>
       <c r="P8">
-        <v>2302.731899048162</v>
+        <v>2287.627548889522</v>
       </c>
       <c r="Q8">
-        <v>3005.131899048161</v>
+        <v>2990.027548889522</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1010587374397627</v>
+        <v>0.1014590628601696</v>
       </c>
       <c r="T8">
-        <v>0.7202065927864153</v>
+        <v>0.7254241750258088</v>
       </c>
       <c r="U8">
         <v>0.07509410488470122</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>26.40914675642847</v>
+        <v>22.63641150551012</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09782627610563091</v>
+        <v>0.0976836124644507</v>
       </c>
       <c r="C9">
-        <v>28742.01979399533</v>
+        <v>28510.7147031438</v>
       </c>
       <c r="D9">
-        <v>27241.91179399533</v>
+        <v>27315.3627031438</v>
       </c>
       <c r="E9">
-        <v>1512.492</v>
+        <v>1817.248</v>
       </c>
       <c r="F9">
-        <v>2133.292</v>
+        <v>2438.048</v>
       </c>
       <c r="G9">
         <v>3633.4</v>
@@ -2031,28 +2031,28 @@
         <v>3626.3</v>
       </c>
       <c r="M9">
-        <v>160.197653197694</v>
+        <v>183.083032225936</v>
       </c>
       <c r="N9">
-        <v>3466.102346802306</v>
+        <v>3443.216967774064</v>
       </c>
       <c r="O9">
-        <v>1178.474797912784</v>
+        <v>1170.693769043182</v>
       </c>
       <c r="P9">
-        <v>2287.627548889522</v>
+        <v>2272.523198730882</v>
       </c>
       <c r="Q9">
-        <v>2990.027548889522</v>
+        <v>2974.923198730882</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1014590628601696</v>
+        <v>0.101868091007107</v>
       </c>
       <c r="T9">
-        <v>0.725424175025809</v>
+        <v>0.7307551829660589</v>
       </c>
       <c r="U9">
         <v>0.07509410488470122</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>22.63641150551011</v>
+        <v>19.80686006732135</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0976836124644507</v>
+        <v>0.09754094882327051</v>
       </c>
       <c r="C10">
-        <v>28510.7147031438</v>
+        <v>28279.80676663071</v>
       </c>
       <c r="D10">
-        <v>27315.3627031438</v>
+        <v>27389.21076663071</v>
       </c>
       <c r="E10">
-        <v>1817.248</v>
+        <v>2122.004</v>
       </c>
       <c r="F10">
-        <v>2438.048</v>
+        <v>2742.804</v>
       </c>
       <c r="G10">
         <v>3633.4</v>
@@ -2113,28 +2113,28 @@
         <v>3626.3</v>
       </c>
       <c r="M10">
-        <v>183.083032225936</v>
+        <v>205.968411254178</v>
       </c>
       <c r="N10">
-        <v>3443.216967774064</v>
+        <v>3420.331588745822</v>
       </c>
       <c r="O10">
-        <v>1170.693769043182</v>
+        <v>1162.91274017358</v>
       </c>
       <c r="P10">
-        <v>2272.523198730882</v>
+        <v>2257.418848572242</v>
       </c>
       <c r="Q10">
-        <v>2974.923198730882</v>
+        <v>2959.818848572242</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.101868091007107</v>
+        <v>0.1022861087836475</v>
       </c>
       <c r="T10">
-        <v>0.7307551829660589</v>
+        <v>0.7362033559159848</v>
       </c>
       <c r="U10">
         <v>0.07509410488470122</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>19.80686006732135</v>
+        <v>17.60609783761898</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09754094882327051</v>
+        <v>0.09739828518209029</v>
       </c>
       <c r="C11">
-        <v>28279.80676663071</v>
+        <v>28049.29921435125</v>
       </c>
       <c r="D11">
-        <v>27389.21076663071</v>
+        <v>27463.45921435125</v>
       </c>
       <c r="E11">
-        <v>2122.004</v>
+        <v>2426.759999999999</v>
       </c>
       <c r="F11">
-        <v>2742.804</v>
+        <v>3047.559999999999</v>
       </c>
       <c r="G11">
         <v>3633.4</v>
@@ -2195,28 +2195,28 @@
         <v>3626.3</v>
       </c>
       <c r="M11">
-        <v>205.968411254178</v>
+        <v>228.85379028242</v>
       </c>
       <c r="N11">
-        <v>3420.331588745822</v>
+        <v>3397.44620971758</v>
       </c>
       <c r="O11">
-        <v>1162.91274017358</v>
+        <v>1155.131711303977</v>
       </c>
       <c r="P11">
-        <v>2257.418848572242</v>
+        <v>2242.314498413603</v>
       </c>
       <c r="Q11">
-        <v>2959.818848572242</v>
+        <v>2944.714498413603</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1022861087836475</v>
+        <v>0.1027134158441111</v>
       </c>
       <c r="T11">
-        <v>0.7362033559159848</v>
+        <v>0.741772599375909</v>
       </c>
       <c r="U11">
         <v>0.07509410488470122</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>17.60609783761898</v>
+        <v>15.84548805385708</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09739828518209029</v>
+        <v>0.09725562154091008</v>
       </c>
       <c r="C12">
-        <v>28049.29921435125</v>
+        <v>27819.19531131901</v>
       </c>
       <c r="D12">
-        <v>27463.45921435125</v>
+        <v>27538.111311319</v>
       </c>
       <c r="E12">
-        <v>2426.76</v>
+        <v>2731.516</v>
       </c>
       <c r="F12">
-        <v>3047.56</v>
+        <v>3352.316</v>
       </c>
       <c r="G12">
         <v>3633.4</v>
@@ -2277,28 +2277,28 @@
         <v>3626.3</v>
       </c>
       <c r="M12">
-        <v>228.8537902824201</v>
+        <v>251.739169310662</v>
       </c>
       <c r="N12">
-        <v>3397.44620971758</v>
+        <v>3374.560830689338</v>
       </c>
       <c r="O12">
-        <v>1155.131711303977</v>
+        <v>1147.350682434375</v>
       </c>
       <c r="P12">
-        <v>2242.314498413603</v>
+        <v>2227.210148254963</v>
       </c>
       <c r="Q12">
-        <v>2944.714498413603</v>
+        <v>2929.610148254963</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1027134158441111</v>
+        <v>0.1031503253104278</v>
       </c>
       <c r="T12">
-        <v>0.741772599375909</v>
+        <v>0.7474669943742585</v>
       </c>
       <c r="U12">
         <v>0.07509410488470122</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>15.84548805385708</v>
+        <v>14.40498913987007</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09725562154091008</v>
+        <v>0.09711295789972989</v>
       </c>
       <c r="C13">
-        <v>27819.19531131901</v>
+        <v>27589.49835814461</v>
       </c>
       <c r="D13">
-        <v>27538.111311319</v>
+        <v>27613.17035814461</v>
       </c>
       <c r="E13">
-        <v>2731.516</v>
+        <v>3036.272</v>
       </c>
       <c r="F13">
-        <v>3352.316</v>
+        <v>3657.072</v>
       </c>
       <c r="G13">
         <v>3633.4</v>
@@ -2359,28 +2359,28 @@
         <v>3626.3</v>
       </c>
       <c r="M13">
-        <v>251.739169310662</v>
+        <v>274.624548338904</v>
       </c>
       <c r="N13">
-        <v>3374.560830689338</v>
+        <v>3351.675451661096</v>
       </c>
       <c r="O13">
-        <v>1147.350682434375</v>
+        <v>1139.569653564773</v>
       </c>
       <c r="P13">
-        <v>2227.210148254963</v>
+        <v>2212.105798096323</v>
       </c>
       <c r="Q13">
-        <v>2929.610148254963</v>
+        <v>2914.505798096323</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1031503253104278</v>
+        <v>0.1035971645373427</v>
       </c>
       <c r="T13">
-        <v>0.7474669943742585</v>
+        <v>0.7532908074407524</v>
       </c>
       <c r="U13">
         <v>0.07509410488470122</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>14.40498913987007</v>
+        <v>13.20457337821423</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09711295789972989</v>
+        <v>0.09697029425854967</v>
       </c>
       <c r="C14">
-        <v>27589.49835814461</v>
+        <v>27360.21169152223</v>
       </c>
       <c r="D14">
-        <v>27613.17035814461</v>
+        <v>27688.63969152222</v>
       </c>
       <c r="E14">
-        <v>3036.272</v>
+        <v>3341.028</v>
       </c>
       <c r="F14">
-        <v>3657.072</v>
+        <v>3961.828</v>
       </c>
       <c r="G14">
         <v>3633.4</v>
@@ -2441,28 +2441,28 @@
         <v>3626.3</v>
       </c>
       <c r="M14">
-        <v>274.624548338904</v>
+        <v>297.5099273671461</v>
       </c>
       <c r="N14">
-        <v>3351.675451661096</v>
+        <v>3328.790072632854</v>
       </c>
       <c r="O14">
-        <v>1139.569653564773</v>
+        <v>1131.78862469517</v>
       </c>
       <c r="P14">
-        <v>2212.105798096323</v>
+        <v>2197.001447937683</v>
       </c>
       <c r="Q14">
-        <v>2914.505798096323</v>
+        <v>2899.401447937683</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1035971645373427</v>
+        <v>0.1040542759303935</v>
       </c>
       <c r="T14">
-        <v>0.7532908074407524</v>
+        <v>0.7592485012673955</v>
       </c>
       <c r="U14">
         <v>0.07509410488470122</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>13.20457337821423</v>
+        <v>12.18883696450544</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09697029425854967</v>
+        <v>0.09682763061736946</v>
       </c>
       <c r="C15">
-        <v>27360.21169152223</v>
+        <v>27131.33868472389</v>
       </c>
       <c r="D15">
-        <v>27688.63969152222</v>
+        <v>27764.52268472389</v>
       </c>
       <c r="E15">
-        <v>3341.028</v>
+        <v>3645.784</v>
       </c>
       <c r="F15">
-        <v>3961.828</v>
+        <v>4266.584</v>
       </c>
       <c r="G15">
         <v>3633.4</v>
@@ -2523,28 +2523,28 @@
         <v>3626.3</v>
       </c>
       <c r="M15">
-        <v>297.5099273671461</v>
+        <v>320.395306395388</v>
       </c>
       <c r="N15">
-        <v>3328.790072632854</v>
+        <v>3305.904693604612</v>
       </c>
       <c r="O15">
-        <v>1131.78862469517</v>
+        <v>1124.007595825568</v>
       </c>
       <c r="P15">
-        <v>2197.001447937683</v>
+        <v>2181.897097779044</v>
       </c>
       <c r="Q15">
-        <v>2899.401447937683</v>
+        <v>2884.297097779044</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1040542759303935</v>
+        <v>0.1045220178209571</v>
       </c>
       <c r="T15">
-        <v>0.7592485012673955</v>
+        <v>0.7653447461132628</v>
       </c>
       <c r="U15">
         <v>0.07509410488470122</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>12.18883696450544</v>
+        <v>11.31820575275506</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09682763061736946</v>
+        <v>0.09668496697618927</v>
       </c>
       <c r="C16">
-        <v>27131.33868472389</v>
+        <v>26902.88274810221</v>
       </c>
       <c r="D16">
-        <v>27764.52268472389</v>
+        <v>27840.82274810221</v>
       </c>
       <c r="E16">
-        <v>3645.784</v>
+        <v>3950.54</v>
       </c>
       <c r="F16">
-        <v>4266.584</v>
+        <v>4571.34</v>
       </c>
       <c r="G16">
         <v>3633.4</v>
@@ -2605,28 +2605,28 @@
         <v>3626.3</v>
       </c>
       <c r="M16">
-        <v>320.395306395388</v>
+        <v>343.2806854236301</v>
       </c>
       <c r="N16">
-        <v>3305.904693604612</v>
+        <v>3283.01931457637</v>
       </c>
       <c r="O16">
-        <v>1124.007595825568</v>
+        <v>1116.226566955966</v>
       </c>
       <c r="P16">
-        <v>2181.897097779044</v>
+        <v>2166.792747620404</v>
       </c>
       <c r="Q16">
-        <v>2884.297097779044</v>
+        <v>2869.192747620404</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1045220178209571</v>
+        <v>0.1050007654030633</v>
       </c>
       <c r="T16">
-        <v>0.7653447461132628</v>
+        <v>0.771584432014327</v>
       </c>
       <c r="U16">
         <v>0.07509410488470122</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.31820575275506</v>
+        <v>10.56365870257139</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09668496697618927</v>
+        <v>0.09654230333500906</v>
       </c>
       <c r="C17">
-        <v>26902.88274810221</v>
+        <v>26674.84732960127</v>
       </c>
       <c r="D17">
-        <v>27840.82274810221</v>
+        <v>27917.54332960127</v>
       </c>
       <c r="E17">
-        <v>3950.539999999999</v>
+        <v>4255.295999999999</v>
       </c>
       <c r="F17">
-        <v>4571.339999999999</v>
+        <v>4876.096</v>
       </c>
       <c r="G17">
         <v>3633.4</v>
@@ -2687,28 +2687,28 @@
         <v>3626.3</v>
       </c>
       <c r="M17">
-        <v>343.28068542363</v>
+        <v>366.166064451872</v>
       </c>
       <c r="N17">
-        <v>3283.01931457637</v>
+        <v>3260.133935548128</v>
       </c>
       <c r="O17">
-        <v>1116.226566955966</v>
+        <v>1108.445538086364</v>
       </c>
       <c r="P17">
-        <v>2166.792747620404</v>
+        <v>2151.688397461764</v>
       </c>
       <c r="Q17">
-        <v>2869.192747620404</v>
+        <v>2854.088397461764</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1050007654030633</v>
+        <v>0.1054909117371245</v>
       </c>
       <c r="T17">
-        <v>0.771584432014327</v>
+        <v>0.7779726818654166</v>
       </c>
       <c r="U17">
         <v>0.07509410488470122</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>10.56365870257139</v>
+        <v>9.903430033660676</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09654230333500906</v>
+        <v>0.09639963969382884</v>
       </c>
       <c r="C18">
-        <v>26674.84732960127</v>
+        <v>26447.23591527597</v>
       </c>
       <c r="D18">
-        <v>27917.54332960127</v>
+        <v>27994.68791527597</v>
       </c>
       <c r="E18">
-        <v>4255.295999999999</v>
+        <v>4560.052</v>
       </c>
       <c r="F18">
-        <v>4876.096</v>
+        <v>5180.852</v>
       </c>
       <c r="G18">
         <v>3633.4</v>
@@ -2769,28 +2769,28 @@
         <v>3626.3</v>
       </c>
       <c r="M18">
-        <v>366.166064451872</v>
+        <v>389.0514434801141</v>
       </c>
       <c r="N18">
-        <v>3260.133935548128</v>
+        <v>3237.248556519886</v>
       </c>
       <c r="O18">
-        <v>1108.445538086364</v>
+        <v>1100.664509216761</v>
       </c>
       <c r="P18">
-        <v>2151.688397461764</v>
+        <v>2136.584047303125</v>
       </c>
       <c r="Q18">
-        <v>2854.088397461764</v>
+        <v>2838.984047303124</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1054909117371245</v>
+        <v>0.1059928688262233</v>
       </c>
       <c r="T18">
-        <v>0.7779726818654166</v>
+        <v>0.7845148654478578</v>
       </c>
       <c r="U18">
         <v>0.07509410488470122</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>9.903430033660676</v>
+        <v>9.320875325798282</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09639963969382884</v>
+        <v>0.09625697605264864</v>
       </c>
       <c r="C19">
-        <v>26447.23591527597</v>
+        <v>26220.05202982002</v>
       </c>
       <c r="D19">
-        <v>27994.68791527597</v>
+        <v>28072.26002982002</v>
       </c>
       <c r="E19">
-        <v>4560.052</v>
+        <v>4864.808</v>
       </c>
       <c r="F19">
-        <v>5180.852</v>
+        <v>5485.608</v>
       </c>
       <c r="G19">
         <v>3633.4</v>
@@ -2851,28 +2851,28 @@
         <v>3626.3</v>
       </c>
       <c r="M19">
-        <v>389.0514434801141</v>
+        <v>411.9368225083561</v>
       </c>
       <c r="N19">
-        <v>3237.248556519886</v>
+        <v>3214.363177491644</v>
       </c>
       <c r="O19">
-        <v>1100.664509216761</v>
+        <v>1092.883480347159</v>
       </c>
       <c r="P19">
-        <v>2136.584047303125</v>
+        <v>2121.479697144485</v>
       </c>
       <c r="Q19">
-        <v>2838.984047303124</v>
+        <v>2823.879697144484</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1059928688262233</v>
+        <v>0.1065070687711538</v>
       </c>
       <c r="T19">
-        <v>0.7845148654478578</v>
+        <v>0.7912166144835291</v>
       </c>
       <c r="U19">
         <v>0.07509410488470122</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>9.320875325798282</v>
+        <v>8.803048918809488</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09625697605264866</v>
+        <v>0.09630241241146845</v>
       </c>
       <c r="C20">
-        <v>26220.05202982002</v>
+        <v>25890.54379061448</v>
       </c>
       <c r="D20">
-        <v>28072.26002982002</v>
+        <v>28047.50779061448</v>
       </c>
       <c r="E20">
-        <v>4864.807999999999</v>
+        <v>5169.563999999999</v>
       </c>
       <c r="F20">
-        <v>5485.607999999999</v>
+        <v>5790.364</v>
       </c>
       <c r="G20">
         <v>3633.4</v>
@@ -2933,45 +2933,45 @@
         <v>3626.3</v>
       </c>
       <c r="M20">
-        <v>411.936822508356</v>
+        <v>443.5077475365981</v>
       </c>
       <c r="N20">
-        <v>3214.363177491644</v>
+        <v>3182.792252463402</v>
       </c>
       <c r="O20">
-        <v>1092.883480347159</v>
+        <v>1082.149365837557</v>
       </c>
       <c r="P20">
-        <v>2121.479697144485</v>
+        <v>2100.642886625846</v>
       </c>
       <c r="Q20">
-        <v>2823.879697144484</v>
+        <v>2803.042886625845</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1065070687711538</v>
+        <v>0.1070339650110209</v>
       </c>
       <c r="T20">
-        <v>0.7912166144835291</v>
+        <v>0.7980838388040319</v>
       </c>
       <c r="U20">
-        <v>0.07509410488470122</v>
+        <v>0.07659410488470123</v>
       </c>
       <c r="V20">
         <v>0.34</v>
       </c>
       <c r="W20">
-        <v>0.0495621092239028</v>
+        <v>0.0505521092239028</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y20">
-        <v>8.803048918809488</v>
+        <v>8.176407334802555</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09630241241146845</v>
+        <v>0.09616964877028823</v>
       </c>
       <c r="C21">
-        <v>25890.54379061448</v>
+        <v>25658.23595491345</v>
       </c>
       <c r="D21">
-        <v>28047.50779061448</v>
+        <v>28119.95595491344</v>
       </c>
       <c r="E21">
-        <v>5169.563999999999</v>
+        <v>5474.32</v>
       </c>
       <c r="F21">
-        <v>5790.364</v>
+        <v>6095.12</v>
       </c>
       <c r="G21">
         <v>3633.4</v>
@@ -3015,28 +3015,28 @@
         <v>3626.3</v>
       </c>
       <c r="M21">
-        <v>443.5077475365981</v>
+        <v>466.8502605648401</v>
       </c>
       <c r="N21">
-        <v>3182.792252463402</v>
+        <v>3159.44973943516</v>
       </c>
       <c r="O21">
-        <v>1082.149365837557</v>
+        <v>1074.212911407955</v>
       </c>
       <c r="P21">
-        <v>2100.642886625846</v>
+        <v>2085.236828027206</v>
       </c>
       <c r="Q21">
-        <v>2803.042886625845</v>
+        <v>2787.636828027205</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1070339650110209</v>
+        <v>0.1075740336568846</v>
       </c>
       <c r="T21">
-        <v>0.7980838388040319</v>
+        <v>0.8051227437325473</v>
       </c>
       <c r="U21">
         <v>0.07659410488470123</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.176407334802555</v>
+        <v>7.767586968062426</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09616964877028823</v>
+        <v>0.09603688512910803</v>
       </c>
       <c r="C22">
-        <v>25658.23595491345</v>
+        <v>25426.30336320333</v>
       </c>
       <c r="D22">
-        <v>28119.95595491344</v>
+        <v>28192.77936320332</v>
       </c>
       <c r="E22">
-        <v>5474.32</v>
+        <v>5779.076</v>
       </c>
       <c r="F22">
-        <v>6095.12</v>
+        <v>6399.876</v>
       </c>
       <c r="G22">
         <v>3633.4</v>
@@ -3097,28 +3097,28 @@
         <v>3626.3</v>
       </c>
       <c r="M22">
-        <v>466.8502605648401</v>
+        <v>490.1927735930822</v>
       </c>
       <c r="N22">
-        <v>3159.44973943516</v>
+        <v>3136.107226406918</v>
       </c>
       <c r="O22">
-        <v>1074.212911407955</v>
+        <v>1066.276456978352</v>
       </c>
       <c r="P22">
-        <v>2085.236828027206</v>
+        <v>2069.830769428566</v>
       </c>
       <c r="Q22">
-        <v>2787.636828027205</v>
+        <v>2772.230769428566</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1075740336568846</v>
+        <v>0.1081277749266942</v>
       </c>
       <c r="T22">
-        <v>0.8051227437325473</v>
+        <v>0.8123398487858352</v>
       </c>
       <c r="U22">
         <v>0.07659410488470123</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>7.767586968062426</v>
+        <v>7.397701874345167</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09603688512910803</v>
+        <v>0.09590412148792783</v>
       </c>
       <c r="C23">
-        <v>25426.30336320333</v>
+        <v>25194.74893840822</v>
       </c>
       <c r="D23">
-        <v>28192.77936320332</v>
+        <v>28265.98093840822</v>
       </c>
       <c r="E23">
-        <v>5779.075999999999</v>
+        <v>6083.831999999999</v>
       </c>
       <c r="F23">
-        <v>6399.875999999999</v>
+        <v>6704.632</v>
       </c>
       <c r="G23">
         <v>3633.4</v>
@@ -3179,28 +3179,28 @@
         <v>3626.3</v>
       </c>
       <c r="M23">
-        <v>490.1927735930821</v>
+        <v>513.5352866213241</v>
       </c>
       <c r="N23">
-        <v>3136.107226406918</v>
+        <v>3112.764713378676</v>
       </c>
       <c r="O23">
-        <v>1066.276456978352</v>
+        <v>1058.34000254875</v>
       </c>
       <c r="P23">
-        <v>2069.830769428566</v>
+        <v>2054.424710829926</v>
       </c>
       <c r="Q23">
-        <v>2772.230769428566</v>
+        <v>2756.824710829926</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1081277749266942</v>
+        <v>0.1086957146906015</v>
       </c>
       <c r="T23">
-        <v>0.8123398487858351</v>
+        <v>0.8197420078148484</v>
       </c>
       <c r="U23">
         <v>0.07659410488470123</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.397701874345168</v>
+        <v>7.06144269823857</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09590412148792783</v>
+        <v>0.09577135784674762</v>
       </c>
       <c r="C24">
-        <v>25194.74893840822</v>
+        <v>24963.57563388832</v>
       </c>
       <c r="D24">
-        <v>28265.98093840822</v>
+        <v>28339.56363388832</v>
       </c>
       <c r="E24">
-        <v>6083.831999999999</v>
+        <v>6388.588</v>
       </c>
       <c r="F24">
-        <v>6704.632</v>
+        <v>7009.388</v>
       </c>
       <c r="G24">
         <v>3633.4</v>
@@ -3261,28 +3261,28 @@
         <v>3626.3</v>
       </c>
       <c r="M24">
-        <v>513.5352866213241</v>
+        <v>536.8777996495661</v>
       </c>
       <c r="N24">
-        <v>3112.764713378676</v>
+        <v>3089.422200350434</v>
       </c>
       <c r="O24">
-        <v>1058.34000254875</v>
+        <v>1050.403548119148</v>
       </c>
       <c r="P24">
-        <v>2054.424710829926</v>
+        <v>2039.018652231287</v>
       </c>
       <c r="Q24">
-        <v>2756.824710829926</v>
+        <v>2741.418652231286</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1086957146906015</v>
+        <v>0.1092784061366883</v>
       </c>
       <c r="T24">
-        <v>0.8197420078148484</v>
+        <v>0.8273364307147451</v>
       </c>
       <c r="U24">
         <v>0.07659410488470123</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.06144269823857</v>
+        <v>6.754423450489067</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09577135784674762</v>
+        <v>0.09590787420556743</v>
       </c>
       <c r="C25">
-        <v>24963.57563388832</v>
+        <v>24583.1625911724</v>
       </c>
       <c r="D25">
-        <v>28339.56363388832</v>
+        <v>28263.9065911724</v>
       </c>
       <c r="E25">
-        <v>6388.588</v>
+        <v>6693.344</v>
       </c>
       <c r="F25">
-        <v>7009.388</v>
+        <v>7314.144</v>
       </c>
       <c r="G25">
         <v>3633.4</v>
@@ -3343,45 +3343,45 @@
         <v>3626.3</v>
       </c>
       <c r="M25">
-        <v>536.8777996495661</v>
+        <v>572.6543574778082</v>
       </c>
       <c r="N25">
-        <v>3089.422200350434</v>
+        <v>3053.645642522192</v>
       </c>
       <c r="O25">
-        <v>1050.403548119148</v>
+        <v>1038.239518457546</v>
       </c>
       <c r="P25">
-        <v>2039.018652231287</v>
+        <v>2015.406124064647</v>
       </c>
       <c r="Q25">
-        <v>2741.418652231286</v>
+        <v>2717.806124064647</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1092784061366883</v>
+        <v>0.1098764315681983</v>
       </c>
       <c r="T25">
-        <v>0.8273364307147451</v>
+        <v>0.8351307068488497</v>
       </c>
       <c r="U25">
-        <v>0.07659410488470123</v>
+        <v>0.07829410488470122</v>
       </c>
       <c r="V25">
         <v>0.34</v>
       </c>
       <c r="W25">
-        <v>0.0505521092239028</v>
+        <v>0.05167410922390279</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>6.754423450489067</v>
+        <v>6.332441118533755</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09590787420556741</v>
+        <v>0.09578633056438721</v>
       </c>
       <c r="C26">
-        <v>24583.16259117241</v>
+        <v>24345.74601942384</v>
       </c>
       <c r="D26">
-        <v>28263.90659117241</v>
+        <v>28331.24601942384</v>
       </c>
       <c r="E26">
-        <v>6693.343999999999</v>
+        <v>6998.099999999999</v>
       </c>
       <c r="F26">
-        <v>7314.143999999999</v>
+        <v>7618.9</v>
       </c>
       <c r="G26">
         <v>3633.4</v>
@@ -3425,28 +3425,28 @@
         <v>3626.3</v>
       </c>
       <c r="M26">
-        <v>572.654357477808</v>
+        <v>596.51495570605</v>
       </c>
       <c r="N26">
-        <v>3053.645642522192</v>
+        <v>3029.78504429395</v>
       </c>
       <c r="O26">
-        <v>1038.239518457546</v>
+        <v>1030.126915059943</v>
       </c>
       <c r="P26">
-        <v>2015.406124064647</v>
+        <v>1999.658129234007</v>
       </c>
       <c r="Q26">
-        <v>2717.806124064647</v>
+        <v>2702.058129234007</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1098764315681983</v>
+        <v>0.1104904043445487</v>
       </c>
       <c r="T26">
-        <v>0.8351307068488495</v>
+        <v>0.8431328303465302</v>
       </c>
       <c r="U26">
         <v>0.07829410488470122</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.332441118533756</v>
+        <v>6.079143473792406</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09578633056438721</v>
+        <v>0.095664786923207</v>
       </c>
       <c r="C27">
-        <v>24345.74601942384</v>
+        <v>24108.65108956673</v>
       </c>
       <c r="D27">
-        <v>28331.24601942384</v>
+        <v>28398.90708956673</v>
       </c>
       <c r="E27">
-        <v>6998.099999999999</v>
+        <v>7302.856</v>
       </c>
       <c r="F27">
-        <v>7618.9</v>
+        <v>7923.656</v>
       </c>
       <c r="G27">
         <v>3633.4</v>
@@ -3507,28 +3507,28 @@
         <v>3626.3</v>
       </c>
       <c r="M27">
-        <v>596.51495570605</v>
+        <v>620.3755539342922</v>
       </c>
       <c r="N27">
-        <v>3029.78504429395</v>
+        <v>3005.924446065708</v>
       </c>
       <c r="O27">
-        <v>1030.126915059943</v>
+        <v>1022.014311662341</v>
       </c>
       <c r="P27">
-        <v>1999.658129234007</v>
+        <v>1983.910134403367</v>
       </c>
       <c r="Q27">
-        <v>2702.058129234007</v>
+        <v>2686.310134403367</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1104904043445487</v>
+        <v>0.1111209709797193</v>
       </c>
       <c r="T27">
-        <v>0.8431328303465302</v>
+        <v>0.8513512274522563</v>
       </c>
       <c r="U27">
         <v>0.07829410488470122</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.079143473792406</v>
+        <v>5.845330263261928</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.095664786923207</v>
+        <v>0.09554324328202679</v>
       </c>
       <c r="C28">
-        <v>24108.65108956673</v>
+        <v>23871.88011156647</v>
       </c>
       <c r="D28">
-        <v>28398.90708956673</v>
+        <v>28466.89211156647</v>
       </c>
       <c r="E28">
-        <v>7302.856</v>
+        <v>7607.612</v>
       </c>
       <c r="F28">
-        <v>7923.656</v>
+        <v>8228.412</v>
       </c>
       <c r="G28">
         <v>3633.4</v>
@@ -3589,28 +3589,28 @@
         <v>3626.3</v>
       </c>
       <c r="M28">
-        <v>620.3755539342922</v>
+        <v>644.2361521625342</v>
       </c>
       <c r="N28">
-        <v>3005.924446065708</v>
+        <v>2982.063847837466</v>
       </c>
       <c r="O28">
-        <v>1022.014311662341</v>
+        <v>1013.901708264738</v>
       </c>
       <c r="P28">
-        <v>1983.910134403367</v>
+        <v>1968.162139572727</v>
       </c>
       <c r="Q28">
-        <v>2686.310134403367</v>
+        <v>2670.562139572727</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1111209709797193</v>
+        <v>0.1117688134131138</v>
       </c>
       <c r="T28">
-        <v>0.8513512274522563</v>
+        <v>0.8597947861225227</v>
       </c>
       <c r="U28">
         <v>0.07829410488470122</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.845330263261928</v>
+        <v>5.628836549807782</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09554324328202679</v>
+        <v>0.09556953964084658</v>
       </c>
       <c r="C29">
-        <v>23871.88011156647</v>
+        <v>23552.38775343516</v>
       </c>
       <c r="D29">
-        <v>28466.89211156647</v>
+        <v>28452.15575343516</v>
       </c>
       <c r="E29">
-        <v>7607.612</v>
+        <v>7912.367999999999</v>
       </c>
       <c r="F29">
-        <v>8228.412</v>
+        <v>8533.168</v>
       </c>
       <c r="G29">
         <v>3633.4</v>
@@ -3671,45 +3671,45 @@
         <v>3626.3</v>
       </c>
       <c r="M29">
-        <v>644.2361521625342</v>
+        <v>674.9232847907762</v>
       </c>
       <c r="N29">
-        <v>2982.063847837466</v>
+        <v>2951.376715209224</v>
       </c>
       <c r="O29">
-        <v>1013.901708264738</v>
+        <v>1003.468083171136</v>
       </c>
       <c r="P29">
-        <v>1968.162139572727</v>
+        <v>1947.908632038088</v>
       </c>
       <c r="Q29">
-        <v>2670.562139572727</v>
+        <v>2650.308632038088</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1117688134131138</v>
+        <v>0.1124346514696581</v>
       </c>
       <c r="T29">
-        <v>0.8597947861225227</v>
+        <v>0.8684728880891854</v>
       </c>
       <c r="U29">
-        <v>0.07829410488470122</v>
+        <v>0.07909410488470123</v>
       </c>
       <c r="V29">
         <v>0.34</v>
       </c>
       <c r="W29">
-        <v>0.05167410922390279</v>
+        <v>0.0522021092239028</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y29">
-        <v>5.628836549807782</v>
+        <v>5.37290693878511</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09556953964084658</v>
+        <v>0.09545327599966637</v>
       </c>
       <c r="C30">
-        <v>23552.38775343516</v>
+        <v>23312.90101863055</v>
       </c>
       <c r="D30">
-        <v>28452.15575343516</v>
+        <v>28517.42501863055</v>
       </c>
       <c r="E30">
-        <v>7912.367999999999</v>
+        <v>8217.124000000002</v>
       </c>
       <c r="F30">
-        <v>8533.168</v>
+        <v>8837.924000000001</v>
       </c>
       <c r="G30">
         <v>3633.4</v>
@@ -3753,28 +3753,28 @@
         <v>3626.3</v>
       </c>
       <c r="M30">
-        <v>674.9232847907762</v>
+        <v>699.0276878190183</v>
       </c>
       <c r="N30">
-        <v>2951.376715209224</v>
+        <v>2927.272312180982</v>
       </c>
       <c r="O30">
-        <v>1003.468083171136</v>
+        <v>995.2725861415339</v>
       </c>
       <c r="P30">
-        <v>1947.908632038088</v>
+        <v>1931.999726039448</v>
       </c>
       <c r="Q30">
-        <v>2650.308632038088</v>
+        <v>2634.399726039448</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1124346514696581</v>
+        <v>0.1131192455277951</v>
       </c>
       <c r="T30">
-        <v>0.8684728880891854</v>
+        <v>0.8773954436323739</v>
       </c>
       <c r="U30">
         <v>0.07909410488470123</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.37290693878511</v>
+        <v>5.187634285723553</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09545327599966637</v>
+        <v>0.09533701235848616</v>
       </c>
       <c r="C31">
-        <v>23312.90101863055</v>
+        <v>23073.71442783652</v>
       </c>
       <c r="D31">
-        <v>28517.42501863055</v>
+        <v>28582.99442783652</v>
       </c>
       <c r="E31">
-        <v>8217.124</v>
+        <v>8521.879999999999</v>
       </c>
       <c r="F31">
-        <v>8837.923999999999</v>
+        <v>9142.679999999998</v>
       </c>
       <c r="G31">
         <v>3633.4</v>
@@ -3835,28 +3835,28 @@
         <v>3626.3</v>
       </c>
       <c r="M31">
-        <v>699.0276878190182</v>
+        <v>723.1320908472601</v>
       </c>
       <c r="N31">
-        <v>2927.272312180982</v>
+        <v>2903.16790915274</v>
       </c>
       <c r="O31">
-        <v>995.272586141534</v>
+        <v>987.0770891119317</v>
       </c>
       <c r="P31">
-        <v>1931.999726039448</v>
+        <v>1916.090820040808</v>
       </c>
       <c r="Q31">
-        <v>2634.399726039448</v>
+        <v>2618.490820040808</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1131192455277951</v>
+        <v>0.1138233994161648</v>
       </c>
       <c r="T31">
-        <v>0.8773954436323739</v>
+        <v>0.8865729293339393</v>
       </c>
       <c r="U31">
         <v>0.07909410488470123</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.187634285723555</v>
+        <v>5.014713142866103</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09533701235848616</v>
+        <v>0.09522074871730596</v>
       </c>
       <c r="C32">
-        <v>23073.71442783652</v>
+        <v>22834.83005616538</v>
       </c>
       <c r="D32">
-        <v>28582.99442783652</v>
+        <v>28648.86605616538</v>
       </c>
       <c r="E32">
-        <v>8521.879999999999</v>
+        <v>8826.636</v>
       </c>
       <c r="F32">
-        <v>9142.679999999998</v>
+        <v>9447.436</v>
       </c>
       <c r="G32">
         <v>3633.4</v>
@@ -3917,28 +3917,28 @@
         <v>3626.3</v>
       </c>
       <c r="M32">
-        <v>723.1320908472601</v>
+        <v>747.2364938755022</v>
       </c>
       <c r="N32">
-        <v>2903.16790915274</v>
+        <v>2879.063506124498</v>
       </c>
       <c r="O32">
-        <v>987.0770891119317</v>
+        <v>978.8815920823293</v>
       </c>
       <c r="P32">
-        <v>1916.090820040808</v>
+        <v>1900.181914042169</v>
       </c>
       <c r="Q32">
-        <v>2618.490820040808</v>
+        <v>2602.581914042168</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1138233994161648</v>
+        <v>0.1145479635621683</v>
       </c>
       <c r="T32">
-        <v>0.8865729293339393</v>
+        <v>0.8960164291138109</v>
       </c>
       <c r="U32">
         <v>0.07909410488470123</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.014713142866103</v>
+        <v>4.852948202773648</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09522074871730596</v>
+        <v>0.09510448507612576</v>
       </c>
       <c r="C33">
-        <v>22834.83005616538</v>
+        <v>22596.24999790267</v>
       </c>
       <c r="D33">
-        <v>28648.86605616538</v>
+        <v>28715.04199790266</v>
       </c>
       <c r="E33">
-        <v>8826.636</v>
+        <v>9131.392</v>
       </c>
       <c r="F33">
-        <v>9447.436</v>
+        <v>9752.191999999999</v>
       </c>
       <c r="G33">
         <v>3633.4</v>
@@ -3999,28 +3999,28 @@
         <v>3626.3</v>
       </c>
       <c r="M33">
-        <v>747.2364938755022</v>
+        <v>771.3408969037441</v>
       </c>
       <c r="N33">
-        <v>2879.063506124498</v>
+        <v>2854.959103096256</v>
       </c>
       <c r="O33">
-        <v>978.8815920823293</v>
+        <v>970.6860950527272</v>
       </c>
       <c r="P33">
-        <v>1900.181914042169</v>
+        <v>1884.273008043529</v>
       </c>
       <c r="Q33">
-        <v>2602.581914042168</v>
+        <v>2586.673008043529</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1145479635621683</v>
+        <v>0.1152938384183483</v>
       </c>
       <c r="T33">
-        <v>0.8960164291138109</v>
+        <v>0.9057376788872079</v>
       </c>
       <c r="U33">
         <v>0.07909410488470123</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.852948202773648</v>
+        <v>4.701293571436972</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09510448507612576</v>
+        <v>0.09498822143494554</v>
       </c>
       <c r="C34">
-        <v>22596.24999790267</v>
+        <v>22357.97636672903</v>
       </c>
       <c r="D34">
-        <v>28715.04199790266</v>
+        <v>28781.52436672903</v>
       </c>
       <c r="E34">
-        <v>9131.392</v>
+        <v>9436.148000000001</v>
       </c>
       <c r="F34">
-        <v>9752.191999999999</v>
+        <v>10056.948</v>
       </c>
       <c r="G34">
         <v>3633.4</v>
@@ -4081,28 +4081,28 @@
         <v>3626.3</v>
       </c>
       <c r="M34">
-        <v>771.3408969037441</v>
+        <v>795.4452999319863</v>
       </c>
       <c r="N34">
-        <v>2854.959103096256</v>
+        <v>2830.854700068014</v>
       </c>
       <c r="O34">
-        <v>970.6860950527272</v>
+        <v>962.4905980231247</v>
       </c>
       <c r="P34">
-        <v>1884.273008043529</v>
+        <v>1868.364102044889</v>
       </c>
       <c r="Q34">
-        <v>2586.673008043529</v>
+        <v>2570.764102044889</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1152938384183483</v>
+        <v>0.1160619781956084</v>
       </c>
       <c r="T34">
-        <v>0.9057376788872079</v>
+        <v>0.915749115221005</v>
       </c>
       <c r="U34">
         <v>0.07909410488470123</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.701293571436972</v>
+        <v>4.558830129878275</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09498822143494554</v>
+        <v>0.09487195779376534</v>
       </c>
       <c r="C35">
-        <v>22357.97636672903</v>
+        <v>22120.0112959453</v>
       </c>
       <c r="D35">
-        <v>28781.52436672903</v>
+        <v>28848.3152959453</v>
       </c>
       <c r="E35">
-        <v>9436.148000000001</v>
+        <v>9740.904</v>
       </c>
       <c r="F35">
-        <v>10056.948</v>
+        <v>10361.704</v>
       </c>
       <c r="G35">
         <v>3633.4</v>
@@ -4163,28 +4163,28 @@
         <v>3626.3</v>
       </c>
       <c r="M35">
-        <v>795.4452999319863</v>
+        <v>819.5497029602283</v>
       </c>
       <c r="N35">
-        <v>2830.854700068014</v>
+        <v>2806.750297039772</v>
       </c>
       <c r="O35">
-        <v>962.4905980231247</v>
+        <v>954.2951009935225</v>
       </c>
       <c r="P35">
-        <v>1868.364102044889</v>
+        <v>1852.455196046249</v>
       </c>
       <c r="Q35">
-        <v>2570.764102044889</v>
+        <v>2554.855196046249</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1160619781956084</v>
+        <v>0.1168533949358158</v>
       </c>
       <c r="T35">
-        <v>0.915749115221005</v>
+        <v>0.926063928413402</v>
       </c>
       <c r="U35">
         <v>0.07909410488470123</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.558830129878275</v>
+        <v>4.424746890764208</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09487195779376534</v>
+        <v>0.09475569415258514</v>
       </c>
       <c r="C36">
-        <v>22120.0112959453</v>
+        <v>21882.35693870067</v>
       </c>
       <c r="D36">
-        <v>28848.3152959453</v>
+        <v>28915.41693870067</v>
       </c>
       <c r="E36">
-        <v>9740.904</v>
+        <v>10045.66</v>
       </c>
       <c r="F36">
-        <v>10361.704</v>
+        <v>10666.46</v>
       </c>
       <c r="G36">
         <v>3633.4</v>
@@ -4245,28 +4245,28 @@
         <v>3626.3</v>
       </c>
       <c r="M36">
-        <v>819.5497029602283</v>
+        <v>843.6541059884703</v>
       </c>
       <c r="N36">
-        <v>2806.750297039772</v>
+        <v>2782.64589401153</v>
       </c>
       <c r="O36">
-        <v>954.2951009935225</v>
+        <v>946.0996039639202</v>
       </c>
       <c r="P36">
-        <v>1852.455196046249</v>
+        <v>1836.54629004761</v>
       </c>
       <c r="Q36">
-        <v>2554.855196046249</v>
+        <v>2538.946290047609</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1168533949358158</v>
+        <v>0.1176691629603372</v>
       </c>
       <c r="T36">
-        <v>0.926063928413402</v>
+        <v>0.9366961204732573</v>
       </c>
       <c r="U36">
         <v>0.07909410488470123</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.424746890764208</v>
+        <v>4.298325551028087</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09475569415258514</v>
+        <v>0.09487703051140493</v>
       </c>
       <c r="C37">
-        <v>21882.35693870067</v>
+        <v>21507.57866321506</v>
       </c>
       <c r="D37">
-        <v>28915.41693870067</v>
+        <v>28845.39466321506</v>
       </c>
       <c r="E37">
-        <v>10045.66</v>
+        <v>10350.416</v>
       </c>
       <c r="F37">
-        <v>10666.46</v>
+        <v>10971.216</v>
       </c>
       <c r="G37">
         <v>3633.4</v>
@@ -4327,45 +4327,45 @@
         <v>3626.3</v>
       </c>
       <c r="M37">
-        <v>843.6541059884703</v>
+        <v>878.7297250167123</v>
       </c>
       <c r="N37">
-        <v>2782.64589401153</v>
+        <v>2747.570274983288</v>
       </c>
       <c r="O37">
-        <v>946.0996039639202</v>
+        <v>934.173893494318</v>
       </c>
       <c r="P37">
-        <v>1836.54629004761</v>
+        <v>1813.39638148897</v>
       </c>
       <c r="Q37">
-        <v>2538.946290047609</v>
+        <v>2515.79638148897</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1176691629603372</v>
+        <v>0.1185104237356249</v>
       </c>
       <c r="T37">
-        <v>0.9366961204732573</v>
+        <v>0.9476605685349833</v>
       </c>
       <c r="U37">
-        <v>0.07909410488470123</v>
+        <v>0.08009410488470123</v>
       </c>
       <c r="V37">
         <v>0.34</v>
       </c>
       <c r="W37">
-        <v>0.0522021092239028</v>
+        <v>0.0528621092239028</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y37">
-        <v>4.298325551028087</v>
+        <v>4.126752398106293</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09487703051140495</v>
+        <v>0.09476736687022473</v>
       </c>
       <c r="C38">
-        <v>21507.57866321506</v>
+        <v>21266.09392783671</v>
       </c>
       <c r="D38">
-        <v>28845.39466321505</v>
+        <v>28908.6659278367</v>
       </c>
       <c r="E38">
-        <v>10350.416</v>
+        <v>10655.172</v>
       </c>
       <c r="F38">
-        <v>10971.216</v>
+        <v>11275.972</v>
       </c>
       <c r="G38">
         <v>3633.4</v>
@@ -4409,28 +4409,28 @@
         <v>3626.3</v>
       </c>
       <c r="M38">
-        <v>878.7297250167121</v>
+        <v>903.1388840449542</v>
       </c>
       <c r="N38">
-        <v>2747.570274983288</v>
+        <v>2723.161115955046</v>
       </c>
       <c r="O38">
-        <v>934.173893494318</v>
+        <v>925.8747794247156</v>
       </c>
       <c r="P38">
-        <v>1813.39638148897</v>
+        <v>1797.28633653033</v>
       </c>
       <c r="Q38">
-        <v>2515.79638148897</v>
+        <v>2499.68633653033</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1185104237356249</v>
+        <v>0.1193783912021916</v>
       </c>
       <c r="T38">
-        <v>0.9476605685349831</v>
+        <v>0.9589730943129543</v>
       </c>
       <c r="U38">
         <v>0.08009410488470123</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.126752398106293</v>
+        <v>4.015218549508825</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09476736687022473</v>
+        <v>0.09465770322904453</v>
       </c>
       <c r="C39">
-        <v>21266.09392783671</v>
+        <v>21024.88736880214</v>
       </c>
       <c r="D39">
-        <v>28908.6659278367</v>
+        <v>28972.21536880214</v>
       </c>
       <c r="E39">
-        <v>10655.172</v>
+        <v>10959.928</v>
       </c>
       <c r="F39">
-        <v>11275.972</v>
+        <v>11580.728</v>
       </c>
       <c r="G39">
         <v>3633.4</v>
@@ -4491,28 +4491,28 @@
         <v>3626.3</v>
       </c>
       <c r="M39">
-        <v>903.1388840449542</v>
+        <v>927.5480430731963</v>
       </c>
       <c r="N39">
-        <v>2723.161115955046</v>
+        <v>2698.751956926804</v>
       </c>
       <c r="O39">
-        <v>925.8747794247156</v>
+        <v>917.5756653551134</v>
       </c>
       <c r="P39">
-        <v>1797.28633653033</v>
+        <v>1781.17629157169</v>
       </c>
       <c r="Q39">
-        <v>2499.68633653033</v>
+        <v>2483.57629157169</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1193783912021916</v>
+        <v>0.1202743576192927</v>
       </c>
       <c r="T39">
-        <v>0.9589730943129543</v>
+        <v>0.9706505402773116</v>
       </c>
       <c r="U39">
         <v>0.08009410488470123</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.015218549508825</v>
+        <v>3.909554903469119</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09465770322904453</v>
+        <v>0.09454803958786433</v>
       </c>
       <c r="C40">
-        <v>21024.88736880214</v>
+        <v>20783.9608246844</v>
       </c>
       <c r="D40">
-        <v>28972.21536880214</v>
+        <v>29036.0448246844</v>
       </c>
       <c r="E40">
-        <v>10959.928</v>
+        <v>11264.684</v>
       </c>
       <c r="F40">
-        <v>11580.728</v>
+        <v>11885.484</v>
       </c>
       <c r="G40">
         <v>3633.4</v>
@@ -4573,28 +4573,28 @@
         <v>3626.3</v>
       </c>
       <c r="M40">
-        <v>927.5480430731963</v>
+        <v>951.9572021014383</v>
       </c>
       <c r="N40">
-        <v>2698.751956926804</v>
+        <v>2674.342797898562</v>
       </c>
       <c r="O40">
-        <v>917.5756653551134</v>
+        <v>909.2765512855111</v>
       </c>
       <c r="P40">
-        <v>1781.17629157169</v>
+        <v>1765.066246613051</v>
       </c>
       <c r="Q40">
-        <v>2483.57629157169</v>
+        <v>2467.46624661305</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1202743576192927</v>
+        <v>0.1211996999844955</v>
       </c>
       <c r="T40">
-        <v>0.9706505402773116</v>
+        <v>0.9827108533224674</v>
       </c>
       <c r="U40">
         <v>0.08009410488470123</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.909554903469119</v>
+        <v>3.80930990594427</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09454803958786433</v>
+        <v>0.09443837594668412</v>
       </c>
       <c r="C41">
-        <v>20783.9608246844</v>
+        <v>20543.31615029475</v>
       </c>
       <c r="D41">
-        <v>29036.0448246844</v>
+        <v>29100.15615029474</v>
       </c>
       <c r="E41">
-        <v>11264.684</v>
+        <v>11569.44</v>
       </c>
       <c r="F41">
-        <v>11885.484</v>
+        <v>12190.24</v>
       </c>
       <c r="G41">
         <v>3633.4</v>
@@ -4655,28 +4655,28 @@
         <v>3626.3</v>
       </c>
       <c r="M41">
-        <v>951.9572021014383</v>
+        <v>976.3663611296803</v>
       </c>
       <c r="N41">
-        <v>2674.342797898562</v>
+        <v>2649.93363887032</v>
       </c>
       <c r="O41">
-        <v>909.2765512855111</v>
+        <v>900.9774372159088</v>
       </c>
       <c r="P41">
-        <v>1765.066246613051</v>
+        <v>1748.956201654411</v>
       </c>
       <c r="Q41">
-        <v>2467.46624661305</v>
+        <v>2451.356201654411</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1211996999844955</v>
+        <v>0.122155887095205</v>
       </c>
       <c r="T41">
-        <v>0.9827108533224674</v>
+        <v>0.9951731768024619</v>
       </c>
       <c r="U41">
         <v>0.08009410488470123</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.80930990594427</v>
+        <v>3.714077158295663</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09443837594668412</v>
+        <v>0.09432871230550391</v>
       </c>
       <c r="C42">
-        <v>20543.31615029475</v>
+        <v>20302.9552168623</v>
       </c>
       <c r="D42">
-        <v>29100.15615029474</v>
+        <v>29164.5512168623</v>
       </c>
       <c r="E42">
-        <v>11569.44</v>
+        <v>11874.196</v>
       </c>
       <c r="F42">
-        <v>12190.24</v>
+        <v>12494.996</v>
       </c>
       <c r="G42">
         <v>3633.4</v>
@@ -4737,28 +4737,28 @@
         <v>3626.3</v>
       </c>
       <c r="M42">
-        <v>976.3663611296803</v>
+        <v>1000.775520157922</v>
       </c>
       <c r="N42">
-        <v>2649.93363887032</v>
+        <v>2625.524479842078</v>
       </c>
       <c r="O42">
-        <v>900.9774372159088</v>
+        <v>892.6783231463064</v>
       </c>
       <c r="P42">
-        <v>1748.956201654411</v>
+        <v>1732.846156695771</v>
       </c>
       <c r="Q42">
-        <v>2451.356201654411</v>
+        <v>2435.246156695771</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.122155887095205</v>
+        <v>0.1231444873283115</v>
       </c>
       <c r="T42">
-        <v>0.9951731768024619</v>
+        <v>1.008057951925846</v>
       </c>
       <c r="U42">
         <v>0.08009410488470123</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.714077158295663</v>
+        <v>3.623489910532354</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09432871230550391</v>
+        <v>0.09421904866432371</v>
       </c>
       <c r="C43">
-        <v>20302.9552168623</v>
+        <v>20062.8799122161</v>
       </c>
       <c r="D43">
-        <v>29164.5512168623</v>
+        <v>29229.2319122161</v>
       </c>
       <c r="E43">
-        <v>11874.196</v>
+        <v>12178.952</v>
       </c>
       <c r="F43">
-        <v>12494.996</v>
+        <v>12799.752</v>
       </c>
       <c r="G43">
         <v>3633.4</v>
@@ -4819,28 +4819,28 @@
         <v>3626.3</v>
       </c>
       <c r="M43">
-        <v>1000.775520157922</v>
+        <v>1025.184679186164</v>
       </c>
       <c r="N43">
-        <v>2625.524479842078</v>
+        <v>2601.115320813836</v>
       </c>
       <c r="O43">
-        <v>892.6783231463064</v>
+        <v>884.3792090767042</v>
       </c>
       <c r="P43">
-        <v>1732.846156695771</v>
+        <v>1716.736111737132</v>
       </c>
       <c r="Q43">
-        <v>2435.246156695771</v>
+        <v>2419.136111737131</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1231444873283115</v>
+        <v>0.1241671772246285</v>
       </c>
       <c r="T43">
-        <v>1.008057951925846</v>
+        <v>1.021387029639692</v>
       </c>
       <c r="U43">
         <v>0.08009410488470123</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.623489910532354</v>
+        <v>3.537216341233965</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09421904866432371</v>
+        <v>0.0941093850231435</v>
       </c>
       <c r="C44">
-        <v>20062.8799122161</v>
+        <v>19823.09214096964</v>
       </c>
       <c r="D44">
-        <v>29229.2319122161</v>
+        <v>29294.20014096964</v>
       </c>
       <c r="E44">
-        <v>12178.952</v>
+        <v>12483.708</v>
       </c>
       <c r="F44">
-        <v>12799.752</v>
+        <v>13104.508</v>
       </c>
       <c r="G44">
         <v>3633.4</v>
@@ -4901,28 +4901,28 @@
         <v>3626.3</v>
       </c>
       <c r="M44">
-        <v>1025.184679186164</v>
+        <v>1049.593838214406</v>
       </c>
       <c r="N44">
-        <v>2601.115320813836</v>
+        <v>2576.706161785594</v>
       </c>
       <c r="O44">
-        <v>884.3792090767042</v>
+        <v>876.0800950071019</v>
       </c>
       <c r="P44">
-        <v>1716.736111737132</v>
+        <v>1700.626066778492</v>
       </c>
       <c r="Q44">
-        <v>2419.136111737131</v>
+        <v>2403.026066778491</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1241671772246285</v>
+        <v>0.1252257509769567</v>
       </c>
       <c r="T44">
-        <v>1.021387029639691</v>
+        <v>1.035183794290865</v>
       </c>
       <c r="U44">
         <v>0.08009410488470123</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.537216341233965</v>
+        <v>3.454955496088989</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.0941093850231435</v>
+        <v>0.09399972138196329</v>
       </c>
       <c r="C45">
-        <v>19823.09214096964</v>
+        <v>19583.59382470777</v>
       </c>
       <c r="D45">
-        <v>29294.20014096964</v>
+        <v>29359.45782470777</v>
       </c>
       <c r="E45">
-        <v>12483.708</v>
+        <v>12788.464</v>
       </c>
       <c r="F45">
-        <v>13104.508</v>
+        <v>13409.264</v>
       </c>
       <c r="G45">
         <v>3633.4</v>
@@ -4983,28 +4983,28 @@
         <v>3626.3</v>
       </c>
       <c r="M45">
-        <v>1049.593838214406</v>
+        <v>1074.002997242648</v>
       </c>
       <c r="N45">
-        <v>2576.706161785594</v>
+        <v>2552.297002757352</v>
       </c>
       <c r="O45">
-        <v>876.0800950071019</v>
+        <v>867.7809809374997</v>
       </c>
       <c r="P45">
-        <v>1700.626066778492</v>
+        <v>1684.516021819852</v>
       </c>
       <c r="Q45">
-        <v>2403.026066778491</v>
+        <v>2386.916021819852</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1252257509769567</v>
+        <v>0.1263221309347251</v>
       </c>
       <c r="T45">
-        <v>1.035183794290865</v>
+        <v>1.049473300536723</v>
       </c>
       <c r="U45">
         <v>0.08009410488470123</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.454955496088989</v>
+        <v>3.376433780268785</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09399972138196329</v>
+        <v>0.09389005774078309</v>
       </c>
       <c r="C46">
-        <v>19583.59382470777</v>
+        <v>19344.38690217612</v>
       </c>
       <c r="D46">
-        <v>29359.45782470777</v>
+        <v>29425.00690217613</v>
       </c>
       <c r="E46">
-        <v>12788.464</v>
+        <v>13093.22</v>
       </c>
       <c r="F46">
-        <v>13409.264</v>
+        <v>13714.02</v>
       </c>
       <c r="G46">
         <v>3633.4</v>
@@ -5065,28 +5065,28 @@
         <v>3626.3</v>
       </c>
       <c r="M46">
-        <v>1074.002997242648</v>
+        <v>1098.41215627089</v>
       </c>
       <c r="N46">
-        <v>2552.297002757352</v>
+        <v>2527.88784372911</v>
       </c>
       <c r="O46">
-        <v>867.7809809374997</v>
+        <v>859.4818668678973</v>
       </c>
       <c r="P46">
-        <v>1684.516021819852</v>
+        <v>1668.405976861212</v>
       </c>
       <c r="Q46">
-        <v>2386.916021819852</v>
+        <v>2370.805976861212</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1263221309347251</v>
+        <v>0.1274583792545942</v>
       </c>
       <c r="T46">
-        <v>1.049473300536723</v>
+        <v>1.064282425191522</v>
       </c>
       <c r="U46">
         <v>0.08009410488470123</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.376433780268785</v>
+        <v>3.301401918485034</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09389005774078309</v>
+        <v>0.09378039409960287</v>
       </c>
       <c r="C47">
-        <v>19344.38690217612</v>
+        <v>19105.47332947324</v>
       </c>
       <c r="D47">
-        <v>29425.00690217613</v>
+        <v>29490.84932947324</v>
       </c>
       <c r="E47">
-        <v>13093.22</v>
+        <v>13397.976</v>
       </c>
       <c r="F47">
-        <v>13714.02</v>
+        <v>14018.776</v>
       </c>
       <c r="G47">
         <v>3633.4</v>
@@ -5147,28 +5147,28 @@
         <v>3626.3</v>
       </c>
       <c r="M47">
-        <v>1098.41215627089</v>
+        <v>1122.821315299132</v>
       </c>
       <c r="N47">
-        <v>2527.88784372911</v>
+        <v>2503.478684700868</v>
       </c>
       <c r="O47">
-        <v>859.4818668678973</v>
+        <v>851.1827527982953</v>
       </c>
       <c r="P47">
-        <v>1668.405976861212</v>
+        <v>1652.295931902573</v>
       </c>
       <c r="Q47">
-        <v>2370.805976861212</v>
+        <v>2354.695931902573</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1274583792545942</v>
+        <v>0.1286367108455696</v>
       </c>
       <c r="T47">
-        <v>1.064282425191522</v>
+        <v>1.079640035944646</v>
       </c>
       <c r="U47">
         <v>0.08009410488470123</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.301401918485034</v>
+        <v>3.229632311561446</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09378039409960287</v>
+        <v>0.09367073045842268</v>
       </c>
       <c r="C48">
-        <v>19105.47332947324</v>
+        <v>18866.85508024495</v>
       </c>
       <c r="D48">
-        <v>29490.84932947324</v>
+        <v>29556.98708024495</v>
       </c>
       <c r="E48">
-        <v>13397.976</v>
+        <v>13702.732</v>
       </c>
       <c r="F48">
-        <v>14018.776</v>
+        <v>14323.532</v>
       </c>
       <c r="G48">
         <v>3633.4</v>
@@ -5229,28 +5229,28 @@
         <v>3626.3</v>
       </c>
       <c r="M48">
-        <v>1122.821315299132</v>
+        <v>1147.230474327374</v>
       </c>
       <c r="N48">
-        <v>2503.478684700868</v>
+        <v>2479.069525672626</v>
       </c>
       <c r="O48">
-        <v>851.1827527982953</v>
+        <v>842.8836387286929</v>
       </c>
       <c r="P48">
-        <v>1652.295931902573</v>
+        <v>1636.185886943933</v>
       </c>
       <c r="Q48">
-        <v>2354.695931902573</v>
+        <v>2338.585886943933</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1286367108455696</v>
+        <v>0.1298595077796007</v>
       </c>
       <c r="T48">
-        <v>1.079640035944646</v>
+        <v>1.095577179179021</v>
       </c>
       <c r="U48">
         <v>0.08009410488470123</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.229632311561446</v>
+        <v>3.160916730464394</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09367073045842268</v>
+        <v>0.09356106681724247</v>
       </c>
       <c r="C49">
-        <v>18866.85508024495</v>
+        <v>18628.53414588179</v>
       </c>
       <c r="D49">
-        <v>29556.98708024495</v>
+        <v>29623.42214588179</v>
       </c>
       <c r="E49">
-        <v>13702.732</v>
+        <v>14007.488</v>
       </c>
       <c r="F49">
-        <v>14323.532</v>
+        <v>14628.288</v>
       </c>
       <c r="G49">
         <v>3633.4</v>
@@ -5311,28 +5311,28 @@
         <v>3626.3</v>
       </c>
       <c r="M49">
-        <v>1147.230474327374</v>
+        <v>1171.639633355616</v>
       </c>
       <c r="N49">
-        <v>2479.069525672626</v>
+        <v>2454.660366644384</v>
       </c>
       <c r="O49">
-        <v>842.8836387286929</v>
+        <v>834.5845246590906</v>
       </c>
       <c r="P49">
-        <v>1636.185886943933</v>
+        <v>1620.075841985293</v>
       </c>
       <c r="Q49">
-        <v>2338.585886943933</v>
+        <v>2322.475841985293</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1298595077796007</v>
+        <v>0.1311293353649406</v>
       </c>
       <c r="T49">
-        <v>1.095577179179021</v>
+        <v>1.112127289460871</v>
       </c>
       <c r="U49">
         <v>0.08009410488470123</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.160916730464394</v>
+        <v>3.095064298579719</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09356106681724247</v>
+        <v>0.09345140317606225</v>
       </c>
       <c r="C50">
-        <v>18628.53414588179</v>
+        <v>18390.51253571874</v>
       </c>
       <c r="D50">
-        <v>29623.42214588179</v>
+        <v>29690.15653571875</v>
       </c>
       <c r="E50">
-        <v>14007.488</v>
+        <v>14312.244</v>
       </c>
       <c r="F50">
-        <v>14628.288</v>
+        <v>14933.044</v>
       </c>
       <c r="G50">
         <v>3633.4</v>
@@ -5393,28 +5393,28 @@
         <v>3626.3</v>
       </c>
       <c r="M50">
-        <v>1171.639633355616</v>
+        <v>1196.048792383858</v>
       </c>
       <c r="N50">
-        <v>2454.660366644384</v>
+        <v>2430.251207616142</v>
       </c>
       <c r="O50">
-        <v>834.5845246590906</v>
+        <v>826.2854105894884</v>
       </c>
       <c r="P50">
-        <v>1620.075841985293</v>
+        <v>1603.965797026653</v>
       </c>
       <c r="Q50">
-        <v>2322.475841985293</v>
+        <v>2306.365797026653</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1311293353649406</v>
+        <v>0.13244896011049</v>
       </c>
       <c r="T50">
-        <v>1.112127289460871</v>
+        <v>1.129326423675343</v>
       </c>
       <c r="U50">
         <v>0.08009410488470123</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.095064298579719</v>
+        <v>3.031899721057684</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09345140317606225</v>
+        <v>0.09416673953488205</v>
       </c>
       <c r="C51">
-        <v>18390.51253571874</v>
+        <v>17655.78552092092</v>
       </c>
       <c r="D51">
-        <v>29690.15653571875</v>
+        <v>29260.18552092092</v>
       </c>
       <c r="E51">
-        <v>14312.244</v>
+        <v>14617</v>
       </c>
       <c r="F51">
-        <v>14933.044</v>
+        <v>15237.8</v>
       </c>
       <c r="G51">
         <v>3633.4</v>
@@ -5475,45 +5475,45 @@
         <v>3626.3</v>
       </c>
       <c r="M51">
-        <v>1196.048792383858</v>
+        <v>1258.5524514121</v>
       </c>
       <c r="N51">
-        <v>2430.251207616142</v>
+        <v>2367.7475485879</v>
       </c>
       <c r="O51">
-        <v>826.2854105894884</v>
+        <v>805.0341665198861</v>
       </c>
       <c r="P51">
-        <v>1603.965797026653</v>
+        <v>1562.713382068014</v>
       </c>
       <c r="Q51">
-        <v>2306.365797026653</v>
+        <v>2265.113382068013</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.13244896011049</v>
+        <v>0.1338213698458613</v>
       </c>
       <c r="T51">
-        <v>1.129326423675343</v>
+        <v>1.147213523258394</v>
       </c>
       <c r="U51">
-        <v>0.08009410488470123</v>
+        <v>0.08259410488470123</v>
       </c>
       <c r="V51">
         <v>0.34</v>
       </c>
       <c r="W51">
-        <v>0.0528621092239028</v>
+        <v>0.0545121092239028</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y51">
-        <v>3.031899721057684</v>
+        <v>2.881326078965782</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09416673953488205</v>
+        <v>0.09407357589370184</v>
       </c>
       <c r="C52">
-        <v>17655.78552092092</v>
+        <v>17406.32120462709</v>
       </c>
       <c r="D52">
-        <v>29260.18552092092</v>
+        <v>29315.47720462708</v>
       </c>
       <c r="E52">
-        <v>14617</v>
+        <v>14921.756</v>
       </c>
       <c r="F52">
-        <v>15237.8</v>
+        <v>15542.556</v>
       </c>
       <c r="G52">
         <v>3633.4</v>
@@ -5557,28 +5557,28 @@
         <v>3626.3</v>
       </c>
       <c r="M52">
-        <v>1258.5524514121</v>
+        <v>1283.723500440342</v>
       </c>
       <c r="N52">
-        <v>2367.7475485879</v>
+        <v>2342.576499559658</v>
       </c>
       <c r="O52">
-        <v>805.0341665198861</v>
+        <v>796.4760098502837</v>
       </c>
       <c r="P52">
-        <v>1562.713382068014</v>
+        <v>1546.100489709374</v>
       </c>
       <c r="Q52">
-        <v>2265.113382068013</v>
+        <v>2248.500489709374</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1338213698458613</v>
+        <v>0.1352497963051253</v>
       </c>
       <c r="T52">
-        <v>1.147213523258394</v>
+        <v>1.165830708538712</v>
       </c>
       <c r="U52">
         <v>0.08259410488470123</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.881326078965782</v>
+        <v>2.824829489182139</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09407357589370184</v>
+        <v>0.09398041225252164</v>
       </c>
       <c r="C53">
-        <v>17406.32120462709</v>
+        <v>17157.06624847022</v>
       </c>
       <c r="D53">
-        <v>29315.47720462708</v>
+        <v>29370.97824847022</v>
       </c>
       <c r="E53">
-        <v>14921.756</v>
+        <v>15226.512</v>
       </c>
       <c r="F53">
-        <v>15542.556</v>
+        <v>15847.312</v>
       </c>
       <c r="G53">
         <v>3633.4</v>
@@ -5639,28 +5639,28 @@
         <v>3626.3</v>
       </c>
       <c r="M53">
-        <v>1283.723500440342</v>
+        <v>1308.894549468585</v>
       </c>
       <c r="N53">
-        <v>2342.576499559658</v>
+        <v>2317.405450531416</v>
       </c>
       <c r="O53">
-        <v>796.4760098502837</v>
+        <v>787.9178531806814</v>
       </c>
       <c r="P53">
-        <v>1546.100489709374</v>
+        <v>1529.487597350734</v>
       </c>
       <c r="Q53">
-        <v>2248.500489709374</v>
+        <v>2231.887597350734</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1352497963051253</v>
+        <v>0.1367377405335254</v>
       </c>
       <c r="T53">
-        <v>1.165830708538712</v>
+        <v>1.185223609872376</v>
       </c>
       <c r="U53">
         <v>0.08259410488470123</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.824829489182139</v>
+        <v>2.770505845159406</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09398041225252164</v>
+        <v>0.09388724861134143</v>
       </c>
       <c r="C54">
-        <v>17157.06624847022</v>
+        <v>16908.02184380874</v>
       </c>
       <c r="D54">
-        <v>29370.97824847022</v>
+        <v>29426.68984380874</v>
       </c>
       <c r="E54">
-        <v>15226.512</v>
+        <v>15531.268</v>
       </c>
       <c r="F54">
-        <v>15847.312</v>
+        <v>16152.068</v>
       </c>
       <c r="G54">
         <v>3633.4</v>
@@ -5721,28 +5721,28 @@
         <v>3626.3</v>
       </c>
       <c r="M54">
-        <v>1308.894549468585</v>
+        <v>1334.065598496826</v>
       </c>
       <c r="N54">
-        <v>2317.405450531416</v>
+        <v>2292.234401503174</v>
       </c>
       <c r="O54">
-        <v>787.9178531806814</v>
+        <v>779.3596965110792</v>
       </c>
       <c r="P54">
-        <v>1529.487597350734</v>
+        <v>1512.874704992095</v>
       </c>
       <c r="Q54">
-        <v>2231.887597350734</v>
+        <v>2215.274704992094</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1367377405335254</v>
+        <v>0.138289001537602</v>
       </c>
       <c r="T54">
-        <v>1.185223609872376</v>
+        <v>1.205441741050027</v>
       </c>
       <c r="U54">
         <v>0.08259410488470123</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.770505845159406</v>
+        <v>2.718232149967719</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09388724861134143</v>
+        <v>0.09379408497016123</v>
       </c>
       <c r="C55">
-        <v>16908.02184380874</v>
+        <v>16659.1891910574</v>
       </c>
       <c r="D55">
-        <v>29426.68984380874</v>
+        <v>29482.6131910574</v>
       </c>
       <c r="E55">
-        <v>15531.268</v>
+        <v>15836.024</v>
       </c>
       <c r="F55">
-        <v>16152.068</v>
+        <v>16456.824</v>
       </c>
       <c r="G55">
         <v>3633.4</v>
@@ -5803,28 +5803,28 @@
         <v>3626.3</v>
       </c>
       <c r="M55">
-        <v>1334.065598496826</v>
+        <v>1359.236647525069</v>
       </c>
       <c r="N55">
-        <v>2292.234401503174</v>
+        <v>2267.063352474932</v>
       </c>
       <c r="O55">
-        <v>779.3596965110792</v>
+        <v>770.8015398414769</v>
       </c>
       <c r="P55">
-        <v>1512.874704992095</v>
+        <v>1496.261812633455</v>
       </c>
       <c r="Q55">
-        <v>2215.274704992094</v>
+        <v>2198.661812633455</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.138289001537602</v>
+        <v>0.1399077086722907</v>
       </c>
       <c r="T55">
-        <v>1.205441741050027</v>
+        <v>1.226538921409315</v>
       </c>
       <c r="U55">
         <v>0.08259410488470123</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.718232149967719</v>
+        <v>2.667894517560909</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09379408497016123</v>
+        <v>0.09370092132898103</v>
       </c>
       <c r="C56">
-        <v>16659.1891910574</v>
+        <v>16410.56949977357</v>
       </c>
       <c r="D56">
-        <v>29482.6131910574</v>
+        <v>29538.74949977357</v>
       </c>
       <c r="E56">
-        <v>15836.024</v>
+        <v>16140.78</v>
       </c>
       <c r="F56">
-        <v>16456.824</v>
+        <v>16761.58</v>
       </c>
       <c r="G56">
         <v>3633.4</v>
@@ -5885,28 +5885,28 @@
         <v>3626.3</v>
       </c>
       <c r="M56">
-        <v>1359.236647525069</v>
+        <v>1384.407696553311</v>
       </c>
       <c r="N56">
-        <v>2267.063352474932</v>
+        <v>2241.89230344669</v>
       </c>
       <c r="O56">
-        <v>770.8015398414769</v>
+        <v>762.2433831718746</v>
       </c>
       <c r="P56">
-        <v>1496.261812633455</v>
+        <v>1479.648920274815</v>
       </c>
       <c r="Q56">
-        <v>2198.661812633455</v>
+        <v>2182.048920274815</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1399077086722907</v>
+        <v>0.1415983583462989</v>
       </c>
       <c r="T56">
-        <v>1.226538921409315</v>
+        <v>1.248573754229015</v>
       </c>
       <c r="U56">
         <v>0.08259410488470123</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.667894517560909</v>
+        <v>2.619387344514347</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09370092132898103</v>
+        <v>0.0936077576878008</v>
       </c>
       <c r="C57">
-        <v>16410.56949977357</v>
+        <v>16162.16398874443</v>
       </c>
       <c r="D57">
-        <v>29538.74949977357</v>
+        <v>29595.09998874443</v>
       </c>
       <c r="E57">
-        <v>16140.78</v>
+        <v>16445.536</v>
       </c>
       <c r="F57">
-        <v>16761.58</v>
+        <v>17066.336</v>
       </c>
       <c r="G57">
         <v>3633.4</v>
@@ -5967,28 +5967,28 @@
         <v>3626.3</v>
       </c>
       <c r="M57">
-        <v>1384.407696553311</v>
+        <v>1409.578745581552</v>
       </c>
       <c r="N57">
-        <v>2241.89230344669</v>
+        <v>2216.721254418448</v>
       </c>
       <c r="O57">
-        <v>762.2433831718746</v>
+        <v>753.6852265022723</v>
       </c>
       <c r="P57">
-        <v>1479.648920274815</v>
+        <v>1463.036027916175</v>
       </c>
       <c r="Q57">
-        <v>2182.048920274815</v>
+        <v>2165.436027916175</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1415983583462989</v>
+        <v>0.1433658557327619</v>
       </c>
       <c r="T57">
-        <v>1.248573754229015</v>
+        <v>1.271610170358701</v>
       </c>
       <c r="U57">
         <v>0.08259410488470123</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.619387344514347</v>
+        <v>2.572612570505163</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.0936077576878008</v>
+        <v>0.0935145940466206</v>
       </c>
       <c r="C58">
-        <v>16162.16398874443</v>
+        <v>15913.97388607508</v>
       </c>
       <c r="D58">
-        <v>29595.09998874443</v>
+        <v>29651.66588607509</v>
       </c>
       <c r="E58">
-        <v>16445.536</v>
+        <v>16750.292</v>
       </c>
       <c r="F58">
-        <v>17066.336</v>
+        <v>17371.092</v>
       </c>
       <c r="G58">
         <v>3633.4</v>
@@ -6049,28 +6049,28 @@
         <v>3626.3</v>
       </c>
       <c r="M58">
-        <v>1409.578745581552</v>
+        <v>1434.749794609794</v>
       </c>
       <c r="N58">
-        <v>2216.721254418448</v>
+        <v>2191.550205390206</v>
       </c>
       <c r="O58">
-        <v>753.6852265022723</v>
+        <v>745.1270698326699</v>
       </c>
       <c r="P58">
-        <v>1463.036027916175</v>
+        <v>1446.423135557536</v>
       </c>
       <c r="Q58">
-        <v>2165.436027916175</v>
+        <v>2148.823135557535</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1433658557327619</v>
+        <v>0.1452155622999907</v>
       </c>
       <c r="T58">
-        <v>1.271610170358701</v>
+        <v>1.295718047703722</v>
       </c>
       <c r="U58">
         <v>0.08259410488470123</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.572612570505163</v>
+        <v>2.527479016636651</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.0935145940466206</v>
+        <v>0.09476123040544041</v>
       </c>
       <c r="C59">
-        <v>15913.97388607508</v>
+        <v>14869.76660893238</v>
       </c>
       <c r="D59">
-        <v>29651.66588607509</v>
+        <v>28912.21460893238</v>
       </c>
       <c r="E59">
-        <v>16750.292</v>
+        <v>17055.048</v>
       </c>
       <c r="F59">
-        <v>17371.092</v>
+        <v>17675.848</v>
       </c>
       <c r="G59">
         <v>3633.4</v>
@@ -6131,45 +6131,45 @@
         <v>3626.3</v>
       </c>
       <c r="M59">
-        <v>1434.749794609794</v>
+        <v>1521.786311638037</v>
       </c>
       <c r="N59">
-        <v>2191.550205390206</v>
+        <v>2104.513688361963</v>
       </c>
       <c r="O59">
-        <v>745.1270698326699</v>
+        <v>715.5346540430676</v>
       </c>
       <c r="P59">
-        <v>1446.423135557536</v>
+        <v>1388.979034318896</v>
       </c>
       <c r="Q59">
-        <v>2148.823135557535</v>
+        <v>2091.379034318896</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1452155622999907</v>
+        <v>0.1471533501323257</v>
       </c>
       <c r="T59">
-        <v>1.295718047703722</v>
+        <v>1.32097391920803</v>
       </c>
       <c r="U59">
-        <v>0.08259410488470123</v>
+        <v>0.08609410488470122</v>
       </c>
       <c r="V59">
         <v>0.34</v>
       </c>
       <c r="W59">
-        <v>0.0545121092239028</v>
+        <v>0.05682210922390279</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y59">
-        <v>2.527479016636651</v>
+        <v>2.382923260820164</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09476123040544039</v>
+        <v>0.0946911667642602</v>
       </c>
       <c r="C60">
-        <v>14869.76660893239</v>
+        <v>14605.58984417184</v>
       </c>
       <c r="D60">
-        <v>28912.21460893239</v>
+        <v>28952.79384417184</v>
       </c>
       <c r="E60">
-        <v>17055.048</v>
+        <v>17359.804</v>
       </c>
       <c r="F60">
-        <v>17675.848</v>
+        <v>17980.604</v>
       </c>
       <c r="G60">
         <v>3633.4</v>
@@ -6213,28 +6213,28 @@
         <v>3626.3</v>
       </c>
       <c r="M60">
-        <v>1521.786311638036</v>
+        <v>1548.024006666278</v>
       </c>
       <c r="N60">
-        <v>2104.513688361964</v>
+        <v>2078.275993333722</v>
       </c>
       <c r="O60">
-        <v>715.5346540430679</v>
+        <v>706.6138377334655</v>
       </c>
       <c r="P60">
-        <v>1388.979034318897</v>
+        <v>1371.662155600256</v>
       </c>
       <c r="Q60">
-        <v>2091.379034318896</v>
+        <v>2074.062155600256</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1471533501323256</v>
+        <v>0.1491856642003843</v>
       </c>
       <c r="T60">
-        <v>1.320973919208029</v>
+        <v>1.347461784444255</v>
       </c>
       <c r="U60">
         <v>0.08609410488470122</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.382923260820164</v>
+        <v>2.342534730975755</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.0946911667642602</v>
+        <v>0.09462110312307997</v>
       </c>
       <c r="C61">
-        <v>14605.58984417184</v>
+        <v>14341.52714806805</v>
       </c>
       <c r="D61">
-        <v>28952.79384417184</v>
+        <v>28993.48714806805</v>
       </c>
       <c r="E61">
-        <v>17359.804</v>
+        <v>17664.56</v>
       </c>
       <c r="F61">
-        <v>17980.604</v>
+        <v>18285.36</v>
       </c>
       <c r="G61">
         <v>3633.4</v>
@@ -6295,28 +6295,28 @@
         <v>3626.3</v>
       </c>
       <c r="M61">
-        <v>1548.024006666278</v>
+        <v>1574.26170169452</v>
       </c>
       <c r="N61">
-        <v>2078.275993333722</v>
+        <v>2052.03829830548</v>
       </c>
       <c r="O61">
-        <v>706.6138377334655</v>
+        <v>697.6930214238633</v>
       </c>
       <c r="P61">
-        <v>1371.662155600256</v>
+        <v>1354.345276881617</v>
       </c>
       <c r="Q61">
-        <v>2074.062155600256</v>
+        <v>2056.745276881617</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1491856642003843</v>
+        <v>0.1513195939718458</v>
       </c>
       <c r="T61">
-        <v>1.347461784444255</v>
+        <v>1.375274042942291</v>
       </c>
       <c r="U61">
         <v>0.08609410488470122</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.342534730975755</v>
+        <v>2.303492485459492</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09462110312307997</v>
+        <v>0.09455103948189977</v>
       </c>
       <c r="C62">
-        <v>14341.52714806805</v>
+        <v>14077.57900227026</v>
       </c>
       <c r="D62">
-        <v>28993.48714806805</v>
+        <v>29034.29500227025</v>
       </c>
       <c r="E62">
-        <v>17664.56</v>
+        <v>17969.316</v>
       </c>
       <c r="F62">
-        <v>18285.36</v>
+        <v>18590.116</v>
       </c>
       <c r="G62">
         <v>3633.4</v>
@@ -6377,28 +6377,28 @@
         <v>3626.3</v>
       </c>
       <c r="M62">
-        <v>1574.26170169452</v>
+        <v>1600.499396722762</v>
       </c>
       <c r="N62">
-        <v>2052.03829830548</v>
+        <v>2025.800603277238</v>
       </c>
       <c r="O62">
-        <v>697.6930214238633</v>
+        <v>688.7722051142609</v>
       </c>
       <c r="P62">
-        <v>1354.345276881617</v>
+        <v>1337.028398162977</v>
       </c>
       <c r="Q62">
-        <v>2056.745276881617</v>
+        <v>2039.428398162977</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1513195939718458</v>
+        <v>0.1535629560392797</v>
       </c>
       <c r="T62">
-        <v>1.375274042942291</v>
+        <v>1.404512571106893</v>
       </c>
       <c r="U62">
         <v>0.08609410488470122</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.303492485459492</v>
+        <v>2.265730313566714</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09455103948189977</v>
+        <v>0.0956267358407196</v>
       </c>
       <c r="C63">
-        <v>14077.57900227026</v>
+        <v>13158.6838899324</v>
       </c>
       <c r="D63">
-        <v>29034.29500227025</v>
+        <v>28420.1558899324</v>
       </c>
       <c r="E63">
-        <v>17969.316</v>
+        <v>18274.072</v>
       </c>
       <c r="F63">
-        <v>18590.116</v>
+        <v>18894.872</v>
       </c>
       <c r="G63">
         <v>3633.4</v>
@@ -6459,45 +6459,45 @@
         <v>3626.3</v>
       </c>
       <c r="M63">
-        <v>1600.499396722762</v>
+        <v>1679.642733351004</v>
       </c>
       <c r="N63">
-        <v>2025.800603277238</v>
+        <v>1946.657266648996</v>
       </c>
       <c r="O63">
-        <v>688.7722051142609</v>
+        <v>661.8634706606587</v>
       </c>
       <c r="P63">
-        <v>1337.028398162977</v>
+        <v>1284.793795988337</v>
       </c>
       <c r="Q63">
-        <v>2039.428398162977</v>
+        <v>1987.193795988337</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1535629560392797</v>
+        <v>0.1559243897944733</v>
       </c>
       <c r="T63">
-        <v>1.404512571106893</v>
+        <v>1.435289969174896</v>
       </c>
       <c r="U63">
-        <v>0.08609410488470122</v>
+        <v>0.08889410488470123</v>
       </c>
       <c r="V63">
         <v>0.34</v>
       </c>
       <c r="W63">
-        <v>0.05682210922390279</v>
+        <v>0.0586701092239028</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y63">
-        <v>2.265730313566714</v>
+        <v>2.158971028776625</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.0956267358407196</v>
+        <v>0.09557515219953937</v>
       </c>
       <c r="C64">
-        <v>13158.6838899324</v>
+        <v>12882.78447693065</v>
       </c>
       <c r="D64">
-        <v>28420.1558899324</v>
+        <v>28449.01247693065</v>
       </c>
       <c r="E64">
-        <v>18274.072</v>
+        <v>18578.828</v>
       </c>
       <c r="F64">
-        <v>18894.872</v>
+        <v>19199.628</v>
       </c>
       <c r="G64">
         <v>3633.4</v>
@@ -6541,28 +6541,28 @@
         <v>3626.3</v>
       </c>
       <c r="M64">
-        <v>1679.642733351004</v>
+        <v>1706.733745179247</v>
       </c>
       <c r="N64">
-        <v>1946.657266648996</v>
+        <v>1919.566254820754</v>
       </c>
       <c r="O64">
-        <v>661.8634706606587</v>
+        <v>652.6525266390563</v>
       </c>
       <c r="P64">
-        <v>1284.793795988337</v>
+        <v>1266.913728181697</v>
       </c>
       <c r="Q64">
-        <v>1987.193795988337</v>
+        <v>1969.313728181697</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1559243897944733</v>
+        <v>0.1584134686175152</v>
       </c>
       <c r="T64">
-        <v>1.435289969174896</v>
+        <v>1.467731010381709</v>
       </c>
       <c r="U64">
         <v>0.08889410488470123</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.158971028776625</v>
+        <v>2.124701647367472</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09557515219953937</v>
+        <v>0.09552356855835917</v>
       </c>
       <c r="C65">
-        <v>12882.78447693065</v>
+        <v>12606.94372292892</v>
       </c>
       <c r="D65">
-        <v>28449.01247693065</v>
+        <v>28477.92772292891</v>
       </c>
       <c r="E65">
-        <v>18578.828</v>
+        <v>18883.584</v>
       </c>
       <c r="F65">
-        <v>19199.628</v>
+        <v>19504.384</v>
       </c>
       <c r="G65">
         <v>3633.4</v>
@@ -6623,28 +6623,28 @@
         <v>3626.3</v>
       </c>
       <c r="M65">
-        <v>1706.733745179247</v>
+        <v>1733.824757007488</v>
       </c>
       <c r="N65">
-        <v>1919.566254820754</v>
+        <v>1892.475242992512</v>
       </c>
       <c r="O65">
-        <v>652.6525266390563</v>
+        <v>643.4415826174541</v>
       </c>
       <c r="P65">
-        <v>1266.913728181697</v>
+        <v>1249.033660375058</v>
       </c>
       <c r="Q65">
-        <v>1969.313728181697</v>
+        <v>1951.433660375057</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1584134686175152</v>
+        <v>0.1610408295973927</v>
       </c>
       <c r="T65">
-        <v>1.467731010381709</v>
+        <v>1.501974331655567</v>
       </c>
       <c r="U65">
         <v>0.08889410488470123</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.124701647367472</v>
+        <v>2.091503184127355</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09552356855835917</v>
+        <v>0.09547198491717898</v>
       </c>
       <c r="C66">
-        <v>12606.94372292892</v>
+        <v>12331.16180697015</v>
       </c>
       <c r="D66">
-        <v>28477.92772292891</v>
+        <v>28506.90180697015</v>
       </c>
       <c r="E66">
-        <v>18883.584</v>
+        <v>19188.34</v>
       </c>
       <c r="F66">
-        <v>19504.384</v>
+        <v>19809.14</v>
       </c>
       <c r="G66">
         <v>3633.4</v>
@@ -6705,28 +6705,28 @@
         <v>3626.3</v>
       </c>
       <c r="M66">
-        <v>1733.824757007488</v>
+        <v>1760.91576883573</v>
       </c>
       <c r="N66">
-        <v>1892.475242992512</v>
+        <v>1865.38423116427</v>
       </c>
       <c r="O66">
-        <v>643.4415826174541</v>
+        <v>634.2306385958518</v>
       </c>
       <c r="P66">
-        <v>1249.033660375058</v>
+        <v>1231.153592568418</v>
       </c>
       <c r="Q66">
-        <v>1951.433660375057</v>
+        <v>1933.553592568418</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1610408295973927</v>
+        <v>0.1638183254904061</v>
       </c>
       <c r="T66">
-        <v>1.501974331655567</v>
+        <v>1.538174414145075</v>
       </c>
       <c r="U66">
         <v>0.08889410488470123</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.091503184127355</v>
+        <v>2.059326212063858</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09547198491717898</v>
+        <v>0.09542040127599877</v>
       </c>
       <c r="C67">
-        <v>12331.16180697015</v>
+        <v>12055.43890882673</v>
       </c>
       <c r="D67">
-        <v>28506.90180697015</v>
+        <v>28535.93490882673</v>
       </c>
       <c r="E67">
-        <v>19188.34</v>
+        <v>19493.096</v>
       </c>
       <c r="F67">
-        <v>19809.14</v>
+        <v>20113.896</v>
       </c>
       <c r="G67">
         <v>3633.4</v>
@@ -6787,28 +6787,28 @@
         <v>3626.3</v>
       </c>
       <c r="M67">
-        <v>1760.91576883573</v>
+        <v>1788.006780663973</v>
       </c>
       <c r="N67">
-        <v>1865.38423116427</v>
+        <v>1838.293219336028</v>
       </c>
       <c r="O67">
-        <v>634.2306385958518</v>
+        <v>625.0196945742493</v>
       </c>
       <c r="P67">
-        <v>1231.153592568418</v>
+        <v>1213.273524761778</v>
       </c>
       <c r="Q67">
-        <v>1933.553592568418</v>
+        <v>1915.673524761778</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1638183254904061</v>
+        <v>0.1667592034947733</v>
       </c>
       <c r="T67">
-        <v>1.538174414145075</v>
+        <v>1.576503913251613</v>
       </c>
       <c r="U67">
         <v>0.08889410488470123</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.059326212063858</v>
+        <v>2.02812429975986</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09542040127599877</v>
+        <v>0.09881797763481856</v>
       </c>
       <c r="C68">
-        <v>12055.43890882673</v>
+        <v>9956.79502203831</v>
       </c>
       <c r="D68">
-        <v>28535.93490882673</v>
+        <v>26742.04702203831</v>
       </c>
       <c r="E68">
-        <v>19493.096</v>
+        <v>19797.852</v>
       </c>
       <c r="F68">
-        <v>20113.896</v>
+        <v>20418.652</v>
       </c>
       <c r="G68">
         <v>3633.4</v>
@@ -6869,45 +6869,45 @@
         <v>3626.3</v>
       </c>
       <c r="M68">
-        <v>1788.006780663973</v>
+        <v>1974.363278092215</v>
       </c>
       <c r="N68">
-        <v>1838.293219336028</v>
+        <v>1651.936721907785</v>
       </c>
       <c r="O68">
-        <v>625.0196945742493</v>
+        <v>561.6584854486471</v>
       </c>
       <c r="P68">
-        <v>1213.273524761778</v>
+        <v>1090.278236459138</v>
       </c>
       <c r="Q68">
-        <v>1915.673524761778</v>
+        <v>1792.678236459138</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1667592034947733</v>
+        <v>0.1698783165297081</v>
       </c>
       <c r="T68">
-        <v>1.576503913251613</v>
+        <v>1.617156412304001</v>
       </c>
       <c r="U68">
-        <v>0.08889410488470123</v>
+        <v>0.09669410488470123</v>
       </c>
       <c r="V68">
         <v>0.34</v>
       </c>
       <c r="W68">
-        <v>0.0586701092239028</v>
+        <v>0.06381810922390281</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y68">
-        <v>2.02812429975986</v>
+        <v>1.836693398949365</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09881797763481856</v>
+        <v>0.09881787399363834</v>
       </c>
       <c r="C69">
-        <v>9956.79502203831</v>
+        <v>9652.09030366542</v>
       </c>
       <c r="D69">
-        <v>26742.04702203831</v>
+        <v>26742.09830366542</v>
       </c>
       <c r="E69">
-        <v>19797.852</v>
+        <v>20102.608</v>
       </c>
       <c r="F69">
-        <v>20418.652</v>
+        <v>20723.408</v>
       </c>
       <c r="G69">
         <v>3633.4</v>
@@ -6951,28 +6951,28 @@
         <v>3626.3</v>
       </c>
       <c r="M69">
-        <v>1974.363278092215</v>
+        <v>2003.831386720457</v>
       </c>
       <c r="N69">
-        <v>1651.936721907785</v>
+        <v>1622.468613279544</v>
       </c>
       <c r="O69">
-        <v>561.6584854486471</v>
+        <v>551.6393285150449</v>
       </c>
       <c r="P69">
-        <v>1090.278236459138</v>
+        <v>1070.829284764499</v>
       </c>
       <c r="Q69">
-        <v>1792.678236459138</v>
+        <v>1773.229284764499</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1698783165297081</v>
+        <v>0.1731923741293264</v>
       </c>
       <c r="T69">
-        <v>1.617156412304001</v>
+        <v>1.660349692547163</v>
       </c>
       <c r="U69">
         <v>0.09669410488470123</v>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.836693398949365</v>
+        <v>1.809683201905992</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09881787399363834</v>
+        <v>0.09881777035245815</v>
       </c>
       <c r="C70">
-        <v>9652.09030366542</v>
+        <v>9347.385585489188</v>
       </c>
       <c r="D70">
-        <v>26742.09830366542</v>
+        <v>26742.14958548919</v>
       </c>
       <c r="E70">
-        <v>20102.608</v>
+        <v>20407.364</v>
       </c>
       <c r="F70">
-        <v>20723.408</v>
+        <v>21028.164</v>
       </c>
       <c r="G70">
         <v>3633.4</v>
@@ -7033,28 +7033,28 @@
         <v>3626.3</v>
       </c>
       <c r="M70">
-        <v>2003.831386720457</v>
+        <v>2033.299495348699</v>
       </c>
       <c r="N70">
-        <v>1622.468613279544</v>
+        <v>1593.000504651302</v>
       </c>
       <c r="O70">
-        <v>551.6393285150449</v>
+        <v>541.6201715814426</v>
       </c>
       <c r="P70">
-        <v>1070.829284764499</v>
+        <v>1051.380333069859</v>
       </c>
       <c r="Q70">
-        <v>1773.229284764499</v>
+        <v>1753.780333069858</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1731923741293264</v>
+        <v>0.176720241896662</v>
       </c>
       <c r="T70">
-        <v>1.660349692547163</v>
+        <v>1.70632963603182</v>
       </c>
       <c r="U70">
         <v>0.09669410488470123</v>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.809683201905992</v>
+        <v>1.783455909124746</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09881777035245815</v>
+        <v>0.09881766671127792</v>
       </c>
       <c r="C71">
-        <v>9347.385585489188</v>
+        <v>9042.680867509654</v>
       </c>
       <c r="D71">
-        <v>26742.14958548919</v>
+        <v>26742.20086750965</v>
       </c>
       <c r="E71">
-        <v>20407.364</v>
+        <v>20712.12</v>
       </c>
       <c r="F71">
-        <v>21028.164</v>
+        <v>21332.92</v>
       </c>
       <c r="G71">
         <v>3633.4</v>
@@ -7115,28 +7115,28 @@
         <v>3626.3</v>
       </c>
       <c r="M71">
-        <v>2033.299495348699</v>
+        <v>2062.767603976941</v>
       </c>
       <c r="N71">
-        <v>1593.000504651302</v>
+        <v>1563.532396023059</v>
       </c>
       <c r="O71">
-        <v>541.6201715814426</v>
+        <v>531.6010146478402</v>
       </c>
       <c r="P71">
-        <v>1051.380333069859</v>
+        <v>1031.931381375219</v>
       </c>
       <c r="Q71">
-        <v>1753.780333069858</v>
+        <v>1734.331381375219</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.176720241896662</v>
+        <v>0.1804833008484866</v>
       </c>
       <c r="T71">
-        <v>1.70632963603182</v>
+        <v>1.75537490908212</v>
       </c>
       <c r="U71">
         <v>0.09669410488470123</v>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.783455909124746</v>
+        <v>1.757977967565821</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09881766671127792</v>
+        <v>0.1006451030700977</v>
       </c>
       <c r="C72">
-        <v>9042.680867509654</v>
+        <v>7863.275380364546</v>
       </c>
       <c r="D72">
-        <v>26742.20086750965</v>
+        <v>25867.55138036454</v>
       </c>
       <c r="E72">
-        <v>20712.12</v>
+        <v>21016.876</v>
       </c>
       <c r="F72">
-        <v>21332.92</v>
+        <v>21637.676</v>
       </c>
       <c r="G72">
         <v>3633.4</v>
@@ -7197,45 +7197,45 @@
         <v>3626.3</v>
       </c>
       <c r="M72">
-        <v>2062.767603976941</v>
+        <v>2176.622649005182</v>
       </c>
       <c r="N72">
-        <v>1563.532396023059</v>
+        <v>1449.677350994818</v>
       </c>
       <c r="O72">
-        <v>531.6010146478402</v>
+        <v>492.8902993382382</v>
       </c>
       <c r="P72">
-        <v>1031.931381375219</v>
+        <v>956.7870516565798</v>
       </c>
       <c r="Q72">
-        <v>1734.331381375219</v>
+        <v>1659.18705165658</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1804833008484866</v>
+        <v>0.1845058811073336</v>
       </c>
       <c r="T72">
-        <v>1.75537490908212</v>
+        <v>1.80780261475658</v>
       </c>
       <c r="U72">
-        <v>0.09669410488470123</v>
+        <v>0.1005941048847012</v>
       </c>
       <c r="V72">
         <v>0.34</v>
       </c>
       <c r="W72">
-        <v>0.06381810922390281</v>
+        <v>0.06639210922390279</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y72">
-        <v>1.757977967565821</v>
+        <v>1.666021439985194</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1006451030700977</v>
+        <v>0.1006707394289175</v>
       </c>
       <c r="C73">
-        <v>7863.275380364546</v>
+        <v>7546.656037600376</v>
       </c>
       <c r="D73">
-        <v>25867.55138036454</v>
+        <v>25855.68803760037</v>
       </c>
       <c r="E73">
-        <v>21016.876</v>
+        <v>21321.632</v>
       </c>
       <c r="F73">
-        <v>21637.676</v>
+        <v>21942.432</v>
       </c>
       <c r="G73">
         <v>3633.4</v>
@@ -7279,28 +7279,28 @@
         <v>3626.3</v>
       </c>
       <c r="M73">
-        <v>2176.622649005182</v>
+        <v>2207.279306033424</v>
       </c>
       <c r="N73">
-        <v>1449.677350994818</v>
+        <v>1419.020693966576</v>
       </c>
       <c r="O73">
-        <v>492.8902993382382</v>
+        <v>482.467035948636</v>
       </c>
       <c r="P73">
-        <v>956.7870516565798</v>
+        <v>936.5536580179403</v>
       </c>
       <c r="Q73">
-        <v>1659.18705165658</v>
+        <v>1638.95365801794</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1845058811073336</v>
+        <v>0.1888157885275268</v>
       </c>
       <c r="T73">
-        <v>1.807802614756579</v>
+        <v>1.863975156550643</v>
       </c>
       <c r="U73">
         <v>0.1005941048847012</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.666021439985194</v>
+        <v>1.642882253318733</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1006707394289175</v>
+        <v>0.1006963757877373</v>
       </c>
       <c r="C74">
-        <v>7546.656037600376</v>
+        <v>7230.047571349682</v>
       </c>
       <c r="D74">
-        <v>25855.68803760037</v>
+        <v>25843.83557134968</v>
       </c>
       <c r="E74">
-        <v>21321.632</v>
+        <v>21626.388</v>
       </c>
       <c r="F74">
-        <v>21942.432</v>
+        <v>22247.188</v>
       </c>
       <c r="G74">
         <v>3633.4</v>
@@ -7361,28 +7361,28 @@
         <v>3626.3</v>
       </c>
       <c r="M74">
-        <v>2207.279306033424</v>
+        <v>2237.935963061666</v>
       </c>
       <c r="N74">
-        <v>1419.020693966576</v>
+        <v>1388.364036938334</v>
       </c>
       <c r="O74">
-        <v>482.467035948636</v>
+        <v>472.0437725590335</v>
       </c>
       <c r="P74">
-        <v>936.5536580179403</v>
+        <v>916.3202643793003</v>
       </c>
       <c r="Q74">
-        <v>1638.95365801794</v>
+        <v>1618.7202643793</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1888157885275268</v>
+        <v>0.1934449483492158</v>
       </c>
       <c r="T74">
-        <v>1.863975156550643</v>
+        <v>1.924308627366488</v>
       </c>
       <c r="U74">
         <v>0.1005941048847012</v>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.642882253318733</v>
+        <v>1.620377016971901</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1006963757877373</v>
+        <v>0.1007220121465571</v>
       </c>
       <c r="C75">
-        <v>7230.047571349682</v>
+        <v>6913.449966661661</v>
       </c>
       <c r="D75">
-        <v>25843.83557134968</v>
+        <v>25831.99396666166</v>
       </c>
       <c r="E75">
-        <v>21626.388</v>
+        <v>21931.144</v>
       </c>
       <c r="F75">
-        <v>22247.188</v>
+        <v>22551.944</v>
       </c>
       <c r="G75">
         <v>3633.4</v>
@@ -7443,28 +7443,28 @@
         <v>3626.3</v>
       </c>
       <c r="M75">
-        <v>2237.935963061666</v>
+        <v>2268.592620089908</v>
       </c>
       <c r="N75">
-        <v>1388.364036938334</v>
+        <v>1357.707379910092</v>
       </c>
       <c r="O75">
-        <v>472.0437725590335</v>
+        <v>461.6205091694312</v>
       </c>
       <c r="P75">
-        <v>916.3202643793003</v>
+        <v>896.0868707406605</v>
       </c>
       <c r="Q75">
-        <v>1618.7202643793</v>
+        <v>1598.48687074066</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1934449483492158</v>
+        <v>0.1984301973879578</v>
       </c>
       <c r="T75">
-        <v>1.924308627366488</v>
+        <v>1.989283134398938</v>
       </c>
       <c r="U75">
         <v>0.1005941048847012</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.620377016971901</v>
+        <v>1.598480030256064</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1007220121465571</v>
+        <v>0.1007476485053769</v>
       </c>
       <c r="C76">
-        <v>6913.449966661661</v>
+        <v>6596.863208612904</v>
       </c>
       <c r="D76">
-        <v>25831.99396666166</v>
+        <v>25820.1632086129</v>
       </c>
       <c r="E76">
-        <v>21931.144</v>
+        <v>22235.9</v>
       </c>
       <c r="F76">
-        <v>22551.944</v>
+        <v>22856.7</v>
       </c>
       <c r="G76">
         <v>3633.4</v>
@@ -7525,28 +7525,28 @@
         <v>3626.3</v>
       </c>
       <c r="M76">
-        <v>2268.592620089908</v>
+        <v>2299.24927711815</v>
       </c>
       <c r="N76">
-        <v>1357.707379910092</v>
+        <v>1327.05072288185</v>
       </c>
       <c r="O76">
-        <v>461.6205091694312</v>
+        <v>451.1972457798291</v>
       </c>
       <c r="P76">
-        <v>896.0868707406605</v>
+        <v>875.8534771020211</v>
       </c>
       <c r="Q76">
-        <v>1598.48687074066</v>
+        <v>1578.253477102021</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1984301973879578</v>
+        <v>0.2038142663497992</v>
       </c>
       <c r="T76">
-        <v>1.989283134398938</v>
+        <v>2.059455601993983</v>
       </c>
       <c r="U76">
         <v>0.1005941048847012</v>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.598480030256064</v>
+        <v>1.577166963185983</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1007476485053769</v>
+        <v>0.1007732848641967</v>
       </c>
       <c r="C77">
-        <v>6596.863208612904</v>
+        <v>6280.287282307323</v>
       </c>
       <c r="D77">
-        <v>25820.1632086129</v>
+        <v>25808.34328230732</v>
       </c>
       <c r="E77">
-        <v>22235.9</v>
+        <v>22540.656</v>
       </c>
       <c r="F77">
-        <v>22856.7</v>
+        <v>23161.456</v>
       </c>
       <c r="G77">
         <v>3633.4</v>
@@ -7607,28 +7607,28 @@
         <v>3626.3</v>
       </c>
       <c r="M77">
-        <v>2299.24927711815</v>
+        <v>2329.905934146392</v>
       </c>
       <c r="N77">
-        <v>1327.05072288185</v>
+        <v>1296.394065853608</v>
       </c>
       <c r="O77">
-        <v>451.1972457798291</v>
+        <v>440.7739823902268</v>
       </c>
       <c r="P77">
-        <v>875.8534771020211</v>
+        <v>855.6200834633812</v>
       </c>
       <c r="Q77">
-        <v>1578.253477102021</v>
+        <v>1558.020083463381</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2038142663497992</v>
+        <v>0.2096470077251274</v>
       </c>
       <c r="T77">
-        <v>2.059455601993983</v>
+        <v>2.135475775221949</v>
       </c>
       <c r="U77">
         <v>0.1005941048847012</v>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.577166963185983</v>
+        <v>1.556414766301957</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1007732848641967</v>
+        <v>0.1007989212230165</v>
       </c>
       <c r="C78">
-        <v>6280.287282307323</v>
+        <v>5963.722172876081</v>
       </c>
       <c r="D78">
-        <v>25808.34328230732</v>
+        <v>25796.53417287608</v>
       </c>
       <c r="E78">
-        <v>22540.656</v>
+        <v>22845.412</v>
       </c>
       <c r="F78">
-        <v>23161.456</v>
+        <v>23466.212</v>
       </c>
       <c r="G78">
         <v>3633.4</v>
@@ -7689,28 +7689,28 @@
         <v>3626.3</v>
       </c>
       <c r="M78">
-        <v>2329.905934146392</v>
+        <v>2360.562591174634</v>
       </c>
       <c r="N78">
-        <v>1296.394065853608</v>
+        <v>1265.737408825366</v>
       </c>
       <c r="O78">
-        <v>440.7739823902268</v>
+        <v>430.3507190006245</v>
       </c>
       <c r="P78">
-        <v>855.6200834633812</v>
+        <v>835.3866898247416</v>
       </c>
       <c r="Q78">
-        <v>1558.020083463381</v>
+        <v>1537.786689824741</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2096470077251274</v>
+        <v>0.215986944002658</v>
       </c>
       <c r="T78">
-        <v>2.135475775221949</v>
+        <v>2.218106398295825</v>
       </c>
       <c r="U78">
         <v>0.1005941048847012</v>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.556414766301957</v>
+        <v>1.536201587518815</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1007989212230165</v>
+        <v>0.1008245575818363</v>
       </c>
       <c r="C79">
-        <v>5963.722172876081</v>
+        <v>5647.167865477575</v>
       </c>
       <c r="D79">
-        <v>25796.53417287608</v>
+        <v>25784.73586547757</v>
       </c>
       <c r="E79">
-        <v>22845.412</v>
+        <v>23150.168</v>
       </c>
       <c r="F79">
-        <v>23466.212</v>
+        <v>23770.968</v>
       </c>
       <c r="G79">
         <v>3633.4</v>
@@ -7771,28 +7771,28 @@
         <v>3626.3</v>
       </c>
       <c r="M79">
-        <v>2360.562591174634</v>
+        <v>2391.219248202876</v>
       </c>
       <c r="N79">
-        <v>1265.737408825366</v>
+        <v>1235.080751797124</v>
       </c>
       <c r="O79">
-        <v>430.3507190006245</v>
+        <v>419.9274556110221</v>
       </c>
       <c r="P79">
-        <v>835.3866898247416</v>
+        <v>815.1532961861017</v>
       </c>
       <c r="Q79">
-        <v>1537.786689824741</v>
+        <v>1517.553296186101</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.215986944002658</v>
+        <v>0.2229032381236004</v>
       </c>
       <c r="T79">
-        <v>2.218106398295825</v>
+        <v>2.308248896194599</v>
       </c>
       <c r="U79">
         <v>0.1005941048847012</v>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.536201587518815</v>
+        <v>1.516506695371138</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1008245575818363</v>
+        <v>0.1082540739406561</v>
       </c>
       <c r="C80">
-        <v>5647.167865477575</v>
+        <v>2324.754956514269</v>
       </c>
       <c r="D80">
-        <v>25784.73586547757</v>
+        <v>22767.07895651427</v>
       </c>
       <c r="E80">
-        <v>23150.168</v>
+        <v>23454.924</v>
       </c>
       <c r="F80">
-        <v>23770.968</v>
+        <v>24075.724</v>
       </c>
       <c r="G80">
         <v>3633.4</v>
@@ -7853,45 +7853,45 @@
         <v>3626.3</v>
       </c>
       <c r="M80">
-        <v>2391.219248202876</v>
+        <v>2763.751186031119</v>
       </c>
       <c r="N80">
-        <v>1235.080751797124</v>
+        <v>862.5488139688814</v>
       </c>
       <c r="O80">
-        <v>419.9274556110221</v>
+        <v>293.2665967494197</v>
       </c>
       <c r="P80">
-        <v>815.1532961861017</v>
+        <v>569.2822172194617</v>
       </c>
       <c r="Q80">
-        <v>1517.553296186101</v>
+        <v>1271.682217219461</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2229032381236004</v>
+        <v>0.230478226922728</v>
       </c>
       <c r="T80">
-        <v>2.308248896194599</v>
+        <v>2.406976393893256</v>
       </c>
       <c r="U80">
-        <v>0.1005941048847012</v>
+        <v>0.1147941048847012</v>
       </c>
       <c r="V80">
         <v>0.34</v>
       </c>
       <c r="W80">
-        <v>0.06639210922390279</v>
+        <v>0.07576410922390281</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y80">
-        <v>1.516506695371138</v>
+        <v>1.312093512009503</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1082540739406561</v>
+        <v>0.1083734302994759</v>
       </c>
       <c r="C81">
-        <v>2324.754956514269</v>
+        <v>1977.273792885295</v>
       </c>
       <c r="D81">
-        <v>22767.07895651427</v>
+        <v>22724.35379288529</v>
       </c>
       <c r="E81">
-        <v>23454.924</v>
+        <v>23759.68</v>
       </c>
       <c r="F81">
-        <v>24075.724</v>
+        <v>24380.48</v>
       </c>
       <c r="G81">
         <v>3633.4</v>
@@ -7935,28 +7935,28 @@
         <v>3626.3</v>
       </c>
       <c r="M81">
-        <v>2763.751186031119</v>
+        <v>2798.735378259361</v>
       </c>
       <c r="N81">
-        <v>862.5488139688814</v>
+        <v>827.5646217406393</v>
       </c>
       <c r="O81">
-        <v>293.2665967494197</v>
+        <v>281.3719713918174</v>
       </c>
       <c r="P81">
-        <v>569.2822172194617</v>
+        <v>546.1926503488219</v>
       </c>
       <c r="Q81">
-        <v>1271.682217219461</v>
+        <v>1248.592650348822</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.230478226922728</v>
+        <v>0.2388107146017682</v>
       </c>
       <c r="T81">
-        <v>2.406976393893256</v>
+        <v>2.515576641361779</v>
       </c>
       <c r="U81">
         <v>0.1147941048847012</v>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.312093512009503</v>
+        <v>1.295692343109384</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1083734302994759</v>
+        <v>0.1084927866582957</v>
       </c>
       <c r="C82">
-        <v>1977.273792885295</v>
+        <v>1629.952686712091</v>
       </c>
       <c r="D82">
-        <v>22724.35379288529</v>
+        <v>22681.78868671209</v>
       </c>
       <c r="E82">
-        <v>23759.68</v>
+        <v>24064.436</v>
       </c>
       <c r="F82">
-        <v>24380.48</v>
+        <v>24685.236</v>
       </c>
       <c r="G82">
         <v>3633.4</v>
@@ -8017,28 +8017,28 @@
         <v>3626.3</v>
       </c>
       <c r="M82">
-        <v>2798.735378259361</v>
+        <v>2833.719570487603</v>
       </c>
       <c r="N82">
-        <v>827.5646217406393</v>
+        <v>792.5804295123971</v>
       </c>
       <c r="O82">
-        <v>281.3719713918174</v>
+        <v>269.477346034215</v>
       </c>
       <c r="P82">
-        <v>546.1926503488219</v>
+        <v>523.103083478182</v>
       </c>
       <c r="Q82">
-        <v>1248.592650348822</v>
+        <v>1225.503083478182</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2388107146017682</v>
+        <v>0.2480203062470232</v>
       </c>
       <c r="T82">
-        <v>2.515576641361779</v>
+        <v>2.635608493826988</v>
       </c>
       <c r="U82">
         <v>0.1147941048847012</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.295692343109384</v>
+        <v>1.279696141342602</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1084927866582957</v>
+        <v>0.1086121430171155</v>
       </c>
       <c r="C83">
-        <v>1629.952686712091</v>
+        <v>1282.790740262837</v>
       </c>
       <c r="D83">
-        <v>22681.78868671209</v>
+        <v>22639.38274026284</v>
       </c>
       <c r="E83">
-        <v>24064.436</v>
+        <v>24369.192</v>
       </c>
       <c r="F83">
-        <v>24685.236</v>
+        <v>24989.992</v>
       </c>
       <c r="G83">
         <v>3633.4</v>
@@ -8099,28 +8099,28 @@
         <v>3626.3</v>
       </c>
       <c r="M83">
-        <v>2833.719570487603</v>
+        <v>2868.703762715845</v>
       </c>
       <c r="N83">
-        <v>792.5804295123971</v>
+        <v>757.596237284155</v>
       </c>
       <c r="O83">
-        <v>269.477346034215</v>
+        <v>257.5827206766127</v>
       </c>
       <c r="P83">
-        <v>523.103083478182</v>
+        <v>500.0135166075423</v>
       </c>
       <c r="Q83">
-        <v>1225.503083478182</v>
+        <v>1202.413516607542</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2480203062470232</v>
+        <v>0.2582531858528621</v>
       </c>
       <c r="T83">
-        <v>2.635608493826988</v>
+        <v>2.768977218788332</v>
       </c>
       <c r="U83">
         <v>0.1147941048847012</v>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.279696141342602</v>
+        <v>1.264090090838424</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1086121430171155</v>
+        <v>0.1244110761599524</v>
       </c>
       <c r="C84">
-        <v>1282.790740262837</v>
+        <v>-3513.185228246137</v>
       </c>
       <c r="D84">
-        <v>22639.38274026284</v>
+        <v>18148.16277175386</v>
       </c>
       <c r="E84">
-        <v>24369.192</v>
+        <v>24673.948</v>
       </c>
       <c r="F84">
-        <v>24989.992</v>
+        <v>25294.748</v>
       </c>
       <c r="G84">
         <v>3633.4</v>
@@ -8181,45 +8181,45 @@
         <v>3626.3</v>
       </c>
       <c r="M84">
-        <v>2868.703762715845</v>
+        <v>3627.117747744087</v>
       </c>
       <c r="N84">
-        <v>757.596237284155</v>
+        <v>-0.8177477440863186</v>
       </c>
       <c r="O84">
-        <v>257.5827206766127</v>
+        <v>-0.2780342329893483</v>
       </c>
       <c r="P84">
-        <v>500.0135166075423</v>
+        <v>-0.5397135110969702</v>
       </c>
       <c r="Q84">
-        <v>1202.413516607542</v>
+        <v>701.8602864889027</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2582531858528621</v>
+        <v>0.2697097784063625</v>
       </c>
       <c r="T84">
-        <v>2.768977218788332</v>
+        <v>2.918295025712408</v>
       </c>
       <c r="U84">
-        <v>0.1147941048847012</v>
+        <v>0.1433941048847012</v>
       </c>
       <c r="V84">
-        <v>0.34</v>
+        <v>0.3399233456831772</v>
       </c>
       <c r="W84">
-        <v>0.07576410922390281</v>
+        <v>0.09465110100104916</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y84">
-        <v>1.264090090838424</v>
+        <v>0.9997745461269916</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1244110761599524</v>
+        <v>0.1253870172087994</v>
       </c>
       <c r="C85">
-        <v>-3513.185228246137</v>
+        <v>-4037.645508790072</v>
       </c>
       <c r="D85">
-        <v>18148.16277175386</v>
+        <v>17928.45849120993</v>
       </c>
       <c r="E85">
-        <v>24673.948</v>
+        <v>24978.704</v>
       </c>
       <c r="F85">
-        <v>25294.748</v>
+        <v>25599.504</v>
       </c>
       <c r="G85">
         <v>3633.4</v>
@@ -8263,37 +8263,37 @@
         <v>3626.3</v>
       </c>
       <c r="M85">
-        <v>3627.117747744087</v>
+        <v>3670.817961572329</v>
       </c>
       <c r="N85">
-        <v>-0.8177477440863186</v>
+        <v>-44.51796157232866</v>
       </c>
       <c r="O85">
-        <v>-0.2780342329893483</v>
+        <v>-15.13610693459174</v>
       </c>
       <c r="P85">
-        <v>-0.5397135110969702</v>
+        <v>-29.38185463773691</v>
       </c>
       <c r="Q85">
-        <v>701.8602864889027</v>
+        <v>673.0181453622628</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2697097784063625</v>
+        <v>0.2837041395567601</v>
       </c>
       <c r="T85">
-        <v>2.918295025712408</v>
+        <v>3.100688464819434</v>
       </c>
       <c r="U85">
         <v>0.1433941048847012</v>
       </c>
       <c r="V85">
-        <v>0.3399233456831772</v>
+        <v>0.3358766391869489</v>
       </c>
       <c r="W85">
-        <v>0.09465110100104916</v>
+        <v>0.09523137485680692</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.9997745461269916</v>
+        <v>0.9878724681969083</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1253870172087994</v>
+        <v>0.1263629582576464</v>
       </c>
       <c r="C86">
-        <v>-4037.645508790069</v>
+        <v>-4556.849874670432</v>
       </c>
       <c r="D86">
-        <v>17928.45849120993</v>
+        <v>17714.01012532957</v>
       </c>
       <c r="E86">
-        <v>24978.704</v>
+        <v>25283.46</v>
       </c>
       <c r="F86">
-        <v>25599.504</v>
+        <v>25904.26</v>
       </c>
       <c r="G86">
         <v>3633.4</v>
@@ -8345,37 +8345,37 @@
         <v>3626.3</v>
       </c>
       <c r="M86">
-        <v>3670.817961572328</v>
+        <v>3714.51817540057</v>
       </c>
       <c r="N86">
-        <v>-44.51796157232775</v>
+        <v>-88.21817540057009</v>
       </c>
       <c r="O86">
-        <v>-15.13610693459144</v>
+        <v>-29.99417963619383</v>
       </c>
       <c r="P86">
-        <v>-29.38185463773631</v>
+        <v>-58.22399576437626</v>
       </c>
       <c r="Q86">
-        <v>673.0181453622633</v>
+        <v>644.1760042356234</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2837041395567599</v>
+        <v>0.2995644155272107</v>
       </c>
       <c r="T86">
-        <v>3.100688464819432</v>
+        <v>3.307401029140728</v>
       </c>
       <c r="U86">
         <v>0.1433941048847012</v>
       </c>
       <c r="V86">
-        <v>0.3358766391869489</v>
+        <v>0.3319251493141613</v>
       </c>
       <c r="W86">
-        <v>0.09523137485680691</v>
+        <v>0.09579799521007627</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.9878724681969085</v>
+        <v>0.9762504391592978</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1263629582576464</v>
+        <v>0.1273388993064934</v>
       </c>
       <c r="C87">
-        <v>-4556.849874670432</v>
+        <v>-5070.984699931869</v>
       </c>
       <c r="D87">
-        <v>17714.01012532957</v>
+        <v>17504.63130006813</v>
       </c>
       <c r="E87">
-        <v>25283.46</v>
+        <v>25588.216</v>
       </c>
       <c r="F87">
-        <v>25904.26</v>
+        <v>26209.016</v>
       </c>
       <c r="G87">
         <v>3633.4</v>
@@ -8427,37 +8427,37 @@
         <v>3626.3</v>
       </c>
       <c r="M87">
-        <v>3714.51817540057</v>
+        <v>3758.218389228813</v>
       </c>
       <c r="N87">
-        <v>-88.21817540057009</v>
+        <v>-131.9183892288124</v>
       </c>
       <c r="O87">
-        <v>-29.99417963619383</v>
+        <v>-44.85225233779623</v>
       </c>
       <c r="P87">
-        <v>-58.22399576437626</v>
+        <v>-87.0661368910162</v>
       </c>
       <c r="Q87">
-        <v>644.1760042356234</v>
+        <v>615.3338631089835</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2995644155272107</v>
+        <v>0.3176904452077257</v>
       </c>
       <c r="T87">
-        <v>3.307401029140728</v>
+        <v>3.543643959793637</v>
       </c>
       <c r="U87">
         <v>0.1433941048847012</v>
       </c>
       <c r="V87">
-        <v>0.3319251493141613</v>
+        <v>0.3280655545546943</v>
       </c>
       <c r="W87">
-        <v>0.09579799521007627</v>
+        <v>0.09635143834582773</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.9762504391592978</v>
+        <v>0.9648986898667478</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1273388993064934</v>
+        <v>0.1283148403553404</v>
       </c>
       <c r="C88">
-        <v>-5070.984699931869</v>
+        <v>-5580.227649824334</v>
       </c>
       <c r="D88">
-        <v>17504.63130006813</v>
+        <v>17300.14435017566</v>
       </c>
       <c r="E88">
-        <v>25588.216</v>
+        <v>25892.972</v>
       </c>
       <c r="F88">
-        <v>26209.016</v>
+        <v>26513.772</v>
       </c>
       <c r="G88">
         <v>3633.4</v>
@@ -8509,37 +8509,37 @@
         <v>3626.3</v>
       </c>
       <c r="M88">
-        <v>3758.218389228813</v>
+        <v>3801.918603057054</v>
       </c>
       <c r="N88">
-        <v>-131.9183892288124</v>
+        <v>-175.6186030570539</v>
       </c>
       <c r="O88">
-        <v>-44.85225233779623</v>
+        <v>-59.71032503939832</v>
       </c>
       <c r="P88">
-        <v>-87.0661368910162</v>
+        <v>-115.9082780176555</v>
       </c>
       <c r="Q88">
-        <v>615.3338631089835</v>
+        <v>586.4917219823441</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3176904452077257</v>
+        <v>0.3386050948390892</v>
       </c>
       <c r="T88">
-        <v>3.543643959793637</v>
+        <v>3.81623195670084</v>
       </c>
       <c r="U88">
         <v>0.1433941048847012</v>
       </c>
       <c r="V88">
-        <v>0.3280655545546943</v>
+        <v>0.3242946861115369</v>
       </c>
       <c r="W88">
-        <v>0.09635143834582773</v>
+        <v>0.09689215865087224</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.9648986898667478</v>
+        <v>0.9538079003280496</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1283148403553404</v>
+        <v>0.1292907814041875</v>
       </c>
       <c r="C89">
-        <v>-5580.227649824334</v>
+        <v>-6084.748183604828</v>
       </c>
       <c r="D89">
-        <v>17300.14435017566</v>
+        <v>17100.37981639517</v>
       </c>
       <c r="E89">
-        <v>25892.972</v>
+        <v>26197.728</v>
       </c>
       <c r="F89">
-        <v>26513.772</v>
+        <v>26818.528</v>
       </c>
       <c r="G89">
         <v>3633.4</v>
@@ -8591,37 +8591,37 @@
         <v>3626.3</v>
       </c>
       <c r="M89">
-        <v>3801.918603057054</v>
+        <v>3845.618816885296</v>
       </c>
       <c r="N89">
-        <v>-175.6186030570539</v>
+        <v>-219.3188168852962</v>
       </c>
       <c r="O89">
-        <v>-59.71032503939832</v>
+        <v>-74.56839774100071</v>
       </c>
       <c r="P89">
-        <v>-115.9082780176555</v>
+        <v>-144.7504191442955</v>
       </c>
       <c r="Q89">
-        <v>586.4917219823441</v>
+        <v>557.6495808557041</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3386050948390892</v>
+        <v>0.3630055194090134</v>
       </c>
       <c r="T89">
-        <v>3.81623195670084</v>
+        <v>4.13425128642591</v>
       </c>
       <c r="U89">
         <v>0.1433941048847012</v>
       </c>
       <c r="V89">
-        <v>0.3242946861115369</v>
+        <v>0.3206095192239057</v>
       </c>
       <c r="W89">
-        <v>0.09689215865087224</v>
+        <v>0.09742058985807485</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.9538079003280496</v>
+        <v>0.942969174187958</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1292907814041875</v>
+        <v>0.1302667224530345</v>
       </c>
       <c r="C90">
-        <v>-6084.748183604828</v>
+        <v>-6584.708022901566</v>
       </c>
       <c r="D90">
-        <v>17100.37981639517</v>
+        <v>16905.17597709843</v>
       </c>
       <c r="E90">
-        <v>26197.728</v>
+        <v>26502.484</v>
       </c>
       <c r="F90">
-        <v>26818.528</v>
+        <v>27123.284</v>
       </c>
       <c r="G90">
         <v>3633.4</v>
@@ -8673,37 +8673,37 @@
         <v>3626.3</v>
       </c>
       <c r="M90">
-        <v>3845.618816885296</v>
+        <v>3889.319030713538</v>
       </c>
       <c r="N90">
-        <v>-219.3188168852962</v>
+        <v>-263.0190307135381</v>
       </c>
       <c r="O90">
-        <v>-74.56839774100071</v>
+        <v>-89.42647044260296</v>
       </c>
       <c r="P90">
-        <v>-144.7504191442955</v>
+        <v>-173.5925602709351</v>
       </c>
       <c r="Q90">
-        <v>557.6495808557041</v>
+        <v>528.8074397290645</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3630055194090134</v>
+        <v>0.3918423848098327</v>
       </c>
       <c r="T90">
-        <v>4.13425128642591</v>
+        <v>4.510092312464629</v>
       </c>
       <c r="U90">
         <v>0.1433941048847012</v>
       </c>
       <c r="V90">
-        <v>0.3206095192239057</v>
+        <v>0.3170071650753226</v>
       </c>
       <c r="W90">
-        <v>0.09742058985807485</v>
+        <v>0.09793714620668863</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.942969174187958</v>
+        <v>0.9323740149274192</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1302667224530345</v>
+        <v>0.1312426635018815</v>
       </c>
       <c r="C91">
-        <v>-6584.708022901566</v>
+        <v>-7080.261588361624</v>
       </c>
       <c r="D91">
-        <v>16905.17597709843</v>
+        <v>16714.37841163838</v>
       </c>
       <c r="E91">
-        <v>26502.484</v>
+        <v>26807.24</v>
       </c>
       <c r="F91">
-        <v>27123.284</v>
+        <v>27428.04</v>
       </c>
       <c r="G91">
         <v>3633.4</v>
@@ -8755,37 +8755,37 @@
         <v>3626.3</v>
       </c>
       <c r="M91">
-        <v>3889.319030713538</v>
+        <v>3933.019244541781</v>
       </c>
       <c r="N91">
-        <v>-263.0190307135381</v>
+        <v>-306.7192445417804</v>
       </c>
       <c r="O91">
-        <v>-89.42647044260296</v>
+        <v>-104.2845431442054</v>
       </c>
       <c r="P91">
-        <v>-173.5925602709351</v>
+        <v>-202.4347013975751</v>
       </c>
       <c r="Q91">
-        <v>528.8074397290645</v>
+        <v>499.9652986024246</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3918423848098327</v>
+        <v>0.4264466232908161</v>
       </c>
       <c r="T91">
-        <v>4.510092312464629</v>
+        <v>4.961101543711093</v>
       </c>
       <c r="U91">
         <v>0.1433941048847012</v>
       </c>
       <c r="V91">
-        <v>0.3170071650753226</v>
+        <v>0.3134848632411523</v>
       </c>
       <c r="W91">
-        <v>0.09793714620668863</v>
+        <v>0.09844222352533323</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.9323740149274192</v>
+        <v>0.9220143036504478</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1312426635018815</v>
+        <v>0.1322186045507285</v>
       </c>
       <c r="C92">
-        <v>-7080.261588361624</v>
+        <v>-7571.55640705947</v>
       </c>
       <c r="D92">
-        <v>16714.37841163838</v>
+        <v>16527.83959294053</v>
       </c>
       <c r="E92">
-        <v>26807.24</v>
+        <v>27111.996</v>
       </c>
       <c r="F92">
-        <v>27428.04</v>
+        <v>27732.796</v>
       </c>
       <c r="G92">
         <v>3633.4</v>
@@ -8837,37 +8837,37 @@
         <v>3626.3</v>
       </c>
       <c r="M92">
-        <v>3933.019244541781</v>
+        <v>3976.719458370022</v>
       </c>
       <c r="N92">
-        <v>-306.7192445417804</v>
+        <v>-350.4194583700223</v>
       </c>
       <c r="O92">
-        <v>-104.2845431442054</v>
+        <v>-119.1426158458076</v>
       </c>
       <c r="P92">
-        <v>-202.4347013975751</v>
+        <v>-231.2768425242147</v>
       </c>
       <c r="Q92">
-        <v>499.9652986024246</v>
+        <v>471.1231574757849</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4264466232908161</v>
+        <v>0.4687406925453512</v>
       </c>
       <c r="T92">
-        <v>4.961101543711093</v>
+        <v>5.512335048567881</v>
       </c>
       <c r="U92">
         <v>0.1433941048847012</v>
       </c>
       <c r="V92">
-        <v>0.3134848632411523</v>
+        <v>0.3100399746341067</v>
       </c>
       <c r="W92">
-        <v>0.09844222352533323</v>
+        <v>0.09893620024356801</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.9220143036504478</v>
+        <v>0.9118822783356078</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1322186045507285</v>
+        <v>0.1331945455995755</v>
       </c>
       <c r="C93">
-        <v>-7571.55640705947</v>
+        <v>-8058.7334929258</v>
       </c>
       <c r="D93">
-        <v>16527.83959294053</v>
+        <v>16345.4185070742</v>
       </c>
       <c r="E93">
-        <v>27111.996</v>
+        <v>27416.752</v>
       </c>
       <c r="F93">
-        <v>27732.796</v>
+        <v>28037.552</v>
       </c>
       <c r="G93">
         <v>3633.4</v>
@@ -8919,37 +8919,37 @@
         <v>3626.3</v>
       </c>
       <c r="M93">
-        <v>3976.719458370022</v>
+        <v>4020.419672198264</v>
       </c>
       <c r="N93">
-        <v>-350.4194583700223</v>
+        <v>-394.1196721982642</v>
       </c>
       <c r="O93">
-        <v>-119.1426158458076</v>
+        <v>-134.0006885474098</v>
       </c>
       <c r="P93">
-        <v>-231.2768425242147</v>
+        <v>-260.1189836508544</v>
       </c>
       <c r="Q93">
-        <v>471.1231574757849</v>
+        <v>442.2810163491453</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4687406925453512</v>
+        <v>0.5216082791135203</v>
       </c>
       <c r="T93">
-        <v>5.512335048567881</v>
+        <v>6.201376929638869</v>
       </c>
       <c r="U93">
         <v>0.1433941048847012</v>
       </c>
       <c r="V93">
-        <v>0.3100399746341067</v>
+        <v>0.3066699749098229</v>
       </c>
       <c r="W93">
-        <v>0.09893620024356801</v>
+        <v>0.09941943833749338</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.9118822783356078</v>
+        <v>0.9019705144406556</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1331945455995755</v>
+        <v>0.1341704866484226</v>
       </c>
       <c r="C94">
-        <v>-8058.7334929258</v>
+        <v>-8541.92770225797</v>
       </c>
       <c r="D94">
-        <v>16345.4185070742</v>
+        <v>16166.98029774203</v>
       </c>
       <c r="E94">
-        <v>27416.752</v>
+        <v>27721.508</v>
       </c>
       <c r="F94">
-        <v>28037.552</v>
+        <v>28342.308</v>
       </c>
       <c r="G94">
         <v>3633.4</v>
@@ -9001,37 +9001,37 @@
         <v>3626.3</v>
       </c>
       <c r="M94">
-        <v>4020.419672198264</v>
+        <v>4064.119886026507</v>
       </c>
       <c r="N94">
-        <v>-394.1196721982642</v>
+        <v>-437.8198860265065</v>
       </c>
       <c r="O94">
-        <v>-134.0006885474098</v>
+        <v>-148.8587612490122</v>
       </c>
       <c r="P94">
-        <v>-260.1189836508544</v>
+        <v>-288.9611247774943</v>
       </c>
       <c r="Q94">
-        <v>442.2810163491453</v>
+        <v>413.4388752225053</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5216082791135203</v>
+        <v>0.5895808904154519</v>
       </c>
       <c r="T94">
-        <v>6.201376929638869</v>
+        <v>7.087287919587281</v>
       </c>
       <c r="U94">
         <v>0.1433941048847012</v>
       </c>
       <c r="V94">
-        <v>0.3066699749098229</v>
+        <v>0.3033724482978893</v>
       </c>
       <c r="W94">
-        <v>0.09941943833749338</v>
+        <v>0.0998922842143451</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.9019705144406556</v>
+        <v>0.8922719067584979</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1341704866484226</v>
+        <v>0.1351464276972695</v>
       </c>
       <c r="C95">
-        <v>-8541.92770225797</v>
+        <v>-9021.268066196026</v>
       </c>
       <c r="D95">
-        <v>16166.98029774203</v>
+        <v>15992.39593380397</v>
       </c>
       <c r="E95">
-        <v>27721.508</v>
+        <v>28026.264</v>
       </c>
       <c r="F95">
-        <v>28342.308</v>
+        <v>28647.064</v>
       </c>
       <c r="G95">
         <v>3633.4</v>
@@ -9083,37 +9083,37 @@
         <v>3626.3</v>
       </c>
       <c r="M95">
-        <v>4064.119886026507</v>
+        <v>4107.820099854749</v>
       </c>
       <c r="N95">
-        <v>-437.8198860265065</v>
+        <v>-481.5200998547489</v>
       </c>
       <c r="O95">
-        <v>-148.8587612490122</v>
+        <v>-163.7168339506146</v>
       </c>
       <c r="P95">
-        <v>-288.9611247774943</v>
+        <v>-317.8032659041343</v>
       </c>
       <c r="Q95">
-        <v>413.4388752225053</v>
+        <v>384.5967340958654</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5895808904154519</v>
+        <v>0.6802110388180272</v>
       </c>
       <c r="T95">
-        <v>7.087287919587281</v>
+        <v>8.268502572851828</v>
       </c>
       <c r="U95">
         <v>0.1433941048847012</v>
       </c>
       <c r="V95">
-        <v>0.3033724482978893</v>
+        <v>0.3001450818266351</v>
       </c>
       <c r="W95">
-        <v>0.0998922842143451</v>
+        <v>0.1003550695406255</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8922719067584979</v>
+        <v>0.8827796524312798</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1351464276972695</v>
+        <v>0.1361223687461166</v>
       </c>
       <c r="C96">
-        <v>-9021.268066196026</v>
+        <v>-9496.878101886741</v>
       </c>
       <c r="D96">
-        <v>15992.39593380397</v>
+        <v>15821.54189811326</v>
       </c>
       <c r="E96">
-        <v>28026.264</v>
+        <v>28331.02</v>
       </c>
       <c r="F96">
-        <v>28647.064</v>
+        <v>28951.82</v>
       </c>
       <c r="G96">
         <v>3633.4</v>
@@ -9165,37 +9165,37 @@
         <v>3626.3</v>
       </c>
       <c r="M96">
-        <v>4107.820099854749</v>
+        <v>4151.52031368299</v>
       </c>
       <c r="N96">
-        <v>-481.5200998547489</v>
+        <v>-525.2203136829903</v>
       </c>
       <c r="O96">
-        <v>-163.7168339506146</v>
+        <v>-178.5749066522167</v>
       </c>
       <c r="P96">
-        <v>-317.8032659041343</v>
+        <v>-346.6454070307736</v>
       </c>
       <c r="Q96">
-        <v>384.5967340958654</v>
+        <v>355.7545929692261</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6802110388180272</v>
+        <v>0.8070932465816331</v>
       </c>
       <c r="T96">
-        <v>8.268502572851828</v>
+        <v>9.922203087422199</v>
       </c>
       <c r="U96">
         <v>0.1433941048847012</v>
       </c>
       <c r="V96">
-        <v>0.3001450818266351</v>
+        <v>0.2969856599126706</v>
       </c>
       <c r="W96">
-        <v>0.1003550695406255</v>
+        <v>0.1008081120179315</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8827796524312798</v>
+        <v>0.8734872350372664</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1361223687461166</v>
+        <v>0.1370983097949636</v>
       </c>
       <c r="C97">
-        <v>-9496.878101886741</v>
+        <v>-9968.876103912578</v>
       </c>
       <c r="D97">
-        <v>15821.54189811326</v>
+        <v>15654.29989608742</v>
       </c>
       <c r="E97">
-        <v>28331.02</v>
+        <v>28635.776</v>
       </c>
       <c r="F97">
-        <v>28951.82</v>
+        <v>29256.576</v>
       </c>
       <c r="G97">
         <v>3633.4</v>
@@ -9247,37 +9247,37 @@
         <v>3626.3</v>
       </c>
       <c r="M97">
-        <v>4151.52031368299</v>
+        <v>4195.220527511233</v>
       </c>
       <c r="N97">
-        <v>-525.2203136829903</v>
+        <v>-568.9205275112326</v>
       </c>
       <c r="O97">
-        <v>-178.5749066522167</v>
+        <v>-193.4329793538191</v>
       </c>
       <c r="P97">
-        <v>-346.6454070307736</v>
+        <v>-375.4875481574135</v>
       </c>
       <c r="Q97">
-        <v>355.7545929692261</v>
+        <v>326.9124518425861</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8070932465816331</v>
+        <v>0.9974165582270418</v>
       </c>
       <c r="T97">
-        <v>9.922203087422199</v>
+        <v>12.40275385927775</v>
       </c>
       <c r="U97">
         <v>0.1433941048847012</v>
       </c>
       <c r="V97">
-        <v>0.2969856599126706</v>
+        <v>0.2938920592885803</v>
       </c>
       <c r="W97">
-        <v>0.1008081120179315</v>
+        <v>0.1012517161102937</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8734872350372664</v>
+        <v>0.8643884096722948</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1370983097949636</v>
+        <v>0.1380742508438106</v>
       </c>
       <c r="C98">
-        <v>-9968.876103912575</v>
+        <v>-10437.37541743073</v>
       </c>
       <c r="D98">
-        <v>15654.29989608742</v>
+        <v>15490.55658256926</v>
       </c>
       <c r="E98">
-        <v>28635.776</v>
+        <v>28940.532</v>
       </c>
       <c r="F98">
-        <v>29256.576</v>
+        <v>29561.332</v>
       </c>
       <c r="G98">
         <v>3633.4</v>
@@ -9329,37 +9329,37 @@
         <v>3626.3</v>
       </c>
       <c r="M98">
-        <v>4195.220527511232</v>
+        <v>4238.920741339474</v>
       </c>
       <c r="N98">
-        <v>-568.9205275112317</v>
+        <v>-612.6207413394741</v>
       </c>
       <c r="O98">
-        <v>-193.4329793538188</v>
+        <v>-208.2910520554212</v>
       </c>
       <c r="P98">
-        <v>-375.4875481574129</v>
+        <v>-404.3296892840528</v>
       </c>
       <c r="Q98">
-        <v>326.9124518425867</v>
+        <v>298.0703107159468</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9974165582270392</v>
+        <v>1.314622077636052</v>
       </c>
       <c r="T98">
-        <v>12.40275385927772</v>
+        <v>16.53700514570363</v>
       </c>
       <c r="U98">
         <v>0.1433941048847012</v>
       </c>
       <c r="V98">
-        <v>0.2938920592885803</v>
+        <v>0.2908622442443681</v>
       </c>
       <c r="W98">
-        <v>0.1012517161102937</v>
+        <v>0.1016861737265247</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8643884096722949</v>
+        <v>0.8554771889540238</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1380742508438106</v>
+        <v>0.1390501918926576</v>
       </c>
       <c r="C99">
-        <v>-10437.37541743073</v>
+        <v>-10902.48469434745</v>
       </c>
       <c r="D99">
-        <v>15490.55658256926</v>
+        <v>15330.20330565255</v>
       </c>
       <c r="E99">
-        <v>28940.532</v>
+        <v>29245.288</v>
       </c>
       <c r="F99">
-        <v>29561.332</v>
+        <v>29866.088</v>
       </c>
       <c r="G99">
         <v>3633.4</v>
@@ -9411,37 +9411,37 @@
         <v>3626.3</v>
       </c>
       <c r="M99">
-        <v>4238.920741339474</v>
+        <v>4282.620955167717</v>
       </c>
       <c r="N99">
-        <v>-612.6207413394741</v>
+        <v>-656.3209551677164</v>
       </c>
       <c r="O99">
-        <v>-208.2910520554212</v>
+        <v>-223.1491247570236</v>
       </c>
       <c r="P99">
-        <v>-404.3296892840528</v>
+        <v>-433.1718304106928</v>
       </c>
       <c r="Q99">
-        <v>298.0703107159468</v>
+        <v>269.2281695893068</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.314622077636052</v>
+        <v>1.949033116454079</v>
       </c>
       <c r="T99">
-        <v>16.53700514570363</v>
+        <v>24.80550771855544</v>
       </c>
       <c r="U99">
         <v>0.1433941048847012</v>
       </c>
       <c r="V99">
-        <v>0.2908622442443681</v>
+        <v>0.2878942621602419</v>
       </c>
       <c r="W99">
-        <v>0.1016861737265247</v>
+        <v>0.1021117648607918</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8554771889540238</v>
+        <v>0.8467478298830643</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1390501918926576</v>
+        <v>0.1400261329415046</v>
       </c>
       <c r="C100">
-        <v>-10902.48469434745</v>
+        <v>-11364.30813374431</v>
       </c>
       <c r="D100">
-        <v>15330.20330565255</v>
+        <v>15173.13586625569</v>
       </c>
       <c r="E100">
-        <v>29245.288</v>
+        <v>29550.044</v>
       </c>
       <c r="F100">
-        <v>29866.088</v>
+        <v>30170.844</v>
       </c>
       <c r="G100">
         <v>3633.4</v>
@@ -9493,37 +9493,37 @@
         <v>3626.3</v>
       </c>
       <c r="M100">
-        <v>4282.620955167717</v>
+        <v>4326.321168995958</v>
       </c>
       <c r="N100">
-        <v>-656.3209551677164</v>
+        <v>-700.0211689959579</v>
       </c>
       <c r="O100">
-        <v>-223.1491247570236</v>
+        <v>-238.0071974586257</v>
       </c>
       <c r="P100">
-        <v>-433.1718304106928</v>
+        <v>-462.0139715373322</v>
       </c>
       <c r="Q100">
-        <v>269.2281695893068</v>
+        <v>240.3860284626675</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.949033116454079</v>
+        <v>3.852266232908156</v>
       </c>
       <c r="T100">
-        <v>24.80550771855544</v>
+        <v>49.61101543711087</v>
       </c>
       <c r="U100">
         <v>0.1433941048847012</v>
       </c>
       <c r="V100">
-        <v>0.2878942621602419</v>
+        <v>0.2849862393101385</v>
       </c>
       <c r="W100">
-        <v>0.1021117648607918</v>
+        <v>0.1025287581943667</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8467478298830643</v>
+        <v>0.8381948215004072</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1400261329415046</v>
-      </c>
-      <c r="C101">
-        <v>-11364.30813374431</v>
-      </c>
-      <c r="D101">
-        <v>15173.13586625569</v>
-      </c>
-      <c r="E101">
-        <v>29550.044</v>
-      </c>
-      <c r="F101">
-        <v>30170.844</v>
-      </c>
-      <c r="G101">
-        <v>3633.4</v>
-      </c>
-      <c r="H101">
-        <v>29854.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>4328.7</v>
-      </c>
-      <c r="K101">
-        <v>702.3999999999996</v>
-      </c>
-      <c r="L101">
-        <v>3626.3</v>
-      </c>
-      <c r="M101">
-        <v>4326.321168995958</v>
-      </c>
-      <c r="N101">
-        <v>-700.0211689959579</v>
-      </c>
-      <c r="O101">
-        <v>-238.0071974586257</v>
-      </c>
-      <c r="P101">
-        <v>-462.0139715373322</v>
-      </c>
-      <c r="Q101">
-        <v>240.3860284626675</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.852266232908156</v>
-      </c>
-      <c r="T101">
-        <v>49.61101543711087</v>
-      </c>
-      <c r="U101">
-        <v>0.1433941048847012</v>
-      </c>
-      <c r="V101">
-        <v>0.2849862393101385</v>
-      </c>
-      <c r="W101">
-        <v>0.1025287581943667</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Caa/CCC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8381948215004072</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
